--- a/BELGRANO 1646/Junio/JUNIO-BLG1646.xlsx
+++ b/BELGRANO 1646/Junio/JUNIO-BLG1646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44982A5-B39C-4AA8-B98F-A243AA8C48C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6A0776-1A04-42B9-9330-1A2465DB1E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$146</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$153</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="178">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -480,54 +480,30 @@
     <t>FEUILLANT, GASTON</t>
   </si>
   <si>
-    <t>Ferreteria</t>
-  </si>
-  <si>
     <t>Contessi provision y colocacion de 60 lts de aceite hidraulico en la sede del monta auto</t>
   </si>
   <si>
     <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 05/05</t>
   </si>
   <si>
-    <t>Arreglo de motor retirado y reemplazado por uno nuevo en montavehiculos</t>
-  </si>
-  <si>
     <t>Debito 12/05</t>
   </si>
   <si>
     <t>Pago mis cuentas 12/05</t>
   </si>
   <si>
-    <t>Fumigacion 12/05</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Ajuste de todas las puertas y reparacion de la puerta principal 16/05</t>
-  </si>
-  <si>
     <t>Camaras del sur 19/05 - compra y colocacion camaras de entradas (pileta y gimnasio)</t>
   </si>
   <si>
-    <t>Servisur - cambio de luminarias 19/05</t>
-  </si>
-  <si>
     <t>Numero 1859135 Debito automatico 5/05</t>
   </si>
   <si>
-    <t xml:space="preserve">Antonio santillan plomero - Arreglo tanque </t>
-  </si>
-  <si>
     <t>Salvatierra limpieza de columna de baño desde piso 3 (inclusive) hasta el piso 10 (inclusive) - 20/05</t>
   </si>
   <si>
-    <t>Guido Alterini - Jardineria : Adelanto compra pasto</t>
-  </si>
-  <si>
     <t>Kromacolor  -  Compra de materiales : Sellador Sika 23/05</t>
   </si>
   <si>
-    <t>Doartero Julio - Emergencia purga de grupo electrogeno por falta de combustible 26/05</t>
-  </si>
-  <si>
     <t>Compra Fabio Tolosa - Combustible 19/05</t>
   </si>
   <si>
@@ -555,18 +531,12 @@
     <t>Reparacion puerta SUM 02/05</t>
   </si>
   <si>
-    <t>Preinstalacion nueva aire acondicionado SUM - Leandro Gomez 27/5</t>
-  </si>
-  <si>
     <t>Compra de Juan Manuel Villa - Combustible 23/05</t>
   </si>
   <si>
     <t>Debito 27/05</t>
   </si>
   <si>
-    <t>Gabriel Villegas - Envio carte documento Edesur</t>
-  </si>
-  <si>
     <t>ADS - Imputado en el mes de Marzo y transferido finalizada las charlas por la desvinculacion</t>
   </si>
   <si>
@@ -592,6 +562,39 @@
   </si>
   <si>
     <t>Ingreso mes de MAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kromacolor </t>
+  </si>
+  <si>
+    <t>Contessi</t>
+  </si>
+  <si>
+    <t>Servisur - cambio de luminarias 18/06</t>
+  </si>
+  <si>
+    <t>Fumigacion 10/06</t>
+  </si>
+  <si>
+    <t>SA seguridad - 10/06 - Servicio tecnico realizado en motor de porton, se lubrica caja reductora</t>
+  </si>
+  <si>
+    <t>Zaffalon Veronica - Por vaciamiento de monta coches con agua y mucho residuo de aceite, extraido con bomba y balde por la pesadez de lo econtrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servisur </t>
+  </si>
+  <si>
+    <t>Eba - Elcetrica de buenos aires</t>
+  </si>
+  <si>
+    <t>Casa ruan - materiales de trabajo</t>
+  </si>
+  <si>
+    <t>Ferreteria Arcamone - Yeso de 5 kilos</t>
+  </si>
+  <si>
+    <t>Presupuesto 18/06</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1322,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1622,6 +1625,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1700,15 +1718,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1718,68 +1727,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2146,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N156"/>
+  <dimension ref="A1:N163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -2156,7 +2166,8 @@
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" customWidth="1"/>
@@ -2203,10 +2214,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
@@ -2234,26 +2245,26 @@
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="202" t="s">
+      <c r="B14" s="207" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="203"/>
-      <c r="D14" s="204"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="209"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="205"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="207"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="211"/>
+      <c r="D15" s="212"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="205"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="207"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="211"/>
+      <c r="D16" s="212"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="208"/>
-      <c r="C17" s="209"/>
-      <c r="D17" s="210"/>
+      <c r="B17" s="213"/>
+      <c r="C17" s="214"/>
+      <c r="D17" s="215"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
@@ -2278,7 +2289,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="130"/>
@@ -2341,7 +2352,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="121" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2710,7 +2721,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="94" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="98"/>
@@ -2732,20 +2743,20 @@
         <v>5</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C53" s="7"/>
-      <c r="D53" s="113">
-        <f>102143.27+6011.02+54099.18</f>
-        <v>162253.47</v>
+      <c r="D53" s="256">
+        <f>55568.88+6174.32+104266.16</f>
+        <v>166009.35999999999</v>
       </c>
       <c r="E53" s="134">
         <f>D53*91.91%</f>
-        <v>149127.16427699997</v>
+        <v>152579.20277599996</v>
       </c>
       <c r="F53" s="134">
         <f>D53*8.09%</f>
-        <v>13126.305722999999</v>
+        <v>13430.157223999999</v>
       </c>
       <c r="H53" s="150"/>
     </row>
@@ -2753,20 +2764,20 @@
       <c r="A54" s="94" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>144</v>
+      <c r="B54" s="258" t="s">
+        <v>142</v>
       </c>
       <c r="C54" s="7"/>
-      <c r="D54" s="113">
-        <v>532295.61</v>
+      <c r="D54" s="256">
+        <v>546846.93999999994</v>
       </c>
       <c r="E54" s="134">
         <f>D54*91.91%</f>
-        <v>489232.89515099995</v>
+        <v>502607.02255399991</v>
       </c>
       <c r="F54" s="134">
         <f>D54*8.09%</f>
-        <v>43062.714848999996</v>
+        <v>44239.917445999992</v>
       </c>
       <c r="H54" s="150"/>
     </row>
@@ -2778,19 +2789,19 @@
       <c r="C55" s="96"/>
       <c r="D55" s="108">
         <f>SUM(D52:D54)</f>
-        <v>699569.08</v>
+        <v>717876.29999999993</v>
       </c>
       <c r="E55" s="108">
         <f t="shared" ref="E55:F55" si="7">SUM(E52:E54)</f>
-        <v>642973.94142799987</v>
+        <v>659800.10732999991</v>
       </c>
       <c r="F55" s="108">
         <f t="shared" si="7"/>
-        <v>56595.138571999996</v>
+        <v>58076.192669999989</v>
       </c>
       <c r="G55" s="109">
         <f>E55+F55</f>
-        <v>699569.07999999984</v>
+        <v>717876.29999999993</v>
       </c>
       <c r="H55" s="150" t="str">
         <f>IF(D55=G55, "", "Error")</f>
@@ -2810,7 +2821,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B57" s="176"/>
       <c r="C57" s="177"/>
@@ -2845,157 +2856,153 @@
       </c>
       <c r="B58" s="176"/>
       <c r="C58" s="177"/>
-      <c r="D58" s="113">
-        <v>330000</v>
+      <c r="D58" s="256">
+        <v>1350000</v>
       </c>
       <c r="E58" s="149">
         <f>D58</f>
-        <v>330000</v>
+        <v>1350000</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="109">
         <f>D58</f>
-        <v>330000</v>
+        <v>1350000</v>
       </c>
       <c r="H58" s="161">
         <f>E58+F58</f>
-        <v>330000</v>
+        <v>1350000</v>
       </c>
       <c r="I58" s="178">
-        <f t="shared" ref="I58:I86" si="11">H58-D58</f>
+        <f t="shared" ref="I58:I93" si="11">H58-D58</f>
         <v>0</v>
       </c>
       <c r="J58" s="178">
-        <f t="shared" ref="J58:J86" si="12">G58-D58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="121" t="s">
+        <f t="shared" ref="J58:J93" si="12">G58-D58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="190" t="s">
+        <v>168</v>
+      </c>
+      <c r="B59" s="176"/>
+      <c r="C59" s="177"/>
+      <c r="D59" s="256">
+        <v>5000</v>
+      </c>
+      <c r="E59" s="149">
+        <f>D59</f>
+        <v>5000</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="109">
+        <f>D59</f>
+        <v>5000</v>
+      </c>
+      <c r="H59" s="161">
+        <f>E59+F59</f>
+        <v>5000</v>
+      </c>
+      <c r="I59" s="178">
+        <f>H59-D59</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="178"/>
+    </row>
+    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="B59" s="163"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="113">
-        <v>143638</v>
-      </c>
-      <c r="E59" s="149">
-        <f t="shared" ref="E59:E63" si="13">D59*91.91%</f>
-        <v>132017.68579999998</v>
-      </c>
-      <c r="F59" s="134">
-        <f t="shared" ref="F59:F63" si="14">D59*8.09%</f>
-        <v>11620.314200000001</v>
-      </c>
-      <c r="G59" s="109">
-        <f t="shared" ref="G59:G86" si="15">D59</f>
-        <v>143638</v>
-      </c>
-      <c r="H59" s="161">
-        <f t="shared" ref="H59:H86" si="16">E59+F59</f>
-        <v>143637.99999999997</v>
-      </c>
-      <c r="I59" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="94" t="s">
-        <v>172</v>
-      </c>
-      <c r="B60" s="7"/>
+      <c r="B60" s="163"/>
       <c r="C60" s="7"/>
       <c r="D60" s="113">
+        <v>143638</v>
+      </c>
+      <c r="E60" s="149">
+        <f t="shared" ref="E60:E64" si="13">D60*91.91%</f>
+        <v>132017.68579999998</v>
+      </c>
+      <c r="F60" s="134">
+        <f t="shared" ref="F60:F64" si="14">D60*8.09%</f>
+        <v>11620.314200000001</v>
+      </c>
+      <c r="G60" s="109">
+        <f t="shared" ref="G60:G93" si="15">D60</f>
+        <v>143638</v>
+      </c>
+      <c r="H60" s="161">
+        <f t="shared" ref="H60:H93" si="16">E60+F60</f>
+        <v>143637.99999999997</v>
+      </c>
+      <c r="I60" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="256">
         <v>129675</v>
       </c>
-      <c r="E60" s="149">
+      <c r="E61" s="149">
         <f t="shared" si="13"/>
         <v>119184.2925</v>
       </c>
-      <c r="F60" s="134">
+      <c r="F61" s="134">
         <f t="shared" si="14"/>
         <v>10490.7075</v>
       </c>
-      <c r="G60" s="109">
+      <c r="G61" s="109">
         <f t="shared" si="15"/>
         <v>129675</v>
       </c>
-      <c r="H60" s="161">
+      <c r="H61" s="161">
         <f t="shared" si="16"/>
         <v>129675</v>
       </c>
-      <c r="I60" s="178">
+      <c r="I61" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J60" s="178">
+      <c r="J61" s="178">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="94" t="s">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="113">
+      <c r="B62" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="113">
         <v>74622</v>
       </c>
-      <c r="E61" s="149">
-        <f>D61*91.91%</f>
+      <c r="E62" s="149">
+        <f>D62*91.91%</f>
         <v>68585.080199999997</v>
       </c>
-      <c r="F61" s="134">
+      <c r="F62" s="134">
         <f t="shared" si="14"/>
         <v>6036.9197999999997</v>
       </c>
-      <c r="G61" s="109">
+      <c r="G62" s="109">
         <f t="shared" si="15"/>
         <v>74622</v>
       </c>
-      <c r="H61" s="161">
-        <f>E61+F61</f>
+      <c r="H62" s="161">
+        <f>E62+F62</f>
         <v>74622</v>
-      </c>
-      <c r="I61" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="113"/>
-      <c r="E62" s="149">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="134">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="G62" s="109">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="161">
-        <f t="shared" si="16"/>
-        <v>0</v>
       </c>
       <c r="I62" s="178">
         <f t="shared" si="11"/>
@@ -3007,31 +3014,29 @@
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="129" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63" s="98" t="s">
-        <v>166</v>
-      </c>
-      <c r="C63" s="98"/>
-      <c r="D63" s="113">
-        <v>846331.1</v>
+      <c r="A63" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="256">
+        <v>614674.98</v>
       </c>
       <c r="E63" s="149">
         <f t="shared" si="13"/>
-        <v>777862.91400999995</v>
+        <v>564947.77411799994</v>
       </c>
       <c r="F63" s="134">
         <f t="shared" si="14"/>
-        <v>68468.185989999998</v>
+        <v>49727.205881999995</v>
       </c>
       <c r="G63" s="109">
         <f t="shared" si="15"/>
-        <v>846331.1</v>
+        <v>614674.98</v>
       </c>
       <c r="H63" s="161">
         <f t="shared" si="16"/>
-        <v>846331.1</v>
+        <v>614674.98</v>
       </c>
       <c r="I63" s="178">
         <f t="shared" si="11"/>
@@ -3043,26 +3048,31 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="98" t="s">
-        <v>147</v>
-      </c>
-      <c r="B64" s="179"/>
-      <c r="C64" s="180"/>
+      <c r="A64" s="129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="98" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" s="98"/>
       <c r="D64" s="113">
-        <v>235500</v>
+        <v>846331.1</v>
       </c>
       <c r="E64" s="149">
-        <f t="shared" ref="E64:E76" si="17">D64</f>
-        <v>235500</v>
-      </c>
-      <c r="F64" s="134"/>
+        <f t="shared" si="13"/>
+        <v>777862.91400999995</v>
+      </c>
+      <c r="F64" s="134">
+        <f t="shared" si="14"/>
+        <v>68468.185989999998</v>
+      </c>
       <c r="G64" s="109">
         <f t="shared" si="15"/>
-        <v>235500</v>
+        <v>846331.1</v>
       </c>
       <c r="H64" s="161">
         <f t="shared" si="16"/>
-        <v>235500</v>
+        <v>846331.1</v>
       </c>
       <c r="I64" s="178">
         <f t="shared" si="11"/>
@@ -3074,29 +3084,26 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="214" t="s">
-        <v>162</v>
-      </c>
-      <c r="B65" s="215"/>
-      <c r="C65" s="216"/>
+      <c r="A65" s="98" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="179"/>
+      <c r="C65" s="180"/>
       <c r="D65" s="113">
-        <v>111026</v>
+        <v>235500</v>
       </c>
       <c r="E65" s="149">
-        <f>D65*91.91%</f>
-        <v>102043.99659999998</v>
-      </c>
-      <c r="F65" s="149">
-        <f>D65*8.09%</f>
-        <v>8982.0033999999996</v>
-      </c>
+        <f t="shared" ref="E65:E81" si="17">D65</f>
+        <v>235500</v>
+      </c>
+      <c r="F65" s="134"/>
       <c r="G65" s="109">
         <f t="shared" si="15"/>
-        <v>111026</v>
+        <v>235500</v>
       </c>
       <c r="H65" s="161">
-        <f>E65+F65</f>
-        <v>111025.99999999999</v>
+        <f t="shared" si="16"/>
+        <v>235500</v>
       </c>
       <c r="I65" s="178">
         <f t="shared" si="11"/>
@@ -3107,66 +3114,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="214" t="s">
-        <v>157</v>
-      </c>
-      <c r="B66" s="215"/>
-      <c r="C66" s="216"/>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="219" t="s">
+        <v>154</v>
+      </c>
+      <c r="B66" s="220"/>
+      <c r="C66" s="221"/>
       <c r="D66" s="113">
+        <v>111026</v>
+      </c>
+      <c r="E66" s="149">
+        <f>D66*91.91%</f>
+        <v>102043.99659999998</v>
+      </c>
+      <c r="F66" s="149">
+        <f>D66*8.09%</f>
+        <v>8982.0033999999996</v>
+      </c>
+      <c r="G66" s="109">
+        <f t="shared" si="15"/>
+        <v>111026</v>
+      </c>
+      <c r="H66" s="161">
+        <f>E66+F66</f>
+        <v>111025.99999999999</v>
+      </c>
+      <c r="I66" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="219" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="220"/>
+      <c r="C67" s="221"/>
+      <c r="D67" s="113">
         <v>104006.06</v>
       </c>
-      <c r="E66" s="149">
-        <f t="shared" ref="E66:E73" si="18">D66*91.91%</f>
+      <c r="E67" s="149">
+        <f t="shared" ref="E67:E74" si="18">D67*91.91%</f>
         <v>95591.969745999988</v>
       </c>
-      <c r="F66" s="149">
-        <f t="shared" ref="F66:F73" si="19">D66*8.09%</f>
+      <c r="F67" s="149">
+        <f t="shared" ref="F67:F74" si="19">D67*8.09%</f>
         <v>8414.0902540000006</v>
       </c>
-      <c r="G66" s="109">
-        <f>D66</f>
+      <c r="G67" s="109">
+        <f>D67</f>
         <v>104006.06</v>
       </c>
-      <c r="H66" s="161">
+      <c r="H67" s="161">
         <f t="shared" si="16"/>
         <v>104006.05999999998</v>
       </c>
-      <c r="I66" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="214" t="s">
-        <v>157</v>
-      </c>
-      <c r="B67" s="215"/>
-      <c r="C67" s="216"/>
-      <c r="D67" s="113">
-        <f>104002.96</f>
-        <v>104002.96</v>
-      </c>
-      <c r="E67" s="149">
-        <f t="shared" si="18"/>
-        <v>95589.120536000002</v>
-      </c>
-      <c r="F67" s="149">
-        <f t="shared" si="19"/>
-        <v>8413.8394640000006</v>
-      </c>
-      <c r="G67" s="109">
-        <f t="shared" ref="G67:G73" si="20">D67</f>
-        <v>104002.96</v>
-      </c>
-      <c r="H67" s="161">
-        <f t="shared" si="16"/>
-        <v>104002.96</v>
-      </c>
       <c r="I67" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -3177,11 +3183,11 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="214" t="s">
-        <v>157</v>
-      </c>
-      <c r="B68" s="215"/>
-      <c r="C68" s="216"/>
+      <c r="A68" s="219" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="220"/>
+      <c r="C68" s="221"/>
       <c r="D68" s="113">
         <f>104002.96</f>
         <v>104002.96</v>
@@ -3195,7 +3201,7 @@
         <v>8413.8394640000006</v>
       </c>
       <c r="G68" s="109">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G68:G74" si="20">D68</f>
         <v>104002.96</v>
       </c>
       <c r="H68" s="161">
@@ -3212,11 +3218,11 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="214" t="s">
-        <v>157</v>
-      </c>
-      <c r="B69" s="215"/>
-      <c r="C69" s="216"/>
+      <c r="A69" s="219" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="220"/>
+      <c r="C69" s="221"/>
       <c r="D69" s="113">
         <f>104002.96</f>
         <v>104002.96</v>
@@ -3247,29 +3253,30 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="228" t="s">
-        <v>156</v>
-      </c>
-      <c r="B70" s="229"/>
-      <c r="C70" s="230"/>
+      <c r="A70" s="219" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" s="220"/>
+      <c r="C70" s="221"/>
       <c r="D70" s="113">
-        <v>100419.01</v>
+        <f>104002.96</f>
+        <v>104002.96</v>
       </c>
       <c r="E70" s="149">
         <f t="shared" si="18"/>
-        <v>92295.112090999988</v>
+        <v>95589.120536000002</v>
       </c>
       <c r="F70" s="149">
         <f t="shared" si="19"/>
-        <v>8123.8979089999993</v>
+        <v>8413.8394640000006</v>
       </c>
       <c r="G70" s="109">
         <f t="shared" si="20"/>
-        <v>100419.01</v>
+        <v>104002.96</v>
       </c>
       <c r="H70" s="161">
         <f t="shared" si="16"/>
-        <v>100419.00999999998</v>
+        <v>104002.96</v>
       </c>
       <c r="I70" s="178">
         <f t="shared" si="11"/>
@@ -3281,29 +3288,29 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="228" t="s">
-        <v>156</v>
-      </c>
-      <c r="B71" s="229"/>
-      <c r="C71" s="230"/>
+      <c r="A71" s="202" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="203"/>
+      <c r="C71" s="204"/>
       <c r="D71" s="113">
-        <v>97003.05</v>
+        <v>100419.01</v>
       </c>
       <c r="E71" s="149">
         <f t="shared" si="18"/>
-        <v>89155.503254999989</v>
+        <v>92295.112090999988</v>
       </c>
       <c r="F71" s="149">
         <f t="shared" si="19"/>
-        <v>7847.5467450000006</v>
+        <v>8123.8979089999993</v>
       </c>
       <c r="G71" s="109">
         <f t="shared" si="20"/>
-        <v>97003.05</v>
+        <v>100419.01</v>
       </c>
       <c r="H71" s="161">
         <f t="shared" si="16"/>
-        <v>97003.049999999988</v>
+        <v>100419.00999999998</v>
       </c>
       <c r="I71" s="178">
         <f t="shared" si="11"/>
@@ -3315,29 +3322,29 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="228" t="s">
-        <v>155</v>
-      </c>
-      <c r="B72" s="229"/>
-      <c r="C72" s="230"/>
+      <c r="A72" s="202" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72" s="203"/>
+      <c r="C72" s="204"/>
       <c r="D72" s="113">
-        <v>98393.96</v>
+        <v>97003.05</v>
       </c>
       <c r="E72" s="149">
         <f t="shared" si="18"/>
-        <v>90433.888636000003</v>
+        <v>89155.503254999989</v>
       </c>
       <c r="F72" s="149">
         <f t="shared" si="19"/>
-        <v>7960.0713640000004</v>
+        <v>7847.5467450000006</v>
       </c>
       <c r="G72" s="109">
         <f t="shared" si="20"/>
-        <v>98393.96</v>
+        <v>97003.05</v>
       </c>
       <c r="H72" s="161">
         <f t="shared" si="16"/>
-        <v>98393.96</v>
+        <v>97003.049999999988</v>
       </c>
       <c r="I72" s="178">
         <f t="shared" si="11"/>
@@ -3349,29 +3356,29 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="197" t="s">
-        <v>165</v>
-      </c>
-      <c r="B73" s="195"/>
-      <c r="C73" s="196"/>
+      <c r="A73" s="202" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" s="203"/>
+      <c r="C73" s="204"/>
       <c r="D73" s="113">
-        <v>99259.05</v>
+        <v>98393.96</v>
       </c>
       <c r="E73" s="149">
         <f t="shared" si="18"/>
-        <v>91228.99285499999</v>
+        <v>90433.888636000003</v>
       </c>
       <c r="F73" s="149">
         <f t="shared" si="19"/>
-        <v>8030.0571449999998</v>
+        <v>7960.0713640000004</v>
       </c>
       <c r="G73" s="109">
         <f t="shared" si="20"/>
-        <v>99259.05</v>
+        <v>98393.96</v>
       </c>
       <c r="H73" s="161">
         <f t="shared" si="16"/>
-        <v>99259.049999999988</v>
+        <v>98393.96</v>
       </c>
       <c r="I73" s="178">
         <f t="shared" si="11"/>
@@ -3382,58 +3389,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="225" t="s">
-        <v>145</v>
-      </c>
-      <c r="B74" s="226"/>
-      <c r="C74" s="227"/>
+    <row r="74" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="197" t="s">
+        <v>156</v>
+      </c>
+      <c r="B74" s="195"/>
+      <c r="C74" s="196"/>
       <c r="D74" s="113">
+        <v>99259.05</v>
+      </c>
+      <c r="E74" s="149">
+        <f t="shared" si="18"/>
+        <v>91228.99285499999</v>
+      </c>
+      <c r="F74" s="149">
+        <f t="shared" si="19"/>
+        <v>8030.0571449999998</v>
+      </c>
+      <c r="G74" s="109">
+        <f t="shared" si="20"/>
+        <v>99259.05</v>
+      </c>
+      <c r="H74" s="161">
+        <f t="shared" si="16"/>
+        <v>99259.049999999988</v>
+      </c>
+      <c r="I74" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="230" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="231"/>
+      <c r="C75" s="232"/>
+      <c r="D75" s="256">
         <v>66000</v>
       </c>
-      <c r="E74" s="149">
+      <c r="E75" s="149">
         <f t="shared" si="17"/>
         <v>66000</v>
-      </c>
-      <c r="F74" s="134"/>
-      <c r="G74" s="109">
-        <f t="shared" si="15"/>
-        <v>66000</v>
-      </c>
-      <c r="H74" s="161">
-        <f t="shared" si="16"/>
-        <v>66000</v>
-      </c>
-      <c r="I74" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="231" t="s">
-        <v>151</v>
-      </c>
-      <c r="B75" s="232"/>
-      <c r="C75" s="233"/>
-      <c r="D75" s="113">
-        <v>218400</v>
-      </c>
-      <c r="E75" s="149">
-        <f t="shared" si="17"/>
-        <v>218400</v>
       </c>
       <c r="F75" s="134"/>
       <c r="G75" s="109">
         <f t="shared" si="15"/>
-        <v>218400</v>
+        <v>66000</v>
       </c>
       <c r="H75" s="161">
         <f t="shared" si="16"/>
-        <v>218400</v>
+        <v>66000</v>
       </c>
       <c r="I75" s="178">
         <f t="shared" si="11"/>
@@ -3445,26 +3455,26 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="193" t="s">
-        <v>148</v>
-      </c>
-      <c r="B76" s="194"/>
-      <c r="C76" s="189"/>
+      <c r="A76" s="233" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="234"/>
+      <c r="C76" s="235"/>
       <c r="D76" s="113">
-        <v>35000</v>
+        <v>218400</v>
       </c>
       <c r="E76" s="149">
         <f t="shared" si="17"/>
-        <v>35000</v>
+        <v>218400</v>
       </c>
       <c r="F76" s="134"/>
       <c r="G76" s="109">
         <f t="shared" si="15"/>
-        <v>35000</v>
+        <v>218400</v>
       </c>
       <c r="H76" s="161">
         <f t="shared" si="16"/>
-        <v>35000</v>
+        <v>218400</v>
       </c>
       <c r="I76" s="178">
         <f t="shared" si="11"/>
@@ -3476,62 +3486,54 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B77" s="7" t="s">
+      <c r="A77" s="259" t="s">
         <v>173</v>
       </c>
+      <c r="B77" s="7"/>
       <c r="C77" s="7"/>
-      <c r="D77" s="113">
-        <v>79895</v>
+      <c r="D77" s="256">
+        <v>315000</v>
       </c>
       <c r="E77" s="149">
-        <f t="shared" ref="E77:E84" si="21">D77</f>
-        <v>79895</v>
-      </c>
-      <c r="F77" s="7"/>
+        <f t="shared" si="17"/>
+        <v>315000</v>
+      </c>
+      <c r="F77" s="134"/>
       <c r="G77" s="109">
         <f t="shared" si="15"/>
-        <v>79895</v>
+        <v>315000</v>
       </c>
       <c r="H77" s="161">
         <f t="shared" si="16"/>
-        <v>79895</v>
+        <v>315000</v>
       </c>
       <c r="I77" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J77" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="94" t="s">
-        <v>139</v>
-      </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="113">
-        <v>6530.7</v>
+      <c r="J77" s="178"/>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="B78" s="194"/>
+      <c r="C78" s="189"/>
+      <c r="D78" s="256">
+        <v>35000</v>
       </c>
       <c r="E78" s="149">
-        <f t="shared" ref="E78:E82" si="22">D78*91.91%</f>
-        <v>6002.3663699999997</v>
-      </c>
-      <c r="F78" s="134">
-        <f t="shared" ref="F78:F82" si="23">D78*8.09%</f>
-        <v>528.33362999999997</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>35000</v>
+      </c>
+      <c r="F78" s="134"/>
       <c r="G78" s="109">
         <f t="shared" si="15"/>
-        <v>6530.7</v>
+        <v>35000</v>
       </c>
       <c r="H78" s="161">
         <f t="shared" si="16"/>
-        <v>6530.7</v>
+        <v>35000</v>
       </c>
       <c r="I78" s="178">
         <f t="shared" si="11"/>
@@ -3542,95 +3544,83 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="94" t="s">
-        <v>150</v>
-      </c>
-      <c r="B79" s="7"/>
+    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="258" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="114"/>
       <c r="C79" s="7"/>
-      <c r="D79" s="113">
-        <v>220000</v>
+      <c r="D79" s="256">
+        <v>143416.32999999999</v>
       </c>
       <c r="E79" s="149">
-        <f t="shared" si="22"/>
-        <v>202201.99999999997</v>
-      </c>
-      <c r="F79" s="134">
-        <f t="shared" si="23"/>
-        <v>17798</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>143416.32999999999</v>
+      </c>
+      <c r="F79" s="134"/>
       <c r="G79" s="109">
         <f t="shared" si="15"/>
-        <v>220000</v>
+        <v>143416.32999999999</v>
       </c>
       <c r="H79" s="161">
         <f t="shared" si="16"/>
-        <v>219999.99999999997</v>
+        <v>143416.32999999999</v>
       </c>
       <c r="I79" s="178">
-        <f>H79-D79</f>
-        <v>0</v>
-      </c>
-      <c r="J79" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="94" t="s">
-        <v>154</v>
-      </c>
-      <c r="B80" s="7"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J79" s="178"/>
+    </row>
+    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="114"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="113">
-        <v>150000</v>
+      <c r="D80" s="256">
+        <v>12100</v>
       </c>
       <c r="E80" s="149">
-        <f t="shared" si="22"/>
-        <v>137865</v>
-      </c>
-      <c r="F80" s="134">
-        <f t="shared" si="23"/>
-        <v>12135</v>
-      </c>
+        <f t="shared" si="17"/>
+        <v>12100</v>
+      </c>
+      <c r="F80" s="134"/>
       <c r="G80" s="109">
         <f t="shared" si="15"/>
-        <v>150000</v>
+        <v>12100</v>
       </c>
       <c r="H80" s="161">
         <f t="shared" si="16"/>
-        <v>150000</v>
+        <v>12100</v>
       </c>
       <c r="I80" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J80" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B81" s="7"/>
+      <c r="J80" s="178"/>
+    </row>
+    <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="257" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="114"/>
       <c r="C81" s="7"/>
-      <c r="D81" s="113">
-        <v>120000</v>
+      <c r="D81" s="256">
+        <v>4200</v>
       </c>
       <c r="E81" s="149">
-        <f t="shared" si="21"/>
-        <v>120000</v>
+        <f t="shared" si="17"/>
+        <v>4200</v>
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="109">
         <f t="shared" si="15"/>
-        <v>120000</v>
+        <v>4200</v>
       </c>
       <c r="H81" s="161">
         <f t="shared" si="16"/>
-        <v>120000</v>
+        <v>4200</v>
       </c>
       <c r="I81" s="178">
         <f t="shared" si="11"/>
@@ -3642,29 +3632,29 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="94" t="s">
-        <v>152</v>
-      </c>
-      <c r="B82" s="114"/>
+      <c r="A82" s="255" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82" s="7"/>
       <c r="C82" s="7"/>
-      <c r="D82" s="113">
-        <v>245000</v>
+      <c r="D82" s="256">
+        <v>736429.26</v>
       </c>
       <c r="E82" s="149">
-        <f t="shared" si="22"/>
-        <v>225179.49999999997</v>
+        <f t="shared" ref="E82:E89" si="21">D82*91.91%</f>
+        <v>676852.13286599994</v>
       </c>
       <c r="F82" s="134">
-        <f t="shared" si="23"/>
-        <v>19820.5</v>
+        <f t="shared" ref="F82:F90" si="22">D82*8.09%</f>
+        <v>59577.127134000002</v>
       </c>
       <c r="G82" s="109">
         <f t="shared" si="15"/>
-        <v>245000</v>
+        <v>736429.26</v>
       </c>
       <c r="H82" s="161">
         <f t="shared" si="16"/>
-        <v>244999.99999999997</v>
+        <v>736429.25999999989</v>
       </c>
       <c r="I82" s="178">
         <f t="shared" si="11"/>
@@ -3676,26 +3666,29 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B83" s="114"/>
+      <c r="A83" s="255" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="7"/>
       <c r="C83" s="7"/>
-      <c r="D83" s="113">
-        <v>120000</v>
+      <c r="D83" s="256">
+        <v>232510.18</v>
       </c>
       <c r="E83" s="149">
         <f t="shared" si="21"/>
-        <v>120000</v>
-      </c>
-      <c r="F83" s="7"/>
+        <v>213700.10643799999</v>
+      </c>
+      <c r="F83" s="134">
+        <f t="shared" si="22"/>
+        <v>18810.073561999998</v>
+      </c>
       <c r="G83" s="109">
         <f t="shared" si="15"/>
-        <v>120000</v>
+        <v>232510.18</v>
       </c>
       <c r="H83" s="161">
         <f t="shared" si="16"/>
-        <v>120000</v>
+        <v>232510.18</v>
       </c>
       <c r="I83" s="178">
         <f t="shared" si="11"/>
@@ -3707,26 +3700,29 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B84" s="114"/>
+      <c r="A84" s="255" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" s="7"/>
       <c r="C84" s="7"/>
-      <c r="D84" s="113">
-        <v>480000</v>
+      <c r="D84" s="256">
+        <v>357622.29</v>
       </c>
       <c r="E84" s="149">
         <f t="shared" si="21"/>
-        <v>480000</v>
-      </c>
-      <c r="F84" s="7"/>
+        <v>328690.64673899993</v>
+      </c>
+      <c r="F84" s="134">
+        <f t="shared" si="22"/>
+        <v>28931.643260999997</v>
+      </c>
       <c r="G84" s="109">
         <f t="shared" si="15"/>
-        <v>480000</v>
+        <v>357622.29</v>
       </c>
       <c r="H84" s="161">
         <f t="shared" si="16"/>
-        <v>480000</v>
+        <v>357622.28999999992</v>
       </c>
       <c r="I84" s="178">
         <f t="shared" si="11"/>
@@ -3738,220 +3734,352 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="94" t="s">
+      <c r="A85" s="255" t="s">
         <v>167</v>
       </c>
-      <c r="B85" s="114"/>
+      <c r="B85" s="7"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="113">
-        <v>250000</v>
+      <c r="D85" s="256">
+        <v>358487.12</v>
       </c>
       <c r="E85" s="149">
-        <f t="shared" ref="E85:E86" si="24">D85*91.91%</f>
-        <v>229774.99999999997</v>
+        <f t="shared" si="21"/>
+        <v>329485.51199199999</v>
       </c>
       <c r="F85" s="134">
-        <f t="shared" ref="F85:F86" si="25">D85*8.09%</f>
-        <v>20225</v>
+        <f t="shared" si="22"/>
+        <v>29001.608007999999</v>
       </c>
       <c r="G85" s="109">
         <f t="shared" si="15"/>
-        <v>250000</v>
-      </c>
-      <c r="H85" s="161"/>
-      <c r="I85" s="178"/>
+        <v>358487.12</v>
+      </c>
+      <c r="H85" s="161">
+        <f t="shared" si="16"/>
+        <v>358487.12</v>
+      </c>
+      <c r="I85" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="J85" s="178">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="129" t="s">
-        <v>158</v>
-      </c>
-      <c r="B86" s="114"/>
-      <c r="C86" s="162"/>
-      <c r="D86" s="113">
+      <c r="A86" s="255" t="s">
+        <v>167</v>
+      </c>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="256">
+        <v>186859.86</v>
+      </c>
+      <c r="E86" s="149">
+        <f t="shared" si="21"/>
+        <v>171742.89732599998</v>
+      </c>
+      <c r="F86" s="134">
+        <f t="shared" si="22"/>
+        <v>15116.962673999999</v>
+      </c>
+      <c r="G86" s="109">
+        <f t="shared" si="15"/>
+        <v>186859.86</v>
+      </c>
+      <c r="H86" s="161">
+        <f t="shared" si="16"/>
+        <v>186859.86</v>
+      </c>
+      <c r="I86" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J86" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="257" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="256">
+        <v>36300</v>
+      </c>
+      <c r="E87" s="149">
+        <f t="shared" si="21"/>
+        <v>33363.329999999994</v>
+      </c>
+      <c r="F87" s="134">
+        <f t="shared" si="22"/>
+        <v>2936.67</v>
+      </c>
+      <c r="G87" s="109">
+        <f t="shared" si="15"/>
+        <v>36300</v>
+      </c>
+      <c r="H87" s="161">
+        <f t="shared" si="16"/>
+        <v>36299.999999999993</v>
+      </c>
+      <c r="I87" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J87" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="230" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="231"/>
+      <c r="C88" s="232"/>
+      <c r="D88" s="256">
+        <v>430000</v>
+      </c>
+      <c r="E88" s="149">
+        <f t="shared" ref="E81:E91" si="23">D88</f>
+        <v>430000</v>
+      </c>
+      <c r="F88" s="7"/>
+      <c r="G88" s="109">
+        <f t="shared" si="15"/>
+        <v>430000</v>
+      </c>
+      <c r="H88" s="161">
+        <f t="shared" si="16"/>
+        <v>430000</v>
+      </c>
+      <c r="I88" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J88" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="113">
+        <v>79895</v>
+      </c>
+      <c r="E89" s="149">
+        <f t="shared" si="21"/>
+        <v>73431.494499999986</v>
+      </c>
+      <c r="F89" s="134">
+        <f t="shared" si="22"/>
+        <v>6463.5055000000002</v>
+      </c>
+      <c r="G89" s="109">
+        <f t="shared" si="15"/>
+        <v>79895</v>
+      </c>
+      <c r="H89" s="161">
+        <f t="shared" si="16"/>
+        <v>79894.999999999985</v>
+      </c>
+      <c r="I89" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J89" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="258" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90" s="114"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="256">
+        <v>180000</v>
+      </c>
+      <c r="E90" s="149">
+        <f t="shared" si="23"/>
+        <v>180000</v>
+      </c>
+      <c r="F90" s="7">
+        <f t="shared" si="22"/>
+        <v>14562</v>
+      </c>
+      <c r="G90" s="109">
+        <f t="shared" si="15"/>
+        <v>180000</v>
+      </c>
+      <c r="H90" s="161">
+        <f t="shared" si="16"/>
+        <v>194562</v>
+      </c>
+      <c r="I90" s="178">
+        <f t="shared" si="11"/>
+        <v>14562</v>
+      </c>
+      <c r="J90" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+      <c r="B91" s="114"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="256"/>
+      <c r="E91" s="149">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F91" s="7"/>
+      <c r="G91" s="109">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="H91" s="161">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J91" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="94"/>
+      <c r="B92" s="114"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="256"/>
+      <c r="E92" s="149">
+        <f t="shared" ref="E92:E93" si="24">D92*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="134">
+        <f t="shared" ref="F92:F93" si="25">D92*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="109">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="H92" s="161"/>
+      <c r="I92" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J92" s="178">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="129" t="s">
+        <v>150</v>
+      </c>
+      <c r="B93" s="114"/>
+      <c r="C93" s="162"/>
+      <c r="D93" s="113">
         <v>50000</v>
       </c>
-      <c r="E86" s="149">
+      <c r="E93" s="149">
         <f t="shared" si="24"/>
         <v>45954.999999999993</v>
       </c>
-      <c r="F86" s="134">
+      <c r="F93" s="134">
         <f t="shared" si="25"/>
         <v>4045</v>
       </c>
-      <c r="G86" s="109">
+      <c r="G93" s="109">
         <f t="shared" si="15"/>
         <v>50000</v>
       </c>
-      <c r="H86" s="161">
+      <c r="H93" s="161">
         <f t="shared" si="16"/>
         <v>49999.999999999993</v>
       </c>
-      <c r="I86" s="178">
+      <c r="I93" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J86" s="178">
+      <c r="J93" s="178">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="155"/>
-      <c r="B87" s="156"/>
-      <c r="C87" s="156"/>
-      <c r="D87" s="166"/>
-      <c r="E87" s="149"/>
-      <c r="F87" s="134"/>
-      <c r="G87" s="109"/>
-      <c r="H87" s="161"/>
-      <c r="I87" t="str">
-        <f>IF(G87=H87, "", "Error")</f>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="155"/>
+      <c r="B94" s="156"/>
+      <c r="C94" s="156"/>
+      <c r="D94" s="166"/>
+      <c r="E94" s="149"/>
+      <c r="F94" s="134"/>
+      <c r="G94" s="109"/>
+      <c r="H94" s="161"/>
+      <c r="I94" t="str">
+        <f>IF(G94=H94, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="96" t="s">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="B88" s="96"/>
-      <c r="C88" s="96"/>
-      <c r="D88" s="108">
-        <f>SUM(D57:D87)</f>
-        <v>5422707.8099999996</v>
-      </c>
-      <c r="E88" s="108">
-        <f>SUM(E57:E87)</f>
-        <v>5176940.6636709999</v>
-      </c>
-      <c r="F88" s="108">
-        <f>SUM(F57:F87)</f>
-        <v>245767.14632900001</v>
-      </c>
-      <c r="G88" s="109">
-        <f>E88+F88</f>
-        <v>5422707.8099999996</v>
-      </c>
-      <c r="H88" s="150" t="str">
-        <f>IF(D88=G88, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I88" s="178">
-        <f>D88-G88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="185"/>
-      <c r="E89" s="115"/>
-      <c r="F89" s="7"/>
-      <c r="H89" s="150"/>
-    </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="185"/>
-      <c r="E90" s="114"/>
-      <c r="F90" s="7"/>
-      <c r="H90" s="150"/>
-    </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="185"/>
-      <c r="E91" s="114"/>
-      <c r="F91" s="7"/>
-      <c r="H91" s="150"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="94" t="s">
-        <v>161</v>
-      </c>
-      <c r="B92" s="98"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="113"/>
-      <c r="E92" s="149">
-        <f>D92*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F92" s="134">
-        <f>D92*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G92" s="160"/>
-      <c r="H92" s="150"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="113"/>
-      <c r="E93" s="164">
-        <f>D93</f>
-        <v>0</v>
-      </c>
-      <c r="F93" s="7"/>
-      <c r="H93" s="150"/>
-      <c r="I93" s="109"/>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="95" t="s">
-        <v>17</v>
-      </c>
-      <c r="B94" s="95"/>
-      <c r="C94" s="95"/>
-      <c r="D94" s="107">
-        <f>SUM(D92:D93)</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="107">
-        <f>SUM(E92:E93)</f>
-        <v>0</v>
-      </c>
-      <c r="F94" s="107">
-        <f>SUM(F92:F93)</f>
-        <v>0</v>
-      </c>
-      <c r="G94" s="109">
-        <f>E94+F94</f>
-        <v>0</v>
-      </c>
-      <c r="H94" s="150" t="str">
-        <f>IF(D94=G94, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J94" s="109"/>
-    </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="185"/>
-      <c r="E95" s="115"/>
-      <c r="F95" s="7"/>
-      <c r="H95" s="150"/>
+      <c r="B95" s="96"/>
+      <c r="C95" s="96"/>
+      <c r="D95" s="108">
+        <f>SUM(D57:D94)</f>
+        <v>8463777.129999999</v>
+      </c>
+      <c r="E95" s="108">
+        <f>SUM(E57:E94)</f>
+        <v>8077952.02128</v>
+      </c>
+      <c r="F95" s="108">
+        <f>SUM(F57:F94)</f>
+        <v>400387.10871999996</v>
+      </c>
+      <c r="G95" s="109">
+        <f>E95+F95</f>
+        <v>8478339.1300000008</v>
+      </c>
+      <c r="H95" s="150" t="str">
+        <f>IF(D95=G95, "", "Error")</f>
+        <v>Error</v>
+      </c>
+      <c r="I95" s="178">
+        <f>D95-G95</f>
+        <v>-14562.000000001863</v>
+      </c>
     </row>
     <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="185"/>
-      <c r="E96" s="114"/>
+      <c r="E96" s="115"/>
       <c r="F96" s="7"/>
       <c r="H96" s="150"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="94" t="s">
-        <v>13</v>
-      </c>
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="185"/>
@@ -3959,78 +4087,70 @@
       <c r="F97" s="7"/>
       <c r="H97" s="150"/>
     </row>
-    <row r="98" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>117</v>
-      </c>
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
       <c r="C98" s="7"/>
-      <c r="D98" s="113">
-        <v>222264.92</v>
-      </c>
-      <c r="E98" s="149">
-        <f>D98*91.91%</f>
-        <v>204283.68797199999</v>
-      </c>
-      <c r="F98" s="134">
-        <f>D98*8.09%</f>
-        <v>17981.232028000002</v>
-      </c>
+      <c r="D98" s="185"/>
+      <c r="E98" s="114"/>
+      <c r="F98" s="7"/>
       <c r="H98" s="150"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="B99" s="7"/>
+        <v>153</v>
+      </c>
+      <c r="B99" s="98"/>
       <c r="C99" s="7"/>
-      <c r="D99" s="113">
-        <v>28000</v>
+      <c r="D99" s="256">
+        <f>67780+35700</f>
+        <v>103480</v>
       </c>
       <c r="E99" s="149">
         <f>D99*91.91%</f>
-        <v>25734.799999999999</v>
+        <v>95108.467999999993</v>
       </c>
       <c r="F99" s="134">
         <f>D99*8.09%</f>
-        <v>2265.1999999999998</v>
-      </c>
+        <v>8371.5319999999992</v>
+      </c>
+      <c r="G99" s="160"/>
       <c r="H99" s="150"/>
-      <c r="J99" s="113"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
-      <c r="D100" s="185"/>
-      <c r="E100" s="116"/>
+      <c r="D100" s="113"/>
+      <c r="E100" s="164">
+        <f>D100</f>
+        <v>0</v>
+      </c>
       <c r="F100" s="7"/>
       <c r="H100" s="150"/>
-      <c r="J100" s="109"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I100" s="109"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="95" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B101" s="95"/>
       <c r="C101" s="95"/>
       <c r="D101" s="107">
-        <f>SUM(D98:D100)</f>
-        <v>250264.92</v>
+        <f>SUM(D99:D100)</f>
+        <v>103480</v>
       </c>
       <c r="E101" s="107">
-        <f>SUM(E98:E100)</f>
-        <v>230018.48797199997</v>
+        <f>SUM(E99:E100)</f>
+        <v>95108.467999999993</v>
       </c>
       <c r="F101" s="107">
-        <f>SUM(F98:F100)</f>
-        <v>20246.432028000003</v>
+        <f>SUM(F99:F100)</f>
+        <v>8371.5319999999992</v>
       </c>
       <c r="G101" s="109">
         <f>E101+F101</f>
-        <v>250264.91999999998</v>
+        <v>103480</v>
       </c>
       <c r="H101" s="150" t="str">
         <f>IF(D101=G101, "", "Error")</f>
@@ -4038,555 +4158,664 @@
       </c>
       <c r="J101" s="109"/>
     </row>
-    <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
-      <c r="D102" s="113"/>
-      <c r="E102" s="117"/>
+      <c r="D102" s="185"/>
+      <c r="E102" s="115"/>
       <c r="F102" s="7"/>
       <c r="H102" s="150"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="94" t="s">
-        <v>102</v>
-      </c>
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
-      <c r="D103" s="113">
-        <v>100104.56</v>
-      </c>
-      <c r="E103" s="149">
-        <f>D103*91.91%</f>
-        <v>92006.101095999984</v>
-      </c>
-      <c r="F103" s="134">
-        <f>D103*8.09%</f>
-        <v>8098.4589040000001</v>
-      </c>
+      <c r="D103" s="185"/>
+      <c r="E103" s="114"/>
+      <c r="F103" s="7"/>
       <c r="H103" s="150"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="185"/>
+      <c r="E104" s="114"/>
+      <c r="F104" s="7"/>
+      <c r="H104" s="150"/>
+    </row>
+    <row r="105" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="113">
+        <v>222264.92</v>
+      </c>
+      <c r="E105" s="149">
+        <f>D105*91.91%</f>
+        <v>204283.68797199999</v>
+      </c>
+      <c r="F105" s="134">
+        <f>D105*8.09%</f>
+        <v>17981.232028000002</v>
+      </c>
+      <c r="H105" s="150"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="256">
+        <v>28000</v>
+      </c>
+      <c r="E106" s="149">
+        <f>D106*91.91%</f>
+        <v>25734.799999999999</v>
+      </c>
+      <c r="F106" s="134">
+        <f>D106*8.09%</f>
+        <v>2265.1999999999998</v>
+      </c>
+      <c r="H106" s="150"/>
+      <c r="J106" s="113"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="185"/>
+      <c r="E107" s="116"/>
+      <c r="F107" s="7"/>
+      <c r="H107" s="150"/>
+      <c r="J107" s="109"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B108" s="95"/>
+      <c r="C108" s="95"/>
+      <c r="D108" s="107">
+        <f>SUM(D105:D107)</f>
+        <v>250264.92</v>
+      </c>
+      <c r="E108" s="107">
+        <f>SUM(E105:E107)</f>
+        <v>230018.48797199997</v>
+      </c>
+      <c r="F108" s="107">
+        <f>SUM(F105:F107)</f>
+        <v>20246.432028000003</v>
+      </c>
+      <c r="G108" s="109">
+        <f>E108+F108</f>
+        <v>250264.91999999998</v>
+      </c>
+      <c r="H108" s="150" t="str">
+        <f>IF(D108=G108, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J108" s="109"/>
+    </row>
+    <row r="109" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="113"/>
+      <c r="E109" s="117"/>
+      <c r="F109" s="7"/>
+      <c r="H109" s="150"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="113">
+        <v>100104.56</v>
+      </c>
+      <c r="E110" s="149">
+        <f>D110*91.91%</f>
+        <v>92006.101095999984</v>
+      </c>
+      <c r="F110" s="134">
+        <f>D110*8.09%</f>
+        <v>8098.4589040000001</v>
+      </c>
+      <c r="H110" s="150"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="94" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="122"/>
-      <c r="D104" s="113">
+      <c r="B111" s="7"/>
+      <c r="C111" s="122"/>
+      <c r="D111" s="113">
         <v>44400</v>
       </c>
-      <c r="E104" s="149">
-        <f>D104*91.91%</f>
+      <c r="E111" s="149">
+        <f>D111*91.91%</f>
         <v>40808.039999999994</v>
       </c>
-      <c r="F104" s="134">
-        <f>D104*8.09%</f>
+      <c r="F111" s="134">
+        <f>D111*8.09%</f>
         <v>3591.96</v>
       </c>
-      <c r="H104" s="150"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="95" t="s">
+      <c r="H111" s="150"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="B105" s="95"/>
-      <c r="C105" s="95"/>
-      <c r="D105" s="158">
-        <f>SUM(D103:D104)</f>
+      <c r="B112" s="95"/>
+      <c r="C112" s="95"/>
+      <c r="D112" s="158">
+        <f>SUM(D110:D111)</f>
         <v>144504.56</v>
       </c>
-      <c r="E105" s="147">
-        <f t="shared" ref="E105:F105" si="26">SUM(E103:E104)</f>
+      <c r="E112" s="147">
+        <f t="shared" ref="E112:F112" si="26">SUM(E110:E111)</f>
         <v>132814.14109599998</v>
       </c>
-      <c r="F105" s="147">
+      <c r="F112" s="147">
         <f t="shared" si="26"/>
         <v>11690.418904</v>
       </c>
-      <c r="G105" s="109">
-        <f>E105+F105</f>
+      <c r="G112" s="109">
+        <f>E112+F112</f>
         <v>144504.55999999997</v>
       </c>
-      <c r="H105" s="150" t="str">
-        <f>IF(D105=G105, "", "Error")</f>
+      <c r="H112" s="150" t="str">
+        <f>IF(D112=G112, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="186"/>
-      <c r="E106" s="12"/>
-      <c r="F106" s="7"/>
-      <c r="H106" s="150"/>
-    </row>
-    <row r="107" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="99" t="s">
+    <row r="113" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="186"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="7"/>
+      <c r="H113" s="150"/>
+    </row>
+    <row r="114" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="99"/>
-      <c r="C107" s="99"/>
-      <c r="D107" s="187"/>
-      <c r="E107" s="118">
-        <f>D107*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F107" s="136">
-        <f>D107*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G107" s="109">
-        <f>E107+F107</f>
-        <v>0</v>
-      </c>
-      <c r="H107" s="150" t="str">
-        <f>IF(D107=G107, "", "Error")</f>
+      <c r="B114" s="99"/>
+      <c r="C114" s="99"/>
+      <c r="D114" s="187"/>
+      <c r="E114" s="118">
+        <f>D114*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F114" s="136">
+        <f>D114*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G114" s="109">
+        <f>E114+F114</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="150" t="str">
+        <f>IF(D114=G114, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1"/>
-      <c r="D108" s="184"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="157"/>
-      <c r="H108" s="150"/>
-    </row>
-    <row r="109" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="4" t="s">
+    <row r="115" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1"/>
+      <c r="D115" s="184"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="10"/>
+      <c r="G115" s="157"/>
+      <c r="H115" s="150"/>
+    </row>
+    <row r="116" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="60"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="188">
-        <f>SUM(D107+D105+D101+D94+D88+D55+D35+D30+D48)</f>
-        <v>7496328.3699999992</v>
-      </c>
-      <c r="E109" s="148">
-        <f>SUM(E107+E105+E101+E94+E88+E55+E35+E30+E48)</f>
-        <v>7082805.3203670001</v>
-      </c>
-      <c r="F109" s="148">
-        <f>SUM(F107+F105+F101+F94+F88+F55+F35+F30+F48)</f>
-        <v>413523.04963299993</v>
-      </c>
-      <c r="G109" s="109">
-        <f>E109+F109</f>
-        <v>7496328.3700000001</v>
-      </c>
-      <c r="H109" s="150" t="str">
-        <f>IF(D109=G109, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I109" s="178">
-        <f>D109-G109</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D110" s="184"/>
-      <c r="E110" s="109"/>
-    </row>
-    <row r="111" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="142" t="s">
+      <c r="B116" s="60"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="188">
+        <f>SUM(D114+D112+D108+D101+D95+D55+D35+D30+D48)</f>
+        <v>10659184.91</v>
+      </c>
+      <c r="E116" s="148">
+        <f>SUM(E114+E112+E108+E101+E95+E55+E35+E30+E48)</f>
+        <v>10095751.311878001</v>
+      </c>
+      <c r="F116" s="148">
+        <f>SUM(F114+F112+F108+F101+F95+F55+F35+F30+F48)</f>
+        <v>577995.59812199988</v>
+      </c>
+      <c r="G116" s="109">
+        <f>E116+F116</f>
+        <v>10673746.910000002</v>
+      </c>
+      <c r="H116" s="150" t="str">
+        <f>IF(D116=G116, "", "Error")</f>
+        <v>Error</v>
+      </c>
+      <c r="I116" s="178">
+        <f>D116-G116</f>
+        <v>-14562.000000001863</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D117" s="184"/>
+      <c r="E117" s="109"/>
+    </row>
+    <row r="118" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="B111" s="141"/>
-      <c r="C111" s="141"/>
-      <c r="E111" s="109"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
-      <c r="C112" s="139"/>
-      <c r="E112" s="109"/>
-    </row>
-    <row r="113" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="1"/>
-      <c r="C113" s="139"/>
-      <c r="E113" s="109"/>
-    </row>
-    <row r="114" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="143" t="s">
+      <c r="B118" s="141"/>
+      <c r="C118" s="141"/>
+      <c r="E118" s="109"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
+      <c r="C119" s="139"/>
+      <c r="E119" s="109"/>
+    </row>
+    <row r="120" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1"/>
+      <c r="C120" s="139"/>
+      <c r="E120" s="109"/>
+    </row>
+    <row r="121" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="B114" s="144"/>
-      <c r="C114" s="140">
-        <f>SUM(C112:C113)</f>
-        <v>0</v>
-      </c>
-      <c r="E114" s="109"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E115" s="109"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E116" s="137"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="223" t="s">
+      <c r="B121" s="144"/>
+      <c r="C121" s="140">
+        <f>SUM(C119:C120)</f>
+        <v>0</v>
+      </c>
+      <c r="E121" s="109"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E122" s="109"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E123" s="137"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="228" t="s">
         <v>114</v>
       </c>
-      <c r="B117" s="224"/>
-      <c r="C117" s="224"/>
-      <c r="D117" s="224"/>
-      <c r="E117" s="171" t="s">
+      <c r="B124" s="229"/>
+      <c r="C124" s="229"/>
+      <c r="D124" s="229"/>
+      <c r="E124" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="F117" s="172" t="s">
+      <c r="F124" s="172" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="220"/>
-      <c r="B118" s="221"/>
-      <c r="C118" s="222"/>
-      <c r="D118" s="166"/>
-      <c r="E118" s="149"/>
-      <c r="F118" s="134"/>
-    </row>
-    <row r="119" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="217" t="s">
-        <v>160</v>
-      </c>
-      <c r="B119" s="218"/>
-      <c r="C119" s="173"/>
-      <c r="D119" s="113">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="225"/>
+      <c r="B125" s="226"/>
+      <c r="C125" s="227"/>
+      <c r="D125" s="166"/>
+      <c r="E125" s="149"/>
+      <c r="F125" s="134"/>
+    </row>
+    <row r="126" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="222" t="s">
+        <v>152</v>
+      </c>
+      <c r="B126" s="223"/>
+      <c r="C126" s="173"/>
+      <c r="D126" s="113">
         <v>300000</v>
       </c>
-      <c r="E119" s="149">
-        <f t="shared" ref="E119:E120" si="27">D119*91.91%</f>
+      <c r="E126" s="149">
+        <f t="shared" ref="E126:E127" si="27">D126*91.91%</f>
         <v>275730</v>
       </c>
-      <c r="F119" s="134">
-        <f t="shared" ref="F119:F120" si="28">D119*8.09%</f>
+      <c r="F126" s="134">
+        <f t="shared" ref="F126:F127" si="28">D126*8.09%</f>
         <v>24270</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="217" t="s">
-        <v>153</v>
-      </c>
-      <c r="B120" s="218"/>
-      <c r="C120" s="173"/>
-      <c r="D120" s="113">
+    <row r="127" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="222" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127" s="223"/>
+      <c r="C127" s="173"/>
+      <c r="D127" s="113">
         <v>10391.24</v>
       </c>
-      <c r="E120" s="149">
+      <c r="E127" s="149">
         <f t="shared" si="27"/>
         <v>9550.5886839999985</v>
       </c>
-      <c r="F120" s="134">
+      <c r="F127" s="134">
         <f t="shared" si="28"/>
         <v>840.65131599999995</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="217"/>
-      <c r="B121" s="218"/>
-      <c r="C121" s="219"/>
-      <c r="D121" s="113"/>
-      <c r="E121" s="149">
-        <f>D121*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F121" s="134">
-        <f>D121*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="211" t="s">
+    <row r="128" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="222"/>
+      <c r="B128" s="223"/>
+      <c r="C128" s="224"/>
+      <c r="D128" s="113"/>
+      <c r="E128" s="149">
+        <f>D128*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F128" s="134">
+        <f>D128*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="216" t="s">
         <v>30</v>
       </c>
-      <c r="B122" s="212"/>
-      <c r="C122" s="213"/>
-      <c r="D122" s="170">
-        <f>SUM(D118:D121)</f>
+      <c r="B129" s="217"/>
+      <c r="C129" s="218"/>
+      <c r="D129" s="170">
+        <f>SUM(D125:D128)</f>
         <v>310391.24</v>
       </c>
-      <c r="E122" s="170">
-        <f>SUM(E118:E121)</f>
+      <c r="E129" s="170">
+        <f>SUM(E125:E128)</f>
         <v>285280.58868400002</v>
       </c>
-      <c r="F122" s="170">
-        <f>SUM(F118:F121)</f>
+      <c r="F129" s="170">
+        <f>SUM(F125:F128)</f>
         <v>25110.651315999999</v>
       </c>
-      <c r="H122" s="109">
-        <f>E122+F122</f>
+      <c r="H129" s="109">
+        <f>E129+F129</f>
         <v>310391.24</v>
       </c>
-      <c r="I122" s="150" t="str">
-        <f>IF(D122=H122, "", "Error")</f>
+      <c r="I129" s="150" t="str">
+        <f>IF(D129=H129, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E124" s="109"/>
-    </row>
-    <row r="125" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="102" t="s">
+    <row r="131" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E131" s="109"/>
+    </row>
+    <row r="132" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="B125" s="103">
-        <f>D109</f>
-        <v>7496328.3699999992</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="104" t="s">
+      <c r="B132" s="103">
+        <f>D116</f>
+        <v>10659184.91</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="B126" s="105">
-        <f>D109-D107</f>
-        <v>7496328.3699999992</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D127" s="235"/>
-      <c r="E127" s="235"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="74" t="s">
+      <c r="B133" s="105">
+        <f>D116-D114</f>
+        <v>10659184.91</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D134" s="206"/>
+      <c r="E134" s="206"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="B128" s="75"/>
-      <c r="C128" s="76"/>
-      <c r="D128" s="235"/>
-      <c r="E128" s="235"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="77" t="s">
+      <c r="B135" s="75"/>
+      <c r="C135" s="76"/>
+      <c r="D135" s="206"/>
+      <c r="E135" s="206"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="B129" s="78">
+      <c r="B136" s="78">
         <v>6056324.5665496523</v>
       </c>
-      <c r="C129" s="78"/>
-      <c r="D129" s="235"/>
-      <c r="E129" s="235"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="79" t="s">
+      <c r="C136" s="78"/>
+      <c r="D136" s="206"/>
+      <c r="E136" s="206"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="B130" s="92">
+      <c r="B137" s="92">
         <f>PRORRATEO!G52</f>
         <v>6320855.3670509998</v>
       </c>
-      <c r="C130" s="78" t="s">
+      <c r="C137" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="D130" s="235"/>
-      <c r="E130" s="235"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="79" t="s">
+      <c r="D137" s="206"/>
+      <c r="E137" s="206"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="B131" s="175">
-        <f>-B126</f>
-        <v>-7496328.3699999992</v>
-      </c>
-      <c r="C131" s="76"/>
-      <c r="D131" s="235"/>
-      <c r="E131" s="235"/>
-      <c r="G131" s="113"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="79" t="s">
+      <c r="B138" s="175">
+        <f>-B133</f>
+        <v>-10659184.91</v>
+      </c>
+      <c r="C138" s="76"/>
+      <c r="D138" s="206"/>
+      <c r="E138" s="206"/>
+      <c r="G138" s="113"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="B132" s="175">
-        <f>-D122</f>
+      <c r="B139" s="175">
+        <f>-D129</f>
         <v>-310391.24</v>
       </c>
-      <c r="C132" s="76"/>
-      <c r="D132" s="235"/>
-      <c r="E132" s="235"/>
-      <c r="G132" s="125"/>
-    </row>
-    <row r="133" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="201" t="s">
-        <v>168</v>
-      </c>
-      <c r="B133" s="175">
+      <c r="C139" s="76"/>
+      <c r="D139" s="206"/>
+      <c r="E139" s="206"/>
+      <c r="G139" s="125"/>
+    </row>
+    <row r="140" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="201" t="s">
+        <v>158</v>
+      </c>
+      <c r="B140" s="175">
         <v>-338000</v>
       </c>
-      <c r="C133" s="76"/>
-      <c r="D133" s="198"/>
-      <c r="E133" s="198"/>
-      <c r="G133" s="125"/>
-    </row>
-    <row r="134" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="200" t="s">
-        <v>175</v>
-      </c>
-      <c r="B134" s="175">
+      <c r="C140" s="76"/>
+      <c r="D140" s="198"/>
+      <c r="E140" s="198"/>
+      <c r="G140" s="125"/>
+    </row>
+    <row r="141" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="200" t="s">
+        <v>165</v>
+      </c>
+      <c r="B141" s="175">
         <v>-308000</v>
       </c>
-      <c r="C134" s="76"/>
-      <c r="D134" s="198"/>
-      <c r="E134" s="198"/>
-      <c r="G134" s="125"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="79" t="s">
+      <c r="C141" s="76"/>
+      <c r="D141" s="198"/>
+      <c r="E141" s="198"/>
+      <c r="G141" s="125"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="B135" s="175">
-        <f>-B142</f>
-        <v>0</v>
-      </c>
-      <c r="C135" s="80"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="79" t="s">
+      <c r="B142" s="175">
+        <f>-B149</f>
+        <v>0</v>
+      </c>
+      <c r="C142" s="80"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="93">
-        <f>-C114</f>
-        <v>0</v>
-      </c>
-      <c r="C136" s="80"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="79"/>
-      <c r="B137" s="75"/>
-      <c r="C137" s="80"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="77" t="s">
+      <c r="B143" s="93">
+        <f>-C121</f>
+        <v>0</v>
+      </c>
+      <c r="C143" s="80"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="79"/>
+      <c r="B144" s="75"/>
+      <c r="C144" s="80"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="B138" s="81">
-        <f>SUM(B129:B137)</f>
-        <v>3924460.3236006536</v>
-      </c>
-      <c r="C138" s="154"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" s="80"/>
-      <c r="C139" s="76"/>
-      <c r="D139" s="83"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C140" s="76"/>
-      <c r="D140" s="109"/>
-      <c r="E140" s="178"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="74" t="s">
+      <c r="B145" s="81">
+        <f>SUM(B136:B144)</f>
+        <v>761603.78360065282</v>
+      </c>
+      <c r="C145" s="154"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146" s="80"/>
+      <c r="C146" s="76"/>
+      <c r="D146" s="83"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C147" s="76"/>
+      <c r="D147" s="109"/>
+      <c r="E147" s="178"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B148" s="11">
         <v>-310694.54000000004</v>
       </c>
-      <c r="C141" s="82"/>
-      <c r="D141" s="178"/>
-      <c r="E141" s="178"/>
-      <c r="F141" s="178"/>
-    </row>
-    <row r="142" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="77" t="s">
-        <v>176</v>
-      </c>
-      <c r="B142" s="93"/>
-      <c r="C142" s="82"/>
-      <c r="D142" s="178"/>
-      <c r="E142" s="199"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="77"/>
-      <c r="B143" s="175"/>
-      <c r="C143" s="82"/>
-      <c r="E143" s="109"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="77" t="s">
-        <v>163</v>
-      </c>
-      <c r="B144" s="175">
+      <c r="C148" s="82"/>
+      <c r="D148" s="178"/>
+      <c r="E148" s="178"/>
+      <c r="F148" s="178"/>
+    </row>
+    <row r="149" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="77" t="s">
+        <v>166</v>
+      </c>
+      <c r="B149" s="93"/>
+      <c r="C149" s="82"/>
+      <c r="D149" s="178"/>
+      <c r="E149" s="199"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150" s="77"/>
+      <c r="B150" s="175"/>
+      <c r="C150" s="82"/>
+      <c r="E150" s="109"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="B151" s="175">
         <v>-55000</v>
       </c>
-      <c r="C144" s="82"/>
-      <c r="E144" s="109"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A145" s="100" t="s">
+      <c r="C151" s="82"/>
+      <c r="E151" s="109"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B145" s="101">
-        <f>SUM(B141:B144)</f>
+      <c r="B152" s="101">
+        <f>SUM(B148:B151)</f>
         <v>-365694.54000000004</v>
       </c>
-      <c r="C145" s="82"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C146" s="83"/>
-      <c r="D146" s="178"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B147" s="80"/>
-      <c r="C147" s="76"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N149" s="12"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B152" s="234" t="s">
-        <v>174</v>
-      </c>
-      <c r="C152" s="234"/>
-      <c r="D152" s="234"/>
-      <c r="E152" s="234"/>
+      <c r="C152" s="82"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B153" s="234"/>
-      <c r="C153" s="234"/>
-      <c r="D153" s="234"/>
-      <c r="E153" s="234"/>
+      <c r="C153" s="83"/>
+      <c r="D153" s="178"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B154" s="234"/>
-      <c r="C154" s="234"/>
-      <c r="D154" s="234"/>
-      <c r="E154" s="234"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B155" s="234"/>
-      <c r="C155" s="234"/>
-      <c r="D155" s="234"/>
-      <c r="E155" s="234"/>
+      <c r="B154" s="80"/>
+      <c r="C154" s="76"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B156" s="234"/>
-      <c r="C156" s="234"/>
-      <c r="D156" s="234"/>
-      <c r="E156" s="234"/>
+      <c r="N156" s="12"/>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B159" s="205" t="s">
+        <v>164</v>
+      </c>
+      <c r="C159" s="205"/>
+      <c r="D159" s="205"/>
+      <c r="E159" s="205"/>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B160" s="205"/>
+      <c r="C160" s="205"/>
+      <c r="D160" s="205"/>
+      <c r="E160" s="205"/>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B161" s="205"/>
+      <c r="C161" s="205"/>
+      <c r="D161" s="205"/>
+      <c r="E161" s="205"/>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B162" s="205"/>
+      <c r="C162" s="205"/>
+      <c r="D162" s="205"/>
+      <c r="E162" s="205"/>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B163" s="205"/>
+      <c r="C163" s="205"/>
+      <c r="D163" s="205"/>
+      <c r="E163" s="205"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B152:E156"/>
-    <mergeCell ref="D127:E132"/>
+  <mergeCells count="20">
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="B159:E163"/>
+    <mergeCell ref="D134:E139"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A69:C69"/>
     <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A71:C71"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4632,15 +4861,15 @@
       <c r="K1" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="243">
-        <f>RESUMEN!D109</f>
-        <v>7496328.3699999992</v>
-      </c>
-      <c r="M1" s="244"/>
+      <c r="L1" s="239">
+        <f>RESUMEN!D116</f>
+        <v>10659184.91</v>
+      </c>
+      <c r="M1" s="240"/>
       <c r="N1" s="152"/>
       <c r="O1" s="135">
         <f>L1*8.09%</f>
-        <v>606452.96513299993</v>
+        <v>862328.05921900005</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -4665,7 +4894,7 @@
       <c r="N2" s="153"/>
       <c r="O2" s="135">
         <f>O1-K7-553-50-86-8</f>
-        <v>207324.22721099993</v>
+        <v>463199.32129700005</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -4687,7 +4916,7 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="128">
-        <f>RESUMEN!D122</f>
+        <f>RESUMEN!D129</f>
         <v>310391.24</v>
       </c>
       <c r="N3" s="151"/>
@@ -4721,13 +4950,13 @@
       <c r="A5" s="236" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="238" t="s">
+      <c r="B5" s="250" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="236" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="240" t="s">
+      <c r="D5" s="248" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="236" t="s">
@@ -4739,43 +4968,43 @@
       <c r="G5" s="236" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="247" t="s">
+      <c r="H5" s="243" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="240" t="s">
+      <c r="I5" s="248" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="245" t="s">
+      <c r="J5" s="241" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="245" t="s">
+      <c r="K5" s="241" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="250" t="s">
+      <c r="L5" s="246" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="245" t="s">
+      <c r="M5" s="241" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="245" t="s">
+      <c r="N5" s="241" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="237"/>
-      <c r="B6" s="239"/>
+      <c r="B6" s="251"/>
       <c r="C6" s="237"/>
-      <c r="D6" s="241"/>
+      <c r="D6" s="252"/>
       <c r="E6" s="237"/>
       <c r="F6" s="237"/>
       <c r="G6" s="237"/>
-      <c r="H6" s="248"/>
-      <c r="I6" s="252"/>
-      <c r="J6" s="246"/>
-      <c r="K6" s="249"/>
-      <c r="L6" s="251"/>
-      <c r="M6" s="249"/>
-      <c r="N6" s="246"/>
+      <c r="H6" s="244"/>
+      <c r="I6" s="249"/>
+      <c r="J6" s="242"/>
+      <c r="K6" s="245"/>
+      <c r="L6" s="247"/>
+      <c r="M6" s="245"/>
+      <c r="N6" s="242"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4889,7 +5118,7 @@
         <v>222096.62408426331</v>
       </c>
       <c r="G9" s="192">
-        <f>250969-G34+RESUMEN!D65</f>
+        <f>250969-G34+RESUMEN!D66</f>
         <v>333122.69579999999</v>
       </c>
       <c r="H9" s="131">
@@ -5574,7 +5803,7 @@
         <v>385103.52163409517</v>
       </c>
       <c r="G23" s="192">
-        <f>447000-G46+RESUMEN!D70+RESUMEN!D71</f>
+        <f>447000-G46+RESUMEN!D71+RESUMEN!D72</f>
         <v>582942.08675000002</v>
       </c>
       <c r="H23" s="131">
@@ -5818,7 +6047,7 @@
         <v>314286.41577654087</v>
       </c>
       <c r="G28" s="191">
-        <f>371000-G32-G33+RESUMEN!D73</f>
+        <f>371000-G32-G33+RESUMEN!D74</f>
         <v>413583.78619999997</v>
       </c>
       <c r="H28" s="131">
@@ -5867,7 +6096,7 @@
         <v>325490.37115669996</v>
       </c>
       <c r="G29" s="192">
-        <f>401000-G42-G43-G44+RESUMEN!D72</f>
+        <f>401000-G42-G43-G44+RESUMEN!D73</f>
         <v>413311.71970000002</v>
       </c>
       <c r="H29" s="132">
@@ -6557,7 +6786,7 @@
       </c>
       <c r="P43" s="109">
         <f>L1-K52</f>
-        <v>1105640.362077998</v>
+        <v>4268496.902077999</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -6989,36 +7218,36 @@
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="138">
         <f>K52-L1</f>
-        <v>-1105640.362077998</v>
+        <v>-4268496.902077999</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="242"/>
-      <c r="D54" s="242"/>
-      <c r="E54" s="242"/>
-      <c r="F54" s="242"/>
-      <c r="G54" s="242"/>
-      <c r="H54" s="242"/>
-      <c r="I54" s="242"/>
-      <c r="J54" s="242"/>
-      <c r="K54" s="242"/>
-      <c r="L54" s="242"/>
-      <c r="M54" s="242"/>
-      <c r="N54" s="242"/>
+      <c r="C54" s="238"/>
+      <c r="D54" s="238"/>
+      <c r="E54" s="238"/>
+      <c r="F54" s="238"/>
+      <c r="G54" s="238"/>
+      <c r="H54" s="238"/>
+      <c r="I54" s="238"/>
+      <c r="J54" s="238"/>
+      <c r="K54" s="238"/>
+      <c r="L54" s="238"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="238"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="242"/>
-      <c r="D55" s="242"/>
-      <c r="E55" s="242"/>
-      <c r="F55" s="242"/>
-      <c r="G55" s="242"/>
-      <c r="H55" s="242"/>
-      <c r="I55" s="242"/>
-      <c r="J55" s="242"/>
-      <c r="K55" s="242"/>
-      <c r="L55" s="242"/>
-      <c r="M55" s="242"/>
-      <c r="N55" s="242"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
+      <c r="I55" s="238"/>
+      <c r="J55" s="238"/>
+      <c r="K55" s="238"/>
+      <c r="L55" s="238"/>
+      <c r="M55" s="238"/>
+      <c r="N55" s="238"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="168"/>
@@ -7035,107 +7264,112 @@
       <c r="N56" s="168"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="242" t="s">
+      <c r="C57" s="238" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="242"/>
-      <c r="E57" s="242"/>
-      <c r="F57" s="242"/>
-      <c r="G57" s="242"/>
-      <c r="H57" s="242"/>
-      <c r="I57" s="242"/>
-      <c r="J57" s="242"/>
-      <c r="K57" s="242"/>
-      <c r="L57" s="242"/>
-      <c r="M57" s="242"/>
-      <c r="N57" s="242"/>
+      <c r="D57" s="238"/>
+      <c r="E57" s="238"/>
+      <c r="F57" s="238"/>
+      <c r="G57" s="238"/>
+      <c r="H57" s="238"/>
+      <c r="I57" s="238"/>
+      <c r="J57" s="238"/>
+      <c r="K57" s="238"/>
+      <c r="L57" s="238"/>
+      <c r="M57" s="238"/>
+      <c r="N57" s="238"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="242"/>
-      <c r="D58" s="242"/>
-      <c r="E58" s="242"/>
-      <c r="F58" s="242"/>
-      <c r="G58" s="242"/>
-      <c r="H58" s="242"/>
-      <c r="I58" s="242"/>
-      <c r="J58" s="242"/>
-      <c r="K58" s="242"/>
-      <c r="L58" s="242"/>
-      <c r="M58" s="242"/>
-      <c r="N58" s="242"/>
+      <c r="C58" s="238"/>
+      <c r="D58" s="238"/>
+      <c r="E58" s="238"/>
+      <c r="F58" s="238"/>
+      <c r="G58" s="238"/>
+      <c r="H58" s="238"/>
+      <c r="I58" s="238"/>
+      <c r="J58" s="238"/>
+      <c r="K58" s="238"/>
+      <c r="L58" s="238"/>
+      <c r="M58" s="238"/>
+      <c r="N58" s="238"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="242"/>
-      <c r="D59" s="242"/>
-      <c r="E59" s="242"/>
-      <c r="F59" s="242"/>
-      <c r="G59" s="242"/>
-      <c r="H59" s="242"/>
-      <c r="I59" s="242"/>
-      <c r="J59" s="242"/>
-      <c r="K59" s="242"/>
-      <c r="L59" s="242"/>
-      <c r="M59" s="242"/>
-      <c r="N59" s="242"/>
+      <c r="C59" s="238"/>
+      <c r="D59" s="238"/>
+      <c r="E59" s="238"/>
+      <c r="F59" s="238"/>
+      <c r="G59" s="238"/>
+      <c r="H59" s="238"/>
+      <c r="I59" s="238"/>
+      <c r="J59" s="238"/>
+      <c r="K59" s="238"/>
+      <c r="L59" s="238"/>
+      <c r="M59" s="238"/>
+      <c r="N59" s="238"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="242"/>
-      <c r="D60" s="242"/>
-      <c r="E60" s="242"/>
-      <c r="F60" s="242"/>
-      <c r="G60" s="242"/>
-      <c r="H60" s="242"/>
-      <c r="I60" s="242"/>
-      <c r="J60" s="242"/>
-      <c r="K60" s="242"/>
-      <c r="L60" s="242"/>
-      <c r="M60" s="242"/>
-      <c r="N60" s="242"/>
+      <c r="C60" s="238"/>
+      <c r="D60" s="238"/>
+      <c r="E60" s="238"/>
+      <c r="F60" s="238"/>
+      <c r="G60" s="238"/>
+      <c r="H60" s="238"/>
+      <c r="I60" s="238"/>
+      <c r="J60" s="238"/>
+      <c r="K60" s="238"/>
+      <c r="L60" s="238"/>
+      <c r="M60" s="238"/>
+      <c r="N60" s="238"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="242"/>
-      <c r="D61" s="242"/>
-      <c r="E61" s="242"/>
-      <c r="F61" s="242"/>
-      <c r="G61" s="242"/>
-      <c r="H61" s="242"/>
-      <c r="I61" s="242"/>
-      <c r="J61" s="242"/>
-      <c r="K61" s="242"/>
-      <c r="L61" s="242"/>
-      <c r="M61" s="242"/>
-      <c r="N61" s="242"/>
+      <c r="C61" s="238"/>
+      <c r="D61" s="238"/>
+      <c r="E61" s="238"/>
+      <c r="F61" s="238"/>
+      <c r="G61" s="238"/>
+      <c r="H61" s="238"/>
+      <c r="I61" s="238"/>
+      <c r="J61" s="238"/>
+      <c r="K61" s="238"/>
+      <c r="L61" s="238"/>
+      <c r="M61" s="238"/>
+      <c r="N61" s="238"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="242"/>
-      <c r="D62" s="242"/>
-      <c r="E62" s="242"/>
-      <c r="F62" s="242"/>
-      <c r="G62" s="242"/>
-      <c r="H62" s="242"/>
-      <c r="I62" s="242"/>
-      <c r="J62" s="242"/>
-      <c r="K62" s="242"/>
-      <c r="L62" s="242"/>
-      <c r="M62" s="242"/>
-      <c r="N62" s="242"/>
+      <c r="C62" s="238"/>
+      <c r="D62" s="238"/>
+      <c r="E62" s="238"/>
+      <c r="F62" s="238"/>
+      <c r="G62" s="238"/>
+      <c r="H62" s="238"/>
+      <c r="I62" s="238"/>
+      <c r="J62" s="238"/>
+      <c r="K62" s="238"/>
+      <c r="L62" s="238"/>
+      <c r="M62" s="238"/>
+      <c r="N62" s="238"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="242"/>
-      <c r="D63" s="242"/>
-      <c r="E63" s="242"/>
-      <c r="F63" s="242"/>
-      <c r="G63" s="242"/>
-      <c r="H63" s="242"/>
-      <c r="I63" s="242"/>
-      <c r="J63" s="242"/>
-      <c r="K63" s="242"/>
-      <c r="L63" s="242"/>
-      <c r="M63" s="242"/>
-      <c r="N63" s="242"/>
+      <c r="C63" s="238"/>
+      <c r="D63" s="238"/>
+      <c r="E63" s="238"/>
+      <c r="F63" s="238"/>
+      <c r="G63" s="238"/>
+      <c r="H63" s="238"/>
+      <c r="I63" s="238"/>
+      <c r="J63" s="238"/>
+      <c r="K63" s="238"/>
+      <c r="L63" s="238"/>
+      <c r="M63" s="238"/>
+      <c r="N63" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
@@ -7148,11 +7382,6 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/BELGRANO 1646/Junio/JUNIO-BLG1646.xlsx
+++ b/BELGRANO 1646/Junio/JUNIO-BLG1646.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELGRANO 1646\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6A0776-1A04-42B9-9330-1A2465DB1E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D5E060-6210-4FDC-ACA7-60822D04DDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$153</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$140</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="181">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -474,102 +474,30 @@
     <t>ARCA</t>
   </si>
   <si>
-    <t xml:space="preserve">Contessi - Mantenimiento de ascensores </t>
-  </si>
-  <si>
     <t>FEUILLANT, GASTON</t>
   </si>
   <si>
-    <t>Contessi provision y colocacion de 60 lts de aceite hidraulico en la sede del monta auto</t>
-  </si>
-  <si>
-    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 05/05</t>
-  </si>
-  <si>
-    <t>Debito 12/05</t>
-  </si>
-  <si>
-    <t>Pago mis cuentas 12/05</t>
-  </si>
-  <si>
-    <t>Camaras del sur 19/05 - compra y colocacion camaras de entradas (pileta y gimnasio)</t>
-  </si>
-  <si>
-    <t>Numero 1859135 Debito automatico 5/05</t>
-  </si>
-  <si>
-    <t>Salvatierra limpieza de columna de baño desde piso 3 (inclusive) hasta el piso 10 (inclusive) - 20/05</t>
-  </si>
-  <si>
-    <t>Kromacolor  -  Compra de materiales : Sellador Sika 23/05</t>
-  </si>
-  <si>
-    <t>Compra Fabio Tolosa - Combustible 19/05</t>
-  </si>
-  <si>
-    <t>Compra Alejandro Davin - Combustible 17/05</t>
-  </si>
-  <si>
-    <t>Combustible comprado por el Sr Lucas - remisero 24/05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas - viajes entregas de combustible </t>
-  </si>
-  <si>
-    <t>Remis Sr. Diego - Dias de paro</t>
-  </si>
-  <si>
-    <t>Silletero - Sr Oscar Colmeiro - Sellado de grieta medianera piso 11 26/05</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Combustible comprado por el Sr Ruso - remisero 23/05</t>
-  </si>
-  <si>
-    <t>Reparacion puerta SUM 02/05</t>
-  </si>
-  <si>
-    <t>Compra de Juan Manuel Villa - Combustible 23/05</t>
-  </si>
-  <si>
-    <t>Debito 27/05</t>
-  </si>
-  <si>
-    <t>ADS - Imputado en el mes de Marzo y transferido finalizada las charlas por la desvinculacion</t>
-  </si>
-  <si>
     <t>VTO: 14/07</t>
   </si>
   <si>
     <t>PERÍODO: JUNIO</t>
   </si>
   <si>
-    <t>Honorarios JUNIO</t>
-  </si>
-  <si>
     <t>Energoup MES DE JUNIO</t>
   </si>
   <si>
     <t xml:space="preserve">Mes de JUNIO </t>
   </si>
   <si>
-    <t>EN TEORIA EN ESTE PUNTO (JUNIO DEL 2025) LA CAJA NO NOS DA BIEN, TENEMOS 173MIL PESOS DE DIFERENCIA</t>
-  </si>
-  <si>
-    <t>Contessi - Imputado en el mes de MAYO y transferido una vez en la municipalidad se asento el contrato</t>
-  </si>
-  <si>
     <t>Ingreso mes de MAYO</t>
   </si>
   <si>
     <t xml:space="preserve">Kromacolor </t>
   </si>
   <si>
-    <t>Contessi</t>
-  </si>
-  <si>
     <t>Servisur - cambio de luminarias 18/06</t>
   </si>
   <si>
@@ -582,9 +510,6 @@
     <t>Zaffalon Veronica - Por vaciamiento de monta coches con agua y mucho residuo de aceite, extraido con bomba y balde por la pesadez de lo econtrado</t>
   </si>
   <si>
-    <t xml:space="preserve">Servisur </t>
-  </si>
-  <si>
     <t>Eba - Elcetrica de buenos aires</t>
   </si>
   <si>
@@ -594,7 +519,91 @@
     <t>Ferreteria Arcamone - Yeso de 5 kilos</t>
   </si>
   <si>
-    <t>Presupuesto 18/06</t>
+    <t>Honorarios JUNIO y SAC</t>
+  </si>
+  <si>
+    <t>Numero 1859135 Debito automatico 02/06</t>
+  </si>
+  <si>
+    <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO 04/06</t>
+  </si>
+  <si>
+    <t>Fotocopias Poliza</t>
+  </si>
+  <si>
+    <t>Servisur - canaleta en la pared para pasar corrugado para elevar el toma corriente en altura - reemplazo de 13 plafones, etc</t>
+  </si>
+  <si>
+    <t>Debito 12/06</t>
+  </si>
+  <si>
+    <t>Pago mis cuentas 12/06</t>
+  </si>
+  <si>
+    <t>SA seguridad - 10/06 - Servicio tecnico realizado en sistema, se repara visibilidad de la camara y se cambia balun de conexión</t>
+  </si>
+  <si>
+    <t>Cerrajeria Walter - Cambio de baterias control de acceso</t>
+  </si>
+  <si>
+    <t>Contessi - Cuota 1 de arreglo montavehiculos</t>
+  </si>
+  <si>
+    <t>Contessi - Mantenimiento de ascensores</t>
+  </si>
+  <si>
+    <t>Contessi provision de llavin abrepuerta al encargado para emergencias</t>
+  </si>
+  <si>
+    <t>Reemplazo Sr. Diego -  Monica Gorosito</t>
+  </si>
+  <si>
+    <t>Seguro de vida Sra. Monica</t>
+  </si>
+  <si>
+    <t>Doartero - Mano de obra de materiales colocacion para ventanales de pileta</t>
+  </si>
+  <si>
+    <t>Guido Alterini : diferencia colocacion cesped</t>
+  </si>
+  <si>
+    <t>Servisur - Instalacion electrica para aire acondicionado del SUM</t>
+  </si>
+  <si>
+    <t>Combustible comprado por el Sr Fabio Tolosa 19/05</t>
+  </si>
+  <si>
+    <t>No llego la factura</t>
+  </si>
+  <si>
+    <t>Subidos en jun de 2025</t>
+  </si>
+  <si>
+    <t>Debito 27/06</t>
+  </si>
+  <si>
+    <t>Kromacolor - Compra de materiales para hall, gimnasio, membrana, recuplast para terraza, lija, etc</t>
+  </si>
+  <si>
+    <t>Kromacolor - Compra de materiales sistemal, aguarras</t>
+  </si>
+  <si>
+    <t>Kromacolor</t>
+  </si>
+  <si>
+    <t>Leonardo Balcalazza - Pintura gimnasio, pasillo + cielo raso y sellado de aberturas salida a zona de tender</t>
+  </si>
+  <si>
+    <t>Leonardo Balcalazza - Pintura SUM (se tapo el agujero del aire original con durlock y se pinto)</t>
+  </si>
+  <si>
+    <t>Leonardo Balcalazza - Pintura hall</t>
+  </si>
+  <si>
+    <t>QUEDARON PENDIENTES TRES PARA JULI</t>
+  </si>
+  <si>
+    <t>BALBOA, ARIEL</t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1331,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1604,42 +1613,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1784,13 +1768,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2156,7 +2134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N163"/>
+  <dimension ref="A1:P150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -2214,10 +2192,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="D5" s="71"/>
       <c r="E5" s="72"/>
@@ -2245,26 +2223,26 @@
     <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="207" t="s">
+      <c r="B14" s="200" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="208"/>
-      <c r="D14" s="209"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="202"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="210"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="212"/>
+      <c r="B15" s="203"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="205"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="210"/>
-      <c r="C16" s="211"/>
-      <c r="D16" s="212"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="205"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="213"/>
-      <c r="C17" s="214"/>
-      <c r="D17" s="215"/>
+      <c r="B17" s="206"/>
+      <c r="C17" s="207"/>
+      <c r="D17" s="208"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
@@ -2289,7 +2267,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="130"/>
@@ -2303,15 +2281,15 @@
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="182">
-        <v>1234864.1000000001</v>
+        <v>1869737.25</v>
       </c>
       <c r="E23" s="134">
         <f>D23*91.91%</f>
-        <v>1134963.5943100001</v>
+        <v>1718475.5064749999</v>
       </c>
       <c r="F23" s="134">
         <f>D23*8.09%</f>
-        <v>99900.505690000005</v>
+        <v>151261.743525</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2321,15 +2299,15 @@
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="182">
-        <v>-268582.93</v>
+        <v>-406667.86</v>
       </c>
       <c r="E24" s="134">
-        <f t="shared" ref="E24:E26" si="0">D24*91.91%</f>
-        <v>-246854.57096299998</v>
+        <f t="shared" ref="E24:E25" si="0">D24*91.91%</f>
+        <v>-373768.43012599996</v>
       </c>
       <c r="F24" s="134">
-        <f t="shared" ref="F24:F26" si="1">D24*8.09%</f>
-        <v>-21728.359036999998</v>
+        <f t="shared" ref="F24:F25" si="1">D24*8.09%</f>
+        <v>-32899.429874000001</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2339,2483 +2317,2226 @@
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="182">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="E25" s="134">
         <f t="shared" si="0"/>
-        <v>0.76285299999999989</v>
+        <v>0.5606509999999999</v>
       </c>
       <c r="F25" s="134">
         <f t="shared" si="1"/>
-        <v>6.7146999999999998E-2</v>
+        <v>4.9348999999999997E-2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="121" t="s">
-        <v>151</v>
-      </c>
+      <c r="A26" s="121"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="182">
-        <v>13000</v>
-      </c>
-      <c r="E26" s="134">
-        <f t="shared" si="0"/>
-        <v>11948.3</v>
-      </c>
-      <c r="F26" s="134">
-        <f t="shared" si="1"/>
-        <v>1051.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="121"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="182"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="D26" s="182"/>
+      <c r="E26" s="134"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="107">
+        <f>SUM(D23:D26)</f>
+        <v>1463070.0000000002</v>
+      </c>
+      <c r="E27" s="107">
+        <f>SUM(E23:E26)</f>
+        <v>1344707.6369999999</v>
+      </c>
+      <c r="F27" s="107">
+        <f>SUM(F23:F26)</f>
+        <v>118362.363</v>
+      </c>
+      <c r="G27" s="109">
+        <f>E27+F27</f>
+        <v>1463069.9999999998</v>
+      </c>
+      <c r="H27" s="150" t="str">
+        <f>IF(D27=G27, "", "Error")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="121"/>
+      <c r="A28" s="94" t="s">
+        <v>110</v>
+      </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="182"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="121"/>
+      <c r="D28" s="183">
+        <v>0</v>
+      </c>
+      <c r="E28" s="134">
+        <f>D28*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="134">
+        <f>D28*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="150"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="94"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="182"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="95" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="95"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="107">
-        <f>SUM(D23:D29)</f>
-        <v>979282.00000000012</v>
-      </c>
-      <c r="E30" s="107">
-        <f t="shared" ref="E30" si="2">SUM(E23:E29)</f>
-        <v>900058.08620000014</v>
-      </c>
-      <c r="F30" s="107">
-        <f>SUM(F23:F29)</f>
-        <v>79223.913799999995</v>
-      </c>
-      <c r="G30" s="109">
-        <f>E30+F30</f>
-        <v>979282.00000000012</v>
-      </c>
-      <c r="H30" s="150" t="str">
-        <f>IF(D30=G30, "", "Error")</f>
-        <v/>
-      </c>
+      <c r="D29" s="182">
+        <v>0</v>
+      </c>
+      <c r="E29" s="134">
+        <f>D29*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="134">
+        <f>D29*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="150"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="94"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="182"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="H30" s="150"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="94" t="s">
-        <v>110</v>
-      </c>
+      <c r="A31" s="94"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="183">
-        <v>0</v>
-      </c>
-      <c r="E31" s="134">
-        <f>D31*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="134">
-        <f>D31*8.09%</f>
-        <v>0</v>
-      </c>
+      <c r="D31" s="182"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
       <c r="H31" s="150"/>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="94"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="182">
-        <v>0</v>
-      </c>
-      <c r="E32" s="134">
-        <f>D32*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="134">
-        <f>D32*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="150"/>
+      <c r="A32" s="95" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="95"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="107">
+        <f>SUM(D28:D30)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="107">
+        <f t="shared" ref="E32:F32" si="2">SUM(E28:E30)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="107">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="109">
+        <f>E32+F32</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="150" t="str">
+        <f>IF(D32=G32, "", "Error")</f>
+        <v/>
+      </c>
     </row>
     <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="94"/>
+      <c r="A33" s="94" t="s">
+        <v>110</v>
+      </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="182"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="134">
+        <f>D33*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="134">
+        <f>D33*8.09%</f>
+        <v>0</v>
+      </c>
       <c r="H33" s="150"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="94"/>
+      <c r="A34" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="182"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="E34" s="134">
+        <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="134">
+        <f t="shared" ref="F34:F35" si="4">D34*8.09%</f>
+        <v>0</v>
+      </c>
       <c r="H34" s="150"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="95" t="s">
+      <c r="A35" s="94" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="182"/>
+      <c r="E35" s="134">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="134">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="150"/>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="95" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="107">
+        <f>SUM(D29:D35)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="107">
+        <f t="shared" ref="E36" si="5">SUM(E29:E35)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="119">
+        <f>E36*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="150"/>
+    </row>
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="129"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="182"/>
+      <c r="E37" s="120"/>
+      <c r="F37" s="120"/>
+      <c r="H37" s="150"/>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="129"/>
+      <c r="B38" s="98"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="182"/>
+      <c r="E38" s="120"/>
+      <c r="F38" s="120"/>
+      <c r="H38" s="150"/>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="98"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="111"/>
+      <c r="D39" s="182"/>
+      <c r="E39" s="120"/>
+      <c r="F39" s="120"/>
+      <c r="H39" s="150"/>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="95" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="95"/>
-      <c r="C35" s="95"/>
-      <c r="D35" s="107">
-        <f>SUM(D31:D33)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="107">
-        <f t="shared" ref="E35:F35" si="3">SUM(E31:E33)</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="107">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="109">
-        <f>E35+F35</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="150" t="str">
-        <f>IF(D35=G35, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="94" t="s">
-        <v>110</v>
-      </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="183"/>
-      <c r="E36" s="134">
-        <f>D36*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="134">
-        <f>D36*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="150"/>
-    </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="182"/>
-      <c r="E37" s="134">
-        <f t="shared" ref="E37:E38" si="4">D37*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="134">
-        <f t="shared" ref="F37:F38" si="5">D37*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="150"/>
-    </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="94" t="s">
-        <v>2</v>
-      </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="182"/>
-      <c r="E38" s="134">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="134">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="150"/>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="95" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" s="95"/>
-      <c r="C39" s="95"/>
-      <c r="D39" s="107">
-        <f>SUM(D32:D38)</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="107">
-        <f t="shared" ref="E39" si="6">SUM(E32:E38)</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="119">
-        <f>E39*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="150"/>
-    </row>
-    <row r="40" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="129"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="182"/>
-      <c r="E40" s="120"/>
-      <c r="F40" s="120"/>
+      <c r="B40" s="95"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="107"/>
+      <c r="E40" s="112">
+        <f>SUM(D37:D39)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="110">
+        <f>(D37)*8.09%</f>
+        <v>0</v>
+      </c>
       <c r="H40" s="150"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="129"/>
-      <c r="B41" s="98"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="182"/>
-      <c r="E41" s="120"/>
-      <c r="F41" s="120"/>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="94" t="s">
+        <v>165</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="113">
+        <v>3567.21</v>
+      </c>
+      <c r="E41" s="134">
+        <f>D41*91.91%</f>
+        <v>3278.6227109999995</v>
+      </c>
+      <c r="F41" s="134">
+        <f>D41*8.09%</f>
+        <v>288.587289</v>
+      </c>
       <c r="H41" s="150"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="98"/>
-      <c r="B42" s="98"/>
-      <c r="C42" s="111"/>
-      <c r="D42" s="182"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="120"/>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="94" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="113">
+        <v>37000</v>
+      </c>
+      <c r="E42" s="134">
+        <f>D42*91.91%</f>
+        <v>34006.699999999997</v>
+      </c>
+      <c r="F42" s="134">
+        <f>D42*8.09%</f>
+        <v>2993.3</v>
+      </c>
       <c r="H42" s="150"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="95" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" s="95"/>
-      <c r="C43" s="95"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="112">
-        <f>SUM(D40:D42)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="110">
-        <f>(D40)*8.09%</f>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="94"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="185"/>
+      <c r="E43" s="134">
+        <f>D43*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="134">
+        <f>D43*8.09%</f>
         <v>0</v>
       </c>
       <c r="H43" s="150"/>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="94"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="184"/>
-      <c r="E44" s="114"/>
-      <c r="F44" s="7"/>
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="95" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="95"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="107">
+        <f>SUM(D41:D43)</f>
+        <v>40567.21</v>
+      </c>
+      <c r="E44" s="159">
+        <f>SUM(E41:E43)</f>
+        <v>37285.322710999993</v>
+      </c>
+      <c r="F44" s="169">
+        <f>SUM(F41:F43)</f>
+        <v>3281.8872890000002</v>
+      </c>
+      <c r="G44" s="109">
+        <f>E44+F44</f>
+        <v>40567.209999999992</v>
+      </c>
       <c r="H44" s="150"/>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="94" t="s">
+        <v>4</v>
+      </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="113"/>
-      <c r="E45" s="149">
-        <f>D45</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="7"/>
+      <c r="D45" s="185"/>
+      <c r="E45" s="114"/>
+      <c r="F45" s="100"/>
       <c r="H45" s="150"/>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="94"/>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="94" t="s">
+        <v>154</v>
+      </c>
       <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="113"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="113">
+        <v>5020</v>
+      </c>
       <c r="E46" s="134">
         <f>D46*91.91%</f>
-        <v>0</v>
+        <v>4613.8819999999996</v>
       </c>
       <c r="F46" s="134">
         <f>D46*8.09%</f>
-        <v>0</v>
+        <v>406.11799999999999</v>
       </c>
       <c r="H46" s="150"/>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="94"/>
-      <c r="B47" s="7"/>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="94" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>157</v>
+      </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="185"/>
+      <c r="D47" s="113">
+        <f>55568.88+6174.32+104266.16</f>
+        <v>166009.35999999999</v>
+      </c>
       <c r="E47" s="134">
         <f>D47*91.91%</f>
-        <v>0</v>
+        <v>152579.20277599996</v>
       </c>
       <c r="F47" s="134">
         <f>D47*8.09%</f>
-        <v>0</v>
+        <v>13430.157223999999</v>
       </c>
       <c r="H47" s="150"/>
     </row>
-    <row r="48" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="95" t="s">
-        <v>128</v>
-      </c>
-      <c r="B48" s="95"/>
-      <c r="C48" s="95"/>
-      <c r="D48" s="107">
-        <f>SUM(D45:D47)</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="159">
-        <f>SUM(E45:E47)</f>
-        <v>0</v>
-      </c>
-      <c r="F48" s="169">
-        <f>SUM(F45:F47)</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="109">
-        <f>E48+F48</f>
-        <v>0</v>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="94" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="113">
+        <v>546846.93999999994</v>
+      </c>
+      <c r="E48" s="134">
+        <f>D48*91.91%</f>
+        <v>502607.02255399991</v>
+      </c>
+      <c r="F48" s="134">
+        <f>D48*8.09%</f>
+        <v>44239.917445999992</v>
       </c>
       <c r="H48" s="150"/>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="185"/>
-      <c r="E49" s="115"/>
-      <c r="F49" s="100"/>
-      <c r="H49" s="150"/>
-    </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="96"/>
+      <c r="C49" s="96"/>
+      <c r="D49" s="108">
+        <f>SUM(D46:D48)</f>
+        <v>717876.29999999993</v>
+      </c>
+      <c r="E49" s="108">
+        <f t="shared" ref="E49:F49" si="6">SUM(E46:E48)</f>
+        <v>659800.10732999991</v>
+      </c>
+      <c r="F49" s="108">
+        <f t="shared" si="6"/>
+        <v>58076.192669999989</v>
+      </c>
+      <c r="G49" s="109">
+        <f>E49+F49</f>
+        <v>717876.29999999993</v>
+      </c>
+      <c r="H49" s="150" t="str">
+        <f>IF(D49=G49, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="185"/>
-      <c r="E50" s="114"/>
-      <c r="F50" s="100"/>
+      <c r="E50" s="115"/>
+      <c r="F50" s="7"/>
       <c r="H50" s="150"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="94" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="185"/>
-      <c r="E51" s="114"/>
-      <c r="F51" s="100"/>
-      <c r="H51" s="150"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="94" t="s">
-        <v>140</v>
-      </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="98"/>
+      <c r="A51" s="114" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" s="176"/>
+      <c r="C51" s="177"/>
+      <c r="D51" s="185">
+        <v>25000</v>
+      </c>
+      <c r="E51" s="149">
+        <f t="shared" ref="E51" si="7">D51</f>
+        <v>25000</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="109">
+        <f t="shared" ref="G51" si="8">D51</f>
+        <v>25000</v>
+      </c>
+      <c r="H51" s="161">
+        <f t="shared" ref="H51" si="9">E51+F51</f>
+        <v>25000</v>
+      </c>
+      <c r="I51" s="178">
+        <f>H51-D51</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="178">
+        <f>G51-D51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="190" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" s="176"/>
+      <c r="C52" s="177"/>
       <c r="D52" s="113">
-        <v>5020</v>
-      </c>
-      <c r="E52" s="134">
-        <f>D52*91.91%</f>
-        <v>4613.8819999999996</v>
-      </c>
-      <c r="F52" s="134">
-        <f>D52*8.09%</f>
-        <v>406.11799999999999</v>
-      </c>
-      <c r="H52" s="150"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="94" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" s="7" t="s">
+        <v>1000000</v>
+      </c>
+      <c r="E52" s="149">
+        <f>D52</f>
+        <v>1000000</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="109">
+        <f>D52</f>
+        <v>1000000</v>
+      </c>
+      <c r="H52" s="161">
+        <f>E52+F52</f>
+        <v>1000000</v>
+      </c>
+      <c r="I52" s="178">
+        <f t="shared" ref="I52:I82" si="10">H52-D52</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="178">
+        <f t="shared" ref="J52:J82" si="11">G52-D52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="190" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="176"/>
+      <c r="C53" s="177"/>
+      <c r="D53" s="113">
+        <v>330000</v>
+      </c>
+      <c r="E53" s="149">
+        <f>D53</f>
+        <v>330000</v>
+      </c>
+      <c r="F53" s="7"/>
+      <c r="G53" s="109">
+        <f>D53</f>
+        <v>330000</v>
+      </c>
+      <c r="H53" s="161">
+        <f>E53+F53</f>
+        <v>330000</v>
+      </c>
+      <c r="I53" s="178">
+        <f>H53-D53</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="178"/>
+    </row>
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="163" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="149">
+        <f t="shared" ref="E54:E59" si="12">D54*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="134">
+        <f t="shared" ref="F54:F59" si="13">D54*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="109">
+        <f t="shared" ref="G54:G82" si="14">D54</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="161">
+        <f t="shared" ref="H54:H82" si="15">E54+F54</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="94" t="s">
         <v>141</v>
       </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="256">
-        <f>55568.88+6174.32+104266.16</f>
-        <v>166009.35999999999</v>
-      </c>
-      <c r="E53" s="134">
-        <f>D53*91.91%</f>
-        <v>152579.20277599996</v>
-      </c>
-      <c r="F53" s="134">
-        <f>D53*8.09%</f>
-        <v>13430.157223999999</v>
-      </c>
-      <c r="H53" s="150"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="B54" s="258" t="s">
-        <v>142</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="256">
-        <v>546846.93999999994</v>
-      </c>
-      <c r="E54" s="134">
-        <f>D54*91.91%</f>
-        <v>502607.02255399991</v>
-      </c>
-      <c r="F54" s="134">
-        <f>D54*8.09%</f>
-        <v>44239.917445999992</v>
-      </c>
-      <c r="H54" s="150"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="95" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="96"/>
-      <c r="C55" s="96"/>
-      <c r="D55" s="108">
-        <f>SUM(D52:D54)</f>
-        <v>717876.29999999993</v>
-      </c>
-      <c r="E55" s="108">
-        <f t="shared" ref="E55:F55" si="7">SUM(E52:E54)</f>
-        <v>659800.10732999991</v>
-      </c>
-      <c r="F55" s="108">
-        <f t="shared" si="7"/>
-        <v>58076.192669999989</v>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="113">
+        <v>129675</v>
+      </c>
+      <c r="E55" s="149">
+        <f t="shared" si="12"/>
+        <v>119184.2925</v>
+      </c>
+      <c r="F55" s="134">
+        <f t="shared" si="13"/>
+        <v>10490.7075</v>
       </c>
       <c r="G55" s="109">
-        <f>E55+F55</f>
-        <v>717876.29999999993</v>
-      </c>
-      <c r="H55" s="150" t="str">
-        <f>IF(D55=G55, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="185"/>
-      <c r="E56" s="115"/>
-      <c r="F56" s="7"/>
-      <c r="H56" s="150"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="114" t="s">
-        <v>139</v>
-      </c>
-      <c r="B57" s="176"/>
-      <c r="C57" s="177"/>
-      <c r="D57" s="185">
-        <v>700000</v>
-      </c>
-      <c r="E57" s="149">
-        <f t="shared" ref="E57" si="8">D57</f>
-        <v>700000</v>
-      </c>
-      <c r="F57" s="7"/>
-      <c r="G57" s="109">
-        <f t="shared" ref="G57" si="9">D57</f>
-        <v>700000</v>
-      </c>
-      <c r="H57" s="161">
-        <f t="shared" ref="H57" si="10">E57+F57</f>
-        <v>700000</v>
-      </c>
-      <c r="I57" s="178">
-        <f>H57-D57</f>
-        <v>0</v>
-      </c>
-      <c r="J57" s="178">
-        <f>G57-D57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="190" t="s">
-        <v>137</v>
-      </c>
-      <c r="B58" s="176"/>
-      <c r="C58" s="177"/>
-      <c r="D58" s="256">
-        <v>1350000</v>
-      </c>
-      <c r="E58" s="149">
-        <f>D58</f>
-        <v>1350000</v>
-      </c>
-      <c r="F58" s="7"/>
-      <c r="G58" s="109">
-        <f>D58</f>
-        <v>1350000</v>
-      </c>
-      <c r="H58" s="161">
-        <f>E58+F58</f>
-        <v>1350000</v>
-      </c>
-      <c r="I58" s="178">
-        <f t="shared" ref="I58:I93" si="11">H58-D58</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="178">
-        <f t="shared" ref="J58:J93" si="12">G58-D58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="190" t="s">
-        <v>168</v>
-      </c>
-      <c r="B59" s="176"/>
-      <c r="C59" s="177"/>
-      <c r="D59" s="256">
-        <v>5000</v>
-      </c>
-      <c r="E59" s="149">
-        <f>D59</f>
-        <v>5000</v>
-      </c>
-      <c r="F59" s="7"/>
-      <c r="G59" s="109">
-        <f>D59</f>
-        <v>5000</v>
-      </c>
-      <c r="H59" s="161">
-        <f>E59+F59</f>
-        <v>5000</v>
-      </c>
-      <c r="I59" s="178">
-        <f>H59-D59</f>
-        <v>0</v>
-      </c>
-      <c r="J59" s="178"/>
-    </row>
-    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="121" t="s">
-        <v>8</v>
-      </c>
-      <c r="B60" s="163"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="113">
-        <v>143638</v>
-      </c>
-      <c r="E60" s="149">
-        <f t="shared" ref="E60:E64" si="13">D60*91.91%</f>
-        <v>132017.68579999998</v>
-      </c>
-      <c r="F60" s="134">
-        <f t="shared" ref="F60:F64" si="14">D60*8.09%</f>
-        <v>11620.314200000001</v>
-      </c>
-      <c r="G60" s="109">
-        <f t="shared" ref="G60:G93" si="15">D60</f>
-        <v>143638</v>
-      </c>
-      <c r="H60" s="161">
-        <f t="shared" ref="H60:H93" si="16">E60+F60</f>
-        <v>143637.99999999997</v>
-      </c>
-      <c r="I60" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="94" t="s">
-        <v>162</v>
-      </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="256">
+        <f t="shared" si="14"/>
         <v>129675</v>
       </c>
-      <c r="E61" s="149">
-        <f t="shared" si="13"/>
-        <v>119184.2925</v>
-      </c>
-      <c r="F61" s="134">
-        <f t="shared" si="14"/>
-        <v>10490.7075</v>
-      </c>
-      <c r="G61" s="109">
+      <c r="H55" s="161">
         <f t="shared" si="15"/>
         <v>129675</v>
       </c>
-      <c r="H61" s="161">
-        <f t="shared" si="16"/>
-        <v>129675</v>
-      </c>
-      <c r="I61" s="178">
+      <c r="I55" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J61" s="178">
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="113">
+        <v>74623.7</v>
+      </c>
+      <c r="E56" s="149">
+        <f>D56*91.91%</f>
+        <v>68586.642669999987</v>
+      </c>
+      <c r="F56" s="134">
+        <f t="shared" si="13"/>
+        <v>6037.0573299999996</v>
+      </c>
+      <c r="G56" s="109">
+        <f t="shared" si="14"/>
+        <v>74623.7</v>
+      </c>
+      <c r="H56" s="161">
+        <f>E56+F56</f>
+        <v>74623.699999999983</v>
+      </c>
+      <c r="I56" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="113">
+        <v>614674.98</v>
+      </c>
+      <c r="E57" s="149">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="113">
-        <v>74622</v>
-      </c>
-      <c r="E62" s="149">
-        <f>D62*91.91%</f>
-        <v>68585.080199999997</v>
-      </c>
-      <c r="F62" s="134">
+        <v>564947.77411799994</v>
+      </c>
+      <c r="F57" s="134">
+        <f t="shared" si="13"/>
+        <v>49727.205881999995</v>
+      </c>
+      <c r="G57" s="109">
         <f t="shared" si="14"/>
-        <v>6036.9197999999997</v>
-      </c>
-      <c r="G62" s="109">
-        <f t="shared" si="15"/>
-        <v>74622</v>
-      </c>
-      <c r="H62" s="161">
-        <f>E62+F62</f>
-        <v>74622</v>
-      </c>
-      <c r="I62" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="256">
         <v>614674.98</v>
       </c>
-      <c r="E63" s="149">
-        <f t="shared" si="13"/>
-        <v>564947.77411799994</v>
-      </c>
-      <c r="F63" s="134">
-        <f t="shared" si="14"/>
-        <v>49727.205881999995</v>
-      </c>
-      <c r="G63" s="109">
+      <c r="H57" s="161">
         <f t="shared" si="15"/>
         <v>614674.98</v>
       </c>
+      <c r="I57" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" s="98" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="98"/>
+      <c r="D58" s="113">
+        <v>1031156.2</v>
+      </c>
+      <c r="E58" s="149">
+        <f t="shared" si="12"/>
+        <v>947735.66341999988</v>
+      </c>
+      <c r="F58" s="134">
+        <f t="shared" si="13"/>
+        <v>83420.53658</v>
+      </c>
+      <c r="G58" s="109">
+        <f t="shared" si="14"/>
+        <v>1031156.2</v>
+      </c>
+      <c r="H58" s="161">
+        <f t="shared" si="15"/>
+        <v>1031156.1999999998</v>
+      </c>
+      <c r="I58" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" s="179"/>
+      <c r="C59" s="180"/>
+      <c r="D59" s="113">
+        <v>305000</v>
+      </c>
+      <c r="E59" s="149">
+        <f t="shared" si="12"/>
+        <v>280325.5</v>
+      </c>
+      <c r="F59" s="134">
+        <f t="shared" si="13"/>
+        <v>24674.5</v>
+      </c>
+      <c r="G59" s="109">
+        <f t="shared" si="14"/>
+        <v>305000</v>
+      </c>
+      <c r="H59" s="161">
+        <f t="shared" si="15"/>
+        <v>305000</v>
+      </c>
+      <c r="I59" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="212" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" s="213"/>
+      <c r="C60" s="214"/>
+      <c r="D60" s="113">
+        <v>98393.96</v>
+      </c>
+      <c r="E60" s="149">
+        <f>D60*91.91%</f>
+        <v>90433.888636000003</v>
+      </c>
+      <c r="F60" s="134">
+        <f>D60*8.09%</f>
+        <v>7960.0713640000004</v>
+      </c>
+      <c r="G60" s="109">
+        <f t="shared" si="14"/>
+        <v>98393.96</v>
+      </c>
+      <c r="H60" s="161">
+        <f>E60+F60</f>
+        <v>98393.96</v>
+      </c>
+      <c r="I60" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="223" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" s="224"/>
+      <c r="C61" s="225"/>
+      <c r="D61" s="113">
+        <v>65500</v>
+      </c>
+      <c r="E61" s="149">
+        <f t="shared" ref="E59:E72" si="16">D61</f>
+        <v>65500</v>
+      </c>
+      <c r="F61" s="134"/>
+      <c r="G61" s="109">
+        <f t="shared" si="14"/>
+        <v>65500</v>
+      </c>
+      <c r="H61" s="161">
+        <f t="shared" si="15"/>
+        <v>65500</v>
+      </c>
+      <c r="I61" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="226" t="s">
+        <v>160</v>
+      </c>
+      <c r="B62" s="227"/>
+      <c r="C62" s="228"/>
+      <c r="D62" s="113">
+        <v>180000</v>
+      </c>
+      <c r="E62" s="149">
+        <f t="shared" si="16"/>
+        <v>180000</v>
+      </c>
+      <c r="F62" s="134"/>
+      <c r="G62" s="109">
+        <f t="shared" si="14"/>
+        <v>180000</v>
+      </c>
+      <c r="H62" s="161">
+        <f t="shared" si="15"/>
+        <v>180000</v>
+      </c>
+      <c r="I62" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="215" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" s="216"/>
+      <c r="C63" s="217"/>
+      <c r="D63" s="113">
+        <v>315000</v>
+      </c>
+      <c r="E63" s="149">
+        <f t="shared" si="16"/>
+        <v>315000</v>
+      </c>
+      <c r="F63" s="134"/>
+      <c r="G63" s="109">
+        <f t="shared" si="14"/>
+        <v>315000</v>
+      </c>
       <c r="H63" s="161">
+        <f t="shared" si="15"/>
+        <v>315000</v>
+      </c>
+      <c r="I63" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="178"/>
+    </row>
+    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="193" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" s="194"/>
+      <c r="C64" s="189"/>
+      <c r="D64" s="113">
+        <v>35000</v>
+      </c>
+      <c r="E64" s="149">
         <f t="shared" si="16"/>
-        <v>614674.98</v>
-      </c>
-      <c r="I63" s="178">
+        <v>35000</v>
+      </c>
+      <c r="F64" s="134"/>
+      <c r="G64" s="109">
+        <f t="shared" si="14"/>
+        <v>35000</v>
+      </c>
+      <c r="H64" s="161">
+        <f t="shared" si="15"/>
+        <v>35000</v>
+      </c>
+      <c r="I64" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J63" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="129" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" s="98" t="s">
-        <v>157</v>
-      </c>
-      <c r="C64" s="98"/>
-      <c r="D64" s="113">
-        <v>846331.1</v>
-      </c>
-      <c r="E64" s="149">
-        <f t="shared" si="13"/>
-        <v>777862.91400999995</v>
-      </c>
-      <c r="F64" s="134">
-        <f t="shared" si="14"/>
-        <v>68468.185989999998</v>
-      </c>
-      <c r="G64" s="109">
-        <f t="shared" si="15"/>
-        <v>846331.1</v>
-      </c>
-      <c r="H64" s="161">
+    </row>
+    <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="193" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="194"/>
+      <c r="C65" s="189"/>
+      <c r="D65" s="113">
+        <v>40000</v>
+      </c>
+      <c r="E65" s="149">
         <f t="shared" si="16"/>
-        <v>846331.1</v>
-      </c>
-      <c r="I64" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="98" t="s">
-        <v>143</v>
-      </c>
-      <c r="B65" s="179"/>
-      <c r="C65" s="180"/>
-      <c r="D65" s="113">
-        <v>235500</v>
-      </c>
-      <c r="E65" s="149">
-        <f t="shared" ref="E65:E81" si="17">D65</f>
-        <v>235500</v>
+        <v>40000</v>
       </c>
       <c r="F65" s="134"/>
       <c r="G65" s="109">
+        <f t="shared" si="14"/>
+        <v>40000</v>
+      </c>
+      <c r="H65" s="161">
         <f t="shared" si="15"/>
-        <v>235500</v>
-      </c>
-      <c r="H65" s="161">
+        <v>40000</v>
+      </c>
+      <c r="I65" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="178">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="98" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" s="114"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="113">
+        <v>143416.32999999999</v>
+      </c>
+      <c r="E66" s="149">
         <f t="shared" si="16"/>
-        <v>235500</v>
-      </c>
-      <c r="I65" s="178">
+        <v>143416.32999999999</v>
+      </c>
+      <c r="F66" s="134"/>
+      <c r="G66" s="109">
+        <f t="shared" si="14"/>
+        <v>143416.32999999999</v>
+      </c>
+      <c r="H66" s="161">
+        <f t="shared" si="15"/>
+        <v>143416.32999999999</v>
+      </c>
+      <c r="I66" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="178"/>
+    </row>
+    <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" s="114"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="113">
+        <f>12100+10400+13800</f>
+        <v>36300</v>
+      </c>
+      <c r="E67" s="149">
+        <f t="shared" si="16"/>
+        <v>36300</v>
+      </c>
+      <c r="F67" s="134"/>
+      <c r="G67" s="109">
+        <f t="shared" si="14"/>
+        <v>36300</v>
+      </c>
+      <c r="H67" s="161">
+        <f t="shared" si="15"/>
+        <v>36300</v>
+      </c>
+      <c r="I67" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="178"/>
+    </row>
+    <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="114"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="113">
+        <v>4200</v>
+      </c>
+      <c r="E68" s="149">
+        <f t="shared" si="16"/>
+        <v>4200</v>
+      </c>
+      <c r="F68" s="7"/>
+      <c r="G68" s="109">
+        <f t="shared" si="14"/>
+        <v>4200</v>
+      </c>
+      <c r="H68" s="161">
+        <f t="shared" si="15"/>
+        <v>4200</v>
+      </c>
+      <c r="I68" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J65" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="219" t="s">
-        <v>154</v>
-      </c>
-      <c r="B66" s="220"/>
-      <c r="C66" s="221"/>
-      <c r="D66" s="113">
-        <v>111026</v>
-      </c>
-      <c r="E66" s="149">
-        <f>D66*91.91%</f>
-        <v>102043.99659999998</v>
-      </c>
-      <c r="F66" s="149">
-        <f>D66*8.09%</f>
-        <v>8982.0033999999996</v>
-      </c>
-      <c r="G66" s="109">
+    </row>
+    <row r="69" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="223" t="s">
+        <v>176</v>
+      </c>
+      <c r="B69" s="224"/>
+      <c r="C69" s="225"/>
+      <c r="D69" s="113">
+        <v>450000</v>
+      </c>
+      <c r="E69" s="149">
+        <f t="shared" si="16"/>
+        <v>450000</v>
+      </c>
+      <c r="F69" s="7"/>
+      <c r="G69" s="109">
+        <f t="shared" si="14"/>
+        <v>450000</v>
+      </c>
+      <c r="H69" s="161">
         <f t="shared" si="15"/>
-        <v>111026</v>
-      </c>
-      <c r="H66" s="161">
-        <f>E66+F66</f>
-        <v>111025.99999999999</v>
-      </c>
-      <c r="I66" s="178">
+        <v>450000</v>
+      </c>
+      <c r="I69" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="178"/>
+    </row>
+    <row r="70" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="223" t="s">
+        <v>178</v>
+      </c>
+      <c r="B70" s="224"/>
+      <c r="C70" s="225"/>
+      <c r="D70" s="113">
+        <v>180000</v>
+      </c>
+      <c r="E70" s="149">
+        <f t="shared" si="16"/>
+        <v>180000</v>
+      </c>
+      <c r="F70" s="7"/>
+      <c r="G70" s="109">
+        <f t="shared" si="14"/>
+        <v>180000</v>
+      </c>
+      <c r="H70" s="161">
+        <f t="shared" si="15"/>
+        <v>180000</v>
+      </c>
+      <c r="I70" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="178"/>
+    </row>
+    <row r="71" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="223" t="s">
+        <v>177</v>
+      </c>
+      <c r="B71" s="224"/>
+      <c r="C71" s="225"/>
+      <c r="D71" s="113">
+        <v>250000</v>
+      </c>
+      <c r="E71" s="149">
+        <f t="shared" si="16"/>
+        <v>250000</v>
+      </c>
+      <c r="F71" s="7"/>
+      <c r="G71" s="109">
+        <f t="shared" si="14"/>
+        <v>250000</v>
+      </c>
+      <c r="H71" s="161">
+        <f t="shared" si="15"/>
+        <v>250000</v>
+      </c>
+      <c r="I71" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="178"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="98" t="s">
+        <v>173</v>
+      </c>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="113">
+        <v>736429.26</v>
+      </c>
+      <c r="E72" s="149">
+        <f t="shared" si="16"/>
+        <v>736429.26</v>
+      </c>
+      <c r="F72" s="134"/>
+      <c r="G72" s="109">
+        <f t="shared" si="14"/>
+        <v>736429.26</v>
+      </c>
+      <c r="H72" s="161">
+        <f t="shared" si="15"/>
+        <v>736429.26</v>
+      </c>
+      <c r="I72" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J66" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="219" t="s">
-        <v>149</v>
-      </c>
-      <c r="B67" s="220"/>
-      <c r="C67" s="221"/>
-      <c r="D67" s="113">
-        <v>104006.06</v>
-      </c>
-      <c r="E67" s="149">
-        <f t="shared" ref="E67:E74" si="18">D67*91.91%</f>
-        <v>95591.969745999988</v>
-      </c>
-      <c r="F67" s="149">
-        <f t="shared" ref="F67:F74" si="19">D67*8.09%</f>
-        <v>8414.0902540000006</v>
-      </c>
-      <c r="G67" s="109">
-        <f>D67</f>
-        <v>104006.06</v>
-      </c>
-      <c r="H67" s="161">
-        <f t="shared" si="16"/>
-        <v>104006.05999999998</v>
-      </c>
-      <c r="I67" s="178">
+      <c r="M72" s="196" t="s">
+        <v>175</v>
+      </c>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="197">
+        <v>232510.18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="196" t="s">
+        <v>175</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="113"/>
+      <c r="E73" s="149">
+        <f t="shared" ref="E72:E80" si="17">D73*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="134">
+        <f t="shared" ref="F72:F81" si="18">D73*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="109">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="161">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J67" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="219" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" s="220"/>
-      <c r="C68" s="221"/>
-      <c r="D68" s="113">
-        <f>104002.96</f>
-        <v>104002.96</v>
-      </c>
-      <c r="E68" s="149">
+      <c r="M73" s="196" t="s">
+        <v>144</v>
+      </c>
+      <c r="N73" s="7"/>
+      <c r="O73" s="7"/>
+      <c r="P73" s="197">
+        <v>357622.29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="196" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="113"/>
+      <c r="E74" s="149">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="134">
         <f t="shared" si="18"/>
-        <v>95589.120536000002</v>
-      </c>
-      <c r="F68" s="149">
-        <f t="shared" si="19"/>
-        <v>8413.8394640000006</v>
-      </c>
-      <c r="G68" s="109">
-        <f t="shared" ref="G68:G74" si="20">D68</f>
-        <v>104002.96</v>
-      </c>
-      <c r="H68" s="161">
-        <f t="shared" si="16"/>
-        <v>104002.96</v>
-      </c>
-      <c r="I68" s="178">
+        <v>0</v>
+      </c>
+      <c r="G74" s="109">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="161">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J68" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="219" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" s="220"/>
-      <c r="C69" s="221"/>
-      <c r="D69" s="113">
-        <f>104002.96</f>
-        <v>104002.96</v>
-      </c>
-      <c r="E69" s="149">
-        <f t="shared" si="18"/>
-        <v>95589.120536000002</v>
-      </c>
-      <c r="F69" s="149">
-        <f t="shared" si="19"/>
-        <v>8413.8394640000006</v>
-      </c>
-      <c r="G69" s="109">
-        <f t="shared" si="20"/>
-        <v>104002.96</v>
-      </c>
-      <c r="H69" s="161">
-        <f t="shared" si="16"/>
-        <v>104002.96</v>
-      </c>
-      <c r="I69" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="219" t="s">
-        <v>149</v>
-      </c>
-      <c r="B70" s="220"/>
-      <c r="C70" s="221"/>
-      <c r="D70" s="113">
-        <f>104002.96</f>
-        <v>104002.96</v>
-      </c>
-      <c r="E70" s="149">
-        <f t="shared" si="18"/>
-        <v>95589.120536000002</v>
-      </c>
-      <c r="F70" s="149">
-        <f t="shared" si="19"/>
-        <v>8413.8394640000006</v>
-      </c>
-      <c r="G70" s="109">
-        <f t="shared" si="20"/>
-        <v>104002.96</v>
-      </c>
-      <c r="H70" s="161">
-        <f t="shared" si="16"/>
-        <v>104002.96</v>
-      </c>
-      <c r="I70" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="202" t="s">
-        <v>148</v>
-      </c>
-      <c r="B71" s="203"/>
-      <c r="C71" s="204"/>
-      <c r="D71" s="113">
-        <v>100419.01</v>
-      </c>
-      <c r="E71" s="149">
-        <f t="shared" si="18"/>
-        <v>92295.112090999988</v>
-      </c>
-      <c r="F71" s="149">
-        <f t="shared" si="19"/>
-        <v>8123.8979089999993</v>
-      </c>
-      <c r="G71" s="109">
-        <f t="shared" si="20"/>
-        <v>100419.01</v>
-      </c>
-      <c r="H71" s="161">
-        <f t="shared" si="16"/>
-        <v>100419.00999999998</v>
-      </c>
-      <c r="I71" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="202" t="s">
-        <v>148</v>
-      </c>
-      <c r="B72" s="203"/>
-      <c r="C72" s="204"/>
-      <c r="D72" s="113">
-        <v>97003.05</v>
-      </c>
-      <c r="E72" s="149">
-        <f t="shared" si="18"/>
-        <v>89155.503254999989</v>
-      </c>
-      <c r="F72" s="149">
-        <f t="shared" si="19"/>
-        <v>7847.5467450000006</v>
-      </c>
-      <c r="G72" s="109">
-        <f t="shared" si="20"/>
-        <v>97003.05</v>
-      </c>
-      <c r="H72" s="161">
-        <f t="shared" si="16"/>
-        <v>97003.049999999988</v>
-      </c>
-      <c r="I72" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J72" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="202" t="s">
-        <v>147</v>
-      </c>
-      <c r="B73" s="203"/>
-      <c r="C73" s="204"/>
-      <c r="D73" s="113">
-        <v>98393.96</v>
-      </c>
-      <c r="E73" s="149">
-        <f t="shared" si="18"/>
-        <v>90433.888636000003</v>
-      </c>
-      <c r="F73" s="149">
-        <f t="shared" si="19"/>
-        <v>7960.0713640000004</v>
-      </c>
-      <c r="G73" s="109">
-        <f t="shared" si="20"/>
-        <v>98393.96</v>
-      </c>
-      <c r="H73" s="161">
-        <f t="shared" si="16"/>
-        <v>98393.96</v>
-      </c>
-      <c r="I73" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="197" t="s">
-        <v>156</v>
-      </c>
-      <c r="B74" s="195"/>
-      <c r="C74" s="196"/>
-      <c r="D74" s="113">
-        <v>99259.05</v>
-      </c>
-      <c r="E74" s="149">
-        <f t="shared" si="18"/>
-        <v>91228.99285499999</v>
-      </c>
-      <c r="F74" s="149">
-        <f t="shared" si="19"/>
-        <v>8030.0571449999998</v>
-      </c>
-      <c r="G74" s="109">
-        <f t="shared" si="20"/>
-        <v>99259.05</v>
-      </c>
-      <c r="H74" s="161">
-        <f t="shared" si="16"/>
-        <v>99259.049999999988</v>
-      </c>
-      <c r="I74" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="230" t="s">
-        <v>170</v>
-      </c>
-      <c r="B75" s="231"/>
-      <c r="C75" s="232"/>
-      <c r="D75" s="256">
-        <v>66000</v>
-      </c>
+      <c r="M74" s="196" t="s">
+        <v>144</v>
+      </c>
+      <c r="N74" s="7"/>
+      <c r="O74" s="7"/>
+      <c r="P74" s="197">
+        <v>358487.12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="196" t="s">
+        <v>144</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="113"/>
       <c r="E75" s="149">
         <f t="shared" si="17"/>
-        <v>66000</v>
-      </c>
-      <c r="F75" s="134"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="134">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
       <c r="G75" s="109">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="161">
         <f t="shared" si="15"/>
-        <v>66000</v>
-      </c>
-      <c r="H75" s="161">
-        <f t="shared" si="16"/>
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="I75" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J75" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="233" t="s">
-        <v>145</v>
-      </c>
-      <c r="B76" s="234"/>
-      <c r="C76" s="235"/>
+    </row>
+    <row r="76" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="98" t="s">
+        <v>174</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
       <c r="D76" s="113">
-        <v>218400</v>
+        <v>186859.86</v>
       </c>
       <c r="E76" s="149">
-        <f t="shared" si="17"/>
-        <v>218400</v>
+        <f t="shared" ref="E76:E78" si="19">D76</f>
+        <v>186859.86</v>
       </c>
       <c r="F76" s="134"/>
       <c r="G76" s="109">
+        <f t="shared" si="14"/>
+        <v>186859.86</v>
+      </c>
+      <c r="H76" s="161">
         <f t="shared" si="15"/>
-        <v>218400</v>
-      </c>
-      <c r="H76" s="161">
-        <f t="shared" si="16"/>
-        <v>218400</v>
+        <v>186859.86</v>
       </c>
       <c r="I76" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J76" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J76" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="259" t="s">
-        <v>173</v>
+    </row>
+    <row r="77" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
-      <c r="D77" s="256">
-        <v>315000</v>
+      <c r="D77" s="113">
+        <v>36300</v>
       </c>
       <c r="E77" s="149">
-        <f t="shared" si="17"/>
-        <v>315000</v>
+        <f t="shared" si="19"/>
+        <v>36300</v>
       </c>
       <c r="F77" s="134"/>
       <c r="G77" s="109">
+        <f t="shared" si="14"/>
+        <v>36300</v>
+      </c>
+      <c r="H77" s="161">
         <f t="shared" si="15"/>
-        <v>315000</v>
-      </c>
-      <c r="H77" s="161">
-        <f t="shared" si="16"/>
-        <v>315000</v>
+        <v>36300</v>
       </c>
       <c r="I77" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J77" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J77" s="178"/>
-    </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="193" t="s">
-        <v>169</v>
-      </c>
-      <c r="B78" s="194"/>
-      <c r="C78" s="189"/>
-      <c r="D78" s="256">
-        <v>35000</v>
+    </row>
+    <row r="78" spans="1:16" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="223" t="s">
+        <v>159</v>
+      </c>
+      <c r="B78" s="224"/>
+      <c r="C78" s="225"/>
+      <c r="D78" s="113">
+        <v>36300</v>
       </c>
       <c r="E78" s="149">
-        <f t="shared" si="17"/>
-        <v>35000</v>
+        <f t="shared" si="19"/>
+        <v>36300</v>
       </c>
       <c r="F78" s="134"/>
       <c r="G78" s="109">
+        <f t="shared" si="14"/>
+        <v>36300</v>
+      </c>
+      <c r="H78" s="161">
         <f t="shared" si="15"/>
-        <v>35000</v>
-      </c>
-      <c r="H78" s="161">
-        <f t="shared" si="16"/>
-        <v>35000</v>
+        <v>36300</v>
       </c>
       <c r="I78" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J78" s="178"/>
+    </row>
+    <row r="79" spans="1:16" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="223" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" s="224"/>
+      <c r="C79" s="225"/>
+      <c r="D79" s="113">
+        <v>430000</v>
+      </c>
+      <c r="E79" s="149">
+        <f t="shared" ref="E79:E82" si="20">D79</f>
+        <v>430000</v>
+      </c>
+      <c r="F79" s="7"/>
+      <c r="G79" s="109">
+        <f t="shared" si="14"/>
+        <v>430000</v>
+      </c>
+      <c r="H79" s="161">
+        <f t="shared" si="15"/>
+        <v>430000</v>
+      </c>
+      <c r="I79" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J79" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J78" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="258" t="s">
-        <v>174</v>
-      </c>
-      <c r="B79" s="114"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="256">
-        <v>143416.32999999999</v>
-      </c>
-      <c r="E79" s="149">
-        <f t="shared" si="17"/>
-        <v>143416.32999999999</v>
-      </c>
-      <c r="F79" s="134"/>
-      <c r="G79" s="109">
-        <f t="shared" si="15"/>
-        <v>143416.32999999999</v>
-      </c>
-      <c r="H79" s="161">
-        <f t="shared" si="16"/>
-        <v>143416.32999999999</v>
-      </c>
-      <c r="I79" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="178"/>
-    </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B80" s="114"/>
+        <v>120</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>142</v>
+      </c>
       <c r="C80" s="7"/>
-      <c r="D80" s="256">
-        <v>12100</v>
+      <c r="D80" s="113">
+        <v>79895</v>
       </c>
       <c r="E80" s="149">
         <f t="shared" si="17"/>
-        <v>12100</v>
-      </c>
-      <c r="F80" s="134"/>
+        <v>73431.494499999986</v>
+      </c>
+      <c r="F80" s="134">
+        <f t="shared" si="18"/>
+        <v>6463.5055000000002</v>
+      </c>
       <c r="G80" s="109">
+        <f t="shared" si="14"/>
+        <v>79895</v>
+      </c>
+      <c r="H80" s="161">
         <f t="shared" si="15"/>
-        <v>12100</v>
-      </c>
-      <c r="H80" s="161">
-        <f t="shared" si="16"/>
-        <v>12100</v>
+        <v>79894.999999999985</v>
       </c>
       <c r="I80" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J80" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J80" s="178"/>
-    </row>
-    <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="257" t="s">
-        <v>176</v>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="B81" s="114"/>
       <c r="C81" s="7"/>
-      <c r="D81" s="256">
-        <v>4200</v>
+      <c r="D81" s="113">
+        <v>1820</v>
       </c>
       <c r="E81" s="149">
-        <f t="shared" si="17"/>
-        <v>4200</v>
-      </c>
-      <c r="F81" s="7"/>
+        <f>D81*91.91%</f>
+        <v>1672.7619999999999</v>
+      </c>
+      <c r="F81" s="7">
+        <f t="shared" si="18"/>
+        <v>147.238</v>
+      </c>
       <c r="G81" s="109">
+        <f t="shared" si="14"/>
+        <v>1820</v>
+      </c>
+      <c r="H81" s="161">
         <f t="shared" si="15"/>
-        <v>4200</v>
-      </c>
-      <c r="H81" s="161">
-        <f t="shared" si="16"/>
-        <v>4200</v>
+        <v>1820</v>
       </c>
       <c r="I81" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J81" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J81" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="255" t="s">
-        <v>167</v>
-      </c>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="256">
-        <v>736429.26</v>
+      <c r="A82" s="248" t="s">
+        <v>166</v>
+      </c>
+      <c r="B82" s="114"/>
+      <c r="C82" s="162"/>
+      <c r="D82" s="113">
+        <v>320000</v>
       </c>
       <c r="E82" s="149">
-        <f t="shared" ref="E82:E89" si="21">D82*91.91%</f>
-        <v>676852.13286599994</v>
-      </c>
-      <c r="F82" s="134">
-        <f t="shared" ref="F82:F90" si="22">D82*8.09%</f>
-        <v>59577.127134000002</v>
-      </c>
+        <f t="shared" si="20"/>
+        <v>320000</v>
+      </c>
+      <c r="F82" s="134"/>
       <c r="G82" s="109">
+        <f t="shared" si="14"/>
+        <v>320000</v>
+      </c>
+      <c r="H82" s="161">
         <f t="shared" si="15"/>
-        <v>736429.26</v>
-      </c>
-      <c r="H82" s="161">
-        <f t="shared" si="16"/>
-        <v>736429.25999999989</v>
+        <v>320000</v>
       </c>
       <c r="I82" s="178">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="178">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J82" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="255" t="s">
-        <v>167</v>
-      </c>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="256">
-        <v>232510.18</v>
-      </c>
-      <c r="E83" s="149">
-        <f t="shared" si="21"/>
-        <v>213700.10643799999</v>
-      </c>
-      <c r="F83" s="134">
-        <f t="shared" si="22"/>
-        <v>18810.073561999998</v>
-      </c>
-      <c r="G83" s="109">
-        <f t="shared" si="15"/>
-        <v>232510.18</v>
-      </c>
-      <c r="H83" s="161">
-        <f t="shared" si="16"/>
-        <v>232510.18</v>
-      </c>
-      <c r="I83" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="255" t="s">
-        <v>167</v>
-      </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="256">
-        <v>357622.29</v>
-      </c>
-      <c r="E84" s="149">
-        <f t="shared" si="21"/>
-        <v>328690.64673899993</v>
-      </c>
-      <c r="F84" s="134">
-        <f t="shared" si="22"/>
-        <v>28931.643260999997</v>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="155"/>
+      <c r="B83" s="156"/>
+      <c r="C83" s="156"/>
+      <c r="D83" s="166"/>
+      <c r="E83" s="149"/>
+      <c r="F83" s="134"/>
+      <c r="G83" s="109"/>
+      <c r="H83" s="161"/>
+      <c r="I83" t="str">
+        <f>IF(G83=H83, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" s="96"/>
+      <c r="C84" s="96"/>
+      <c r="D84" s="108">
+        <f>SUM(D51:D83)</f>
+        <v>7135544.29</v>
+      </c>
+      <c r="E84" s="108">
+        <f>SUM(E51:E83)</f>
+        <v>6946623.4678440001</v>
+      </c>
+      <c r="F84" s="108">
+        <f>SUM(F51:F83)</f>
+        <v>188920.82215600001</v>
       </c>
       <c r="G84" s="109">
-        <f t="shared" si="15"/>
-        <v>357622.29</v>
-      </c>
-      <c r="H84" s="161">
-        <f t="shared" si="16"/>
-        <v>357622.28999999992</v>
+        <f>E84+F84</f>
+        <v>7135544.29</v>
+      </c>
+      <c r="H84" s="150" t="str">
+        <f>IF(D84=G84, "", "Error")</f>
+        <v/>
       </c>
       <c r="I84" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J84" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="255" t="s">
-        <v>167</v>
-      </c>
+        <f>D84-G84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
-      <c r="D85" s="256">
-        <v>358487.12</v>
-      </c>
-      <c r="E85" s="149">
-        <f t="shared" si="21"/>
-        <v>329485.51199199999</v>
-      </c>
-      <c r="F85" s="134">
-        <f t="shared" si="22"/>
-        <v>29001.608007999999</v>
-      </c>
-      <c r="G85" s="109">
-        <f t="shared" si="15"/>
-        <v>358487.12</v>
-      </c>
-      <c r="H85" s="161">
-        <f t="shared" si="16"/>
-        <v>358487.12</v>
-      </c>
-      <c r="I85" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="255" t="s">
-        <v>167</v>
-      </c>
+      <c r="D85" s="185"/>
+      <c r="E85" s="115"/>
+      <c r="F85" s="7"/>
+      <c r="H85" s="150"/>
+    </row>
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
-      <c r="D86" s="256">
-        <v>186859.86</v>
-      </c>
-      <c r="E86" s="149">
-        <f t="shared" si="21"/>
-        <v>171742.89732599998</v>
-      </c>
-      <c r="F86" s="134">
-        <f t="shared" si="22"/>
-        <v>15116.962673999999</v>
-      </c>
-      <c r="G86" s="109">
-        <f t="shared" si="15"/>
-        <v>186859.86</v>
-      </c>
-      <c r="H86" s="161">
-        <f t="shared" si="16"/>
-        <v>186859.86</v>
-      </c>
-      <c r="I86" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J86" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="257" t="s">
-        <v>171</v>
-      </c>
+      <c r="D86" s="185"/>
+      <c r="E86" s="114"/>
+      <c r="F86" s="7"/>
+      <c r="H86" s="150"/>
+    </row>
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
-      <c r="D87" s="256">
-        <v>36300</v>
-      </c>
-      <c r="E87" s="149">
-        <f t="shared" si="21"/>
-        <v>33363.329999999994</v>
-      </c>
-      <c r="F87" s="134">
-        <f t="shared" si="22"/>
-        <v>2936.67</v>
-      </c>
-      <c r="G87" s="109">
-        <f t="shared" si="15"/>
-        <v>36300</v>
-      </c>
-      <c r="H87" s="161">
-        <f t="shared" si="16"/>
-        <v>36299.999999999993</v>
-      </c>
-      <c r="I87" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="230" t="s">
-        <v>172</v>
-      </c>
-      <c r="B88" s="231"/>
-      <c r="C88" s="232"/>
-      <c r="D88" s="256">
-        <v>430000</v>
+      <c r="D87" s="185"/>
+      <c r="E87" s="114"/>
+      <c r="F87" s="7"/>
+      <c r="H87" s="150"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="94" t="s">
+        <v>138</v>
+      </c>
+      <c r="B88" s="98"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="113">
+        <f>67780+35700</f>
+        <v>103480</v>
       </c>
       <c r="E88" s="149">
-        <f t="shared" ref="E81:E91" si="23">D88</f>
-        <v>430000</v>
-      </c>
-      <c r="F88" s="7"/>
-      <c r="G88" s="109">
-        <f t="shared" si="15"/>
-        <v>430000</v>
-      </c>
-      <c r="H88" s="161">
-        <f t="shared" si="16"/>
-        <v>430000</v>
-      </c>
-      <c r="I88" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J88" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>163</v>
-      </c>
+        <f>D88*91.91%</f>
+        <v>95108.467999999993</v>
+      </c>
+      <c r="F88" s="134">
+        <f>D88*8.09%</f>
+        <v>8371.5319999999992</v>
+      </c>
+      <c r="G88" s="160"/>
+      <c r="H88" s="150"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
       <c r="C89" s="7"/>
-      <c r="D89" s="113">
-        <v>79895</v>
-      </c>
-      <c r="E89" s="149">
-        <f t="shared" si="21"/>
-        <v>73431.494499999986</v>
-      </c>
-      <c r="F89" s="134">
-        <f t="shared" si="22"/>
-        <v>6463.5055000000002</v>
-      </c>
-      <c r="G89" s="109">
-        <f t="shared" si="15"/>
-        <v>79895</v>
-      </c>
-      <c r="H89" s="161">
-        <f t="shared" si="16"/>
-        <v>79894.999999999985</v>
-      </c>
-      <c r="I89" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J89" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="258" t="s">
-        <v>177</v>
-      </c>
-      <c r="B90" s="114"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="256">
-        <v>180000</v>
-      </c>
-      <c r="E90" s="149">
-        <f t="shared" si="23"/>
-        <v>180000</v>
-      </c>
-      <c r="F90" s="7">
-        <f t="shared" si="22"/>
-        <v>14562</v>
+      <c r="D89" s="113"/>
+      <c r="E89" s="164">
+        <f>D89</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="7"/>
+      <c r="H89" s="150"/>
+      <c r="I89" s="109"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" s="95"/>
+      <c r="C90" s="95"/>
+      <c r="D90" s="107">
+        <f>SUM(D88:D89)</f>
+        <v>103480</v>
+      </c>
+      <c r="E90" s="107">
+        <f>SUM(E88:E89)</f>
+        <v>95108.467999999993</v>
+      </c>
+      <c r="F90" s="107">
+        <f>SUM(F88:F89)</f>
+        <v>8371.5319999999992</v>
       </c>
       <c r="G90" s="109">
-        <f t="shared" si="15"/>
-        <v>180000</v>
-      </c>
-      <c r="H90" s="161">
-        <f t="shared" si="16"/>
-        <v>194562</v>
-      </c>
-      <c r="I90" s="178">
-        <f t="shared" si="11"/>
-        <v>14562</v>
-      </c>
-      <c r="J90" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f>E90+F90</f>
+        <v>103480</v>
+      </c>
+      <c r="H90" s="150" t="str">
+        <f>IF(D90=G90, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J90" s="109"/>
+    </row>
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7"/>
-      <c r="B91" s="114"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="7"/>
-      <c r="D91" s="256"/>
-      <c r="E91" s="149">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
+      <c r="D91" s="185"/>
+      <c r="E91" s="115"/>
       <c r="F91" s="7"/>
-      <c r="G91" s="109">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H91" s="161">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J91" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="94"/>
-      <c r="B92" s="114"/>
+      <c r="H91" s="150"/>
+    </row>
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
       <c r="C92" s="7"/>
-      <c r="D92" s="256"/>
-      <c r="E92" s="149">
-        <f t="shared" ref="E92:E93" si="24">D92*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F92" s="134">
-        <f t="shared" ref="F92:F93" si="25">D92*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G92" s="109">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="161"/>
-      <c r="I92" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J92" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="B93" s="114"/>
-      <c r="C93" s="162"/>
-      <c r="D93" s="113">
-        <v>50000</v>
-      </c>
-      <c r="E93" s="149">
-        <f t="shared" si="24"/>
-        <v>45954.999999999993</v>
-      </c>
-      <c r="F93" s="134">
-        <f t="shared" si="25"/>
-        <v>4045</v>
-      </c>
-      <c r="G93" s="109">
-        <f t="shared" si="15"/>
-        <v>50000</v>
-      </c>
-      <c r="H93" s="161">
-        <f t="shared" si="16"/>
-        <v>49999.999999999993</v>
-      </c>
-      <c r="I93" s="178">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J93" s="178">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="155"/>
-      <c r="B94" s="156"/>
-      <c r="C94" s="156"/>
-      <c r="D94" s="166"/>
-      <c r="E94" s="149"/>
-      <c r="F94" s="134"/>
-      <c r="G94" s="109"/>
-      <c r="H94" s="161"/>
-      <c r="I94" t="str">
-        <f>IF(G94=H94, "", "Error")</f>
-        <v/>
-      </c>
+      <c r="D92" s="185"/>
+      <c r="E92" s="114"/>
+      <c r="F92" s="7"/>
+      <c r="H92" s="150"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="185"/>
+      <c r="E93" s="114"/>
+      <c r="F93" s="7"/>
+      <c r="H93" s="150"/>
+    </row>
+    <row r="94" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C94" s="7"/>
+      <c r="D94" s="113">
+        <v>246000</v>
+      </c>
+      <c r="E94" s="149">
+        <f>D94*91.91%</f>
+        <v>226098.59999999998</v>
+      </c>
+      <c r="F94" s="134">
+        <f>D94*8.09%</f>
+        <v>19901.400000000001</v>
+      </c>
+      <c r="G94" t="s">
+        <v>171</v>
+      </c>
+      <c r="H94" s="150"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" s="96"/>
-      <c r="C95" s="96"/>
-      <c r="D95" s="108">
-        <f>SUM(D57:D94)</f>
-        <v>8463777.129999999</v>
-      </c>
-      <c r="E95" s="108">
-        <f>SUM(E57:E94)</f>
-        <v>8077952.02128</v>
-      </c>
-      <c r="F95" s="108">
-        <f>SUM(F57:F94)</f>
-        <v>400387.10871999996</v>
-      </c>
-      <c r="G95" s="109">
-        <f>E95+F95</f>
-        <v>8478339.1300000008</v>
-      </c>
-      <c r="H95" s="150" t="str">
-        <f>IF(D95=G95, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I95" s="178">
-        <f>D95-G95</f>
-        <v>-14562.000000001863</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="113">
+        <v>28000</v>
+      </c>
+      <c r="E95" s="149">
+        <f>D95*91.91%</f>
+        <v>25734.799999999999</v>
+      </c>
+      <c r="F95" s="134">
+        <f>D95*8.09%</f>
+        <v>2265.1999999999998</v>
+      </c>
+      <c r="H95" s="150"/>
+      <c r="J95" s="113"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="185"/>
-      <c r="E96" s="115"/>
+      <c r="E96" s="116"/>
       <c r="F96" s="7"/>
       <c r="H96" s="150"/>
-    </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="185"/>
-      <c r="E97" s="114"/>
-      <c r="F97" s="7"/>
-      <c r="H97" s="150"/>
-    </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="J96" s="109"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" s="95"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="107">
+        <f>SUM(D94:D96)</f>
+        <v>274000</v>
+      </c>
+      <c r="E97" s="107">
+        <f>SUM(E94:E96)</f>
+        <v>251833.39999999997</v>
+      </c>
+      <c r="F97" s="107">
+        <f>SUM(F94:F96)</f>
+        <v>22166.600000000002</v>
+      </c>
+      <c r="G97" s="109">
+        <f>E97+F97</f>
+        <v>273999.99999999994</v>
+      </c>
+      <c r="H97" s="150" t="str">
+        <f>IF(D97=G97, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J97" s="109"/>
+    </row>
+    <row r="98" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
-      <c r="D98" s="185"/>
-      <c r="E98" s="114"/>
+      <c r="D98" s="113"/>
+      <c r="E98" s="117"/>
       <c r="F98" s="7"/>
       <c r="H98" s="150"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="94" t="s">
-        <v>153</v>
-      </c>
-      <c r="B99" s="98"/>
+        <v>102</v>
+      </c>
+      <c r="B99" s="7"/>
       <c r="C99" s="7"/>
-      <c r="D99" s="256">
-        <f>67780+35700</f>
-        <v>103480</v>
+      <c r="D99" s="113">
+        <v>116023.77</v>
       </c>
       <c r="E99" s="149">
         <f>D99*91.91%</f>
-        <v>95108.467999999993</v>
+        <v>106637.447007</v>
       </c>
       <c r="F99" s="134">
         <f>D99*8.09%</f>
-        <v>8371.5319999999992</v>
-      </c>
-      <c r="G99" s="160"/>
+        <v>9386.3229929999998</v>
+      </c>
       <c r="H99" s="150"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="7"/>
+      <c r="A100" s="94" t="s">
+        <v>103</v>
+      </c>
       <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="113"/>
-      <c r="E100" s="164">
-        <f>D100</f>
-        <v>0</v>
-      </c>
-      <c r="F100" s="7"/>
+      <c r="C100" s="122"/>
+      <c r="D100" s="113">
+        <v>44400</v>
+      </c>
+      <c r="E100" s="149">
+        <f>D100*91.91%</f>
+        <v>40808.039999999994</v>
+      </c>
+      <c r="F100" s="134">
+        <f>D100*8.09%</f>
+        <v>3591.96</v>
+      </c>
       <c r="H100" s="150"/>
-      <c r="I100" s="109"/>
-    </row>
-    <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="95" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B101" s="95"/>
       <c r="C101" s="95"/>
-      <c r="D101" s="107">
+      <c r="D101" s="158">
         <f>SUM(D99:D100)</f>
-        <v>103480</v>
-      </c>
-      <c r="E101" s="107">
-        <f>SUM(E99:E100)</f>
-        <v>95108.467999999993</v>
-      </c>
-      <c r="F101" s="107">
-        <f>SUM(F99:F100)</f>
-        <v>8371.5319999999992</v>
+        <v>160423.77000000002</v>
+      </c>
+      <c r="E101" s="147">
+        <f t="shared" ref="E101:F101" si="21">SUM(E99:E100)</f>
+        <v>147445.48700699999</v>
+      </c>
+      <c r="F101" s="147">
+        <f t="shared" si="21"/>
+        <v>12978.282993000001</v>
       </c>
       <c r="G101" s="109">
         <f>E101+F101</f>
-        <v>103480</v>
+        <v>160423.76999999999</v>
       </c>
       <c r="H101" s="150" t="str">
         <f>IF(D101=G101, "", "Error")</f>
         <v/>
       </c>
-      <c r="J101" s="109"/>
-    </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
-      <c r="D102" s="185"/>
-      <c r="E102" s="115"/>
+      <c r="D102" s="186"/>
+      <c r="E102" s="12"/>
       <c r="F102" s="7"/>
       <c r="H102" s="150"/>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="185"/>
-      <c r="E103" s="114"/>
-      <c r="F103" s="7"/>
-      <c r="H103" s="150"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="94" t="s">
-        <v>13</v>
-      </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="185"/>
-      <c r="E104" s="114"/>
-      <c r="F104" s="7"/>
+    <row r="103" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" s="99"/>
+      <c r="C103" s="99"/>
+      <c r="D103" s="187"/>
+      <c r="E103" s="118">
+        <f>D103*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="136">
+        <f>D103*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G103" s="109">
+        <f>E103+F103</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="150" t="str">
+        <f>IF(D103=G103, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1"/>
+      <c r="D104" s="184"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="10"/>
+      <c r="G104" s="157"/>
       <c r="H104" s="150"/>
     </row>
-    <row r="105" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="113">
-        <v>222264.92</v>
-      </c>
-      <c r="E105" s="149">
-        <f>D105*91.91%</f>
-        <v>204283.68797199999</v>
-      </c>
-      <c r="F105" s="134">
-        <f>D105*8.09%</f>
-        <v>17981.232028000002</v>
-      </c>
-      <c r="H105" s="150"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="94" t="s">
-        <v>108</v>
-      </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="256">
-        <v>28000</v>
-      </c>
-      <c r="E106" s="149">
-        <f>D106*91.91%</f>
-        <v>25734.799999999999</v>
-      </c>
-      <c r="F106" s="134">
-        <f>D106*8.09%</f>
-        <v>2265.1999999999998</v>
-      </c>
-      <c r="H106" s="150"/>
-      <c r="J106" s="113"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="185"/>
-      <c r="E107" s="116"/>
-      <c r="F107" s="7"/>
-      <c r="H107" s="150"/>
-      <c r="J107" s="109"/>
+    <row r="105" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" s="60"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="188">
+        <f>SUM(D103+D101+D97+D90+D84+D49+D32+D27+D44)</f>
+        <v>9894961.5700000022</v>
+      </c>
+      <c r="E105" s="148">
+        <f>SUM(E103+E101+E97+E90+E84+E49+E32+E27+E44)</f>
+        <v>9482803.8898920007</v>
+      </c>
+      <c r="F105" s="148">
+        <f>SUM(F103+F101+F97+F90+F84+F49+F32+F27+F44)</f>
+        <v>412157.680108</v>
+      </c>
+      <c r="G105" s="109">
+        <f>E105+F105</f>
+        <v>9894961.5700000003</v>
+      </c>
+      <c r="H105" s="150" t="str">
+        <f>IF(D105=G105, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I105" s="178">
+        <f>D105-G105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D106" s="184"/>
+      <c r="E106" s="109"/>
+    </row>
+    <row r="107" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="B107" s="141"/>
+      <c r="C107" s="141"/>
+      <c r="E107" s="109"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="95" t="s">
-        <v>101</v>
-      </c>
-      <c r="B108" s="95"/>
-      <c r="C108" s="95"/>
-      <c r="D108" s="107">
-        <f>SUM(D105:D107)</f>
-        <v>250264.92</v>
-      </c>
-      <c r="E108" s="107">
-        <f>SUM(E105:E107)</f>
-        <v>230018.48797199997</v>
-      </c>
-      <c r="F108" s="107">
-        <f>SUM(F105:F107)</f>
-        <v>20246.432028000003</v>
-      </c>
-      <c r="G108" s="109">
-        <f>E108+F108</f>
-        <v>250264.91999999998</v>
-      </c>
-      <c r="H108" s="150" t="str">
-        <f>IF(D108=G108, "", "Error")</f>
+      <c r="A108" s="1"/>
+      <c r="C108" s="139"/>
+      <c r="E108" s="109"/>
+    </row>
+    <row r="109" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1"/>
+      <c r="C109" s="139"/>
+      <c r="E109" s="109"/>
+    </row>
+    <row r="110" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="143" t="s">
+        <v>30</v>
+      </c>
+      <c r="B110" s="144"/>
+      <c r="C110" s="140">
+        <f>SUM(C108:C109)</f>
+        <v>0</v>
+      </c>
+      <c r="E110" s="109"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E111" s="109"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E112" s="137"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="221" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="222"/>
+      <c r="C113" s="222"/>
+      <c r="D113" s="222"/>
+      <c r="E113" s="171" t="s">
+        <v>22</v>
+      </c>
+      <c r="F113" s="172" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="218"/>
+      <c r="B114" s="219"/>
+      <c r="C114" s="220"/>
+      <c r="D114" s="166"/>
+      <c r="E114" s="149"/>
+      <c r="F114" s="134"/>
+    </row>
+    <row r="115" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="215"/>
+      <c r="B115" s="216"/>
+      <c r="C115" s="173"/>
+      <c r="D115" s="113"/>
+      <c r="E115" s="149">
+        <f t="shared" ref="E115:E116" si="22">D115*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F115" s="134">
+        <f t="shared" ref="F115:F116" si="23">D115*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="215"/>
+      <c r="B116" s="216"/>
+      <c r="C116" s="173"/>
+      <c r="D116" s="113"/>
+      <c r="E116" s="149">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="134">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="215"/>
+      <c r="B117" s="216"/>
+      <c r="C117" s="217"/>
+      <c r="D117" s="113"/>
+      <c r="E117" s="149">
+        <f>D117*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F117" s="134">
+        <f>D117*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="209" t="s">
+        <v>30</v>
+      </c>
+      <c r="B118" s="210"/>
+      <c r="C118" s="211"/>
+      <c r="D118" s="170">
+        <f>SUM(D114:D117)</f>
+        <v>0</v>
+      </c>
+      <c r="E118" s="170">
+        <f>SUM(E114:E117)</f>
+        <v>0</v>
+      </c>
+      <c r="F118" s="170">
+        <f>SUM(F114:F117)</f>
+        <v>0</v>
+      </c>
+      <c r="H118" s="109">
+        <f>E118+F118</f>
+        <v>0</v>
+      </c>
+      <c r="I118" s="150" t="str">
+        <f>IF(D118=H118, "", "Error")</f>
         <v/>
       </c>
-      <c r="J108" s="109"/>
-    </row>
-    <row r="109" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="113"/>
-      <c r="E109" s="117"/>
-      <c r="F109" s="7"/>
-      <c r="H109" s="150"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="113">
-        <v>100104.56</v>
-      </c>
-      <c r="E110" s="149">
-        <f>D110*91.91%</f>
-        <v>92006.101095999984</v>
-      </c>
-      <c r="F110" s="134">
-        <f>D110*8.09%</f>
-        <v>8098.4589040000001</v>
-      </c>
-      <c r="H110" s="150"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="94" t="s">
-        <v>103</v>
-      </c>
-      <c r="B111" s="7"/>
-      <c r="C111" s="122"/>
-      <c r="D111" s="113">
-        <v>44400</v>
-      </c>
-      <c r="E111" s="149">
-        <f>D111*91.91%</f>
-        <v>40808.039999999994</v>
-      </c>
-      <c r="F111" s="134">
-        <f>D111*8.09%</f>
-        <v>3591.96</v>
-      </c>
-      <c r="H111" s="150"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" s="95"/>
-      <c r="C112" s="95"/>
-      <c r="D112" s="158">
-        <f>SUM(D110:D111)</f>
-        <v>144504.56</v>
-      </c>
-      <c r="E112" s="147">
-        <f t="shared" ref="E112:F112" si="26">SUM(E110:E111)</f>
-        <v>132814.14109599998</v>
-      </c>
-      <c r="F112" s="147">
-        <f t="shared" si="26"/>
-        <v>11690.418904</v>
-      </c>
-      <c r="G112" s="109">
-        <f>E112+F112</f>
-        <v>144504.55999999997</v>
-      </c>
-      <c r="H112" s="150" t="str">
-        <f>IF(D112=G112, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="186"/>
-      <c r="E113" s="12"/>
-      <c r="F113" s="7"/>
-      <c r="H113" s="150"/>
-    </row>
-    <row r="114" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="B114" s="99"/>
-      <c r="C114" s="99"/>
-      <c r="D114" s="187"/>
-      <c r="E114" s="118">
-        <f>D114*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F114" s="136">
-        <f>D114*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G114" s="109">
-        <f>E114+F114</f>
-        <v>0</v>
-      </c>
-      <c r="H114" s="150" t="str">
-        <f>IF(D114=G114, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="1"/>
-      <c r="D115" s="184"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="10"/>
-      <c r="G115" s="157"/>
-      <c r="H115" s="150"/>
-    </row>
-    <row r="116" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B116" s="60"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="188">
-        <f>SUM(D114+D112+D108+D101+D95+D55+D35+D30+D48)</f>
-        <v>10659184.91</v>
-      </c>
-      <c r="E116" s="148">
-        <f>SUM(E114+E112+E108+E101+E95+E55+E35+E30+E48)</f>
-        <v>10095751.311878001</v>
-      </c>
-      <c r="F116" s="148">
-        <f>SUM(F114+F112+F108+F101+F95+F55+F35+F30+F48)</f>
-        <v>577995.59812199988</v>
-      </c>
-      <c r="G116" s="109">
-        <f>E116+F116</f>
-        <v>10673746.910000002</v>
-      </c>
-      <c r="H116" s="150" t="str">
-        <f>IF(D116=G116, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I116" s="178">
-        <f>D116-G116</f>
-        <v>-14562.000000001863</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D117" s="184"/>
-      <c r="E117" s="109"/>
-    </row>
-    <row r="118" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="142" t="s">
+    </row>
+    <row r="120" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E120" s="109"/>
+    </row>
+    <row r="121" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="B121" s="103">
+        <f>D105</f>
+        <v>9894961.5700000022</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="104" t="s">
+        <v>107</v>
+      </c>
+      <c r="B122" s="105">
+        <f>D105-D103</f>
+        <v>9894961.5700000022</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D123" s="199"/>
+      <c r="E123" s="199"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B124" s="75"/>
+      <c r="C124" s="76"/>
+      <c r="D124" s="199"/>
+      <c r="E124" s="199"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="B125" s="11">
+        <v>3924460.3236006536</v>
+      </c>
+      <c r="C125" s="78"/>
+      <c r="D125" s="199"/>
+      <c r="E125" s="199"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="B126" s="92">
+        <f>PRORRATEO!G52</f>
+        <v>5340180.0816379944</v>
+      </c>
+      <c r="C126" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="D126" s="199"/>
+      <c r="E126" s="199"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="B127" s="175">
+        <f>-B122</f>
+        <v>-9894961.5700000022</v>
+      </c>
+      <c r="C127" s="76"/>
+      <c r="D127" s="199"/>
+      <c r="E127" s="199"/>
+      <c r="G127" s="113"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B128" s="175">
+        <f>-D118</f>
+        <v>0</v>
+      </c>
+      <c r="C128" s="76"/>
+      <c r="D128" s="199"/>
+      <c r="E128" s="199"/>
+      <c r="G128" s="125"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="B129" s="175">
+        <f>-B136</f>
+        <v>0</v>
+      </c>
+      <c r="C129" s="80"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="B118" s="141"/>
-      <c r="C118" s="141"/>
-      <c r="E118" s="109"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-      <c r="C119" s="139"/>
-      <c r="E119" s="109"/>
-    </row>
-    <row r="120" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="1"/>
-      <c r="C120" s="139"/>
-      <c r="E120" s="109"/>
-    </row>
-    <row r="121" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="143" t="s">
+      <c r="B130" s="93">
+        <f>-C110</f>
+        <v>0</v>
+      </c>
+      <c r="C130" s="80"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131" s="79"/>
+      <c r="B131" s="75"/>
+      <c r="C131" s="80"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="B132" s="81">
+        <f>SUM(B125:B131)</f>
+        <v>-630321.16476135515</v>
+      </c>
+      <c r="C132" s="154"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" s="80"/>
+      <c r="C133" s="76"/>
+      <c r="D133" s="83"/>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C134" s="76"/>
+      <c r="D134" s="109"/>
+      <c r="E134" s="178"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="B135" s="11">
+        <v>-365694.54000000004</v>
+      </c>
+      <c r="C135" s="82"/>
+      <c r="D135" s="178"/>
+      <c r="E135" s="178"/>
+      <c r="F135" s="178"/>
+    </row>
+    <row r="136" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="77" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="93"/>
+      <c r="C136" s="82"/>
+      <c r="D136" s="178"/>
+      <c r="E136" s="195"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" s="77"/>
+      <c r="B137" s="175"/>
+      <c r="C137" s="82"/>
+      <c r="E137" s="109"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" s="77"/>
+      <c r="B138" s="175"/>
+      <c r="C138" s="82"/>
+      <c r="E138" s="109"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B121" s="144"/>
-      <c r="C121" s="140">
-        <f>SUM(C119:C120)</f>
-        <v>0</v>
-      </c>
-      <c r="E121" s="109"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E122" s="109"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E123" s="137"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="228" t="s">
-        <v>114</v>
-      </c>
-      <c r="B124" s="229"/>
-      <c r="C124" s="229"/>
-      <c r="D124" s="229"/>
-      <c r="E124" s="171" t="s">
-        <v>22</v>
-      </c>
-      <c r="F124" s="172" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="225"/>
-      <c r="B125" s="226"/>
-      <c r="C125" s="227"/>
-      <c r="D125" s="166"/>
-      <c r="E125" s="149"/>
-      <c r="F125" s="134"/>
-    </row>
-    <row r="126" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="222" t="s">
-        <v>152</v>
-      </c>
-      <c r="B126" s="223"/>
-      <c r="C126" s="173"/>
-      <c r="D126" s="113">
-        <v>300000</v>
-      </c>
-      <c r="E126" s="149">
-        <f t="shared" ref="E126:E127" si="27">D126*91.91%</f>
-        <v>275730</v>
-      </c>
-      <c r="F126" s="134">
-        <f t="shared" ref="F126:F127" si="28">D126*8.09%</f>
-        <v>24270</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="222" t="s">
-        <v>146</v>
-      </c>
-      <c r="B127" s="223"/>
-      <c r="C127" s="173"/>
-      <c r="D127" s="113">
-        <v>10391.24</v>
-      </c>
-      <c r="E127" s="149">
-        <f t="shared" si="27"/>
-        <v>9550.5886839999985</v>
-      </c>
-      <c r="F127" s="134">
-        <f t="shared" si="28"/>
-        <v>840.65131599999995</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="222"/>
-      <c r="B128" s="223"/>
-      <c r="C128" s="224"/>
-      <c r="D128" s="113"/>
-      <c r="E128" s="149">
-        <f>D128*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F128" s="134">
-        <f>D128*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="216" t="s">
-        <v>30</v>
-      </c>
-      <c r="B129" s="217"/>
-      <c r="C129" s="218"/>
-      <c r="D129" s="170">
-        <f>SUM(D125:D128)</f>
-        <v>310391.24</v>
-      </c>
-      <c r="E129" s="170">
-        <f>SUM(E125:E128)</f>
-        <v>285280.58868400002</v>
-      </c>
-      <c r="F129" s="170">
-        <f>SUM(F125:F128)</f>
-        <v>25110.651315999999</v>
-      </c>
-      <c r="H129" s="109">
-        <f>E129+F129</f>
-        <v>310391.24</v>
-      </c>
-      <c r="I129" s="150" t="str">
-        <f>IF(D129=H129, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E131" s="109"/>
-    </row>
-    <row r="132" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="102" t="s">
-        <v>105</v>
-      </c>
-      <c r="B132" s="103">
-        <f>D116</f>
-        <v>10659184.91</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B133" s="105">
-        <f>D116-D114</f>
-        <v>10659184.91</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D134" s="206"/>
-      <c r="E134" s="206"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="74" t="s">
-        <v>91</v>
-      </c>
-      <c r="B135" s="75"/>
-      <c r="C135" s="76"/>
-      <c r="D135" s="206"/>
-      <c r="E135" s="206"/>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="B136" s="78">
-        <v>6056324.5665496523</v>
-      </c>
-      <c r="C136" s="78"/>
-      <c r="D136" s="206"/>
-      <c r="E136" s="206"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="B137" s="92">
-        <f>PRORRATEO!G52</f>
-        <v>6320855.3670509998</v>
-      </c>
-      <c r="C137" s="78" t="s">
-        <v>94</v>
-      </c>
-      <c r="D137" s="206"/>
-      <c r="E137" s="206"/>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="79" t="s">
-        <v>116</v>
-      </c>
-      <c r="B138" s="175">
-        <f>-B133</f>
-        <v>-10659184.91</v>
-      </c>
-      <c r="C138" s="76"/>
-      <c r="D138" s="206"/>
-      <c r="E138" s="206"/>
-      <c r="G138" s="113"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B139" s="175">
-        <f>-D129</f>
-        <v>-310391.24</v>
-      </c>
-      <c r="C139" s="76"/>
-      <c r="D139" s="206"/>
-      <c r="E139" s="206"/>
-      <c r="G139" s="125"/>
-    </row>
-    <row r="140" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="201" t="s">
-        <v>158</v>
-      </c>
-      <c r="B140" s="175">
-        <v>-338000</v>
-      </c>
-      <c r="C140" s="76"/>
-      <c r="D140" s="198"/>
-      <c r="E140" s="198"/>
-      <c r="G140" s="125"/>
-    </row>
-    <row r="141" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="200" t="s">
-        <v>165</v>
-      </c>
-      <c r="B141" s="175">
-        <v>-308000</v>
-      </c>
+      <c r="B139" s="101">
+        <f>SUM(B135:B138)</f>
+        <v>-365694.54000000004</v>
+      </c>
+      <c r="C139" s="82"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C140" s="83"/>
+      <c r="D140" s="178"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B141" s="80"/>
       <c r="C141" s="76"/>
-      <c r="D141" s="198"/>
-      <c r="E141" s="198"/>
-      <c r="G141" s="125"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="B142" s="175">
-        <f>-B149</f>
-        <v>0</v>
-      </c>
-      <c r="C142" s="80"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="79" t="s">
-        <v>121</v>
-      </c>
-      <c r="B143" s="93">
-        <f>-C121</f>
-        <v>0</v>
-      </c>
-      <c r="C143" s="80"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="79"/>
-      <c r="B144" s="75"/>
-      <c r="C144" s="80"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A145" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="B145" s="81">
-        <f>SUM(B136:B144)</f>
-        <v>761603.78360065282</v>
-      </c>
-      <c r="C145" s="154"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A146" s="80"/>
-      <c r="C146" s="76"/>
-      <c r="D146" s="83"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C147" s="76"/>
-      <c r="D147" s="109"/>
-      <c r="E147" s="178"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A148" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="B148" s="11">
-        <v>-310694.54000000004</v>
-      </c>
-      <c r="C148" s="82"/>
-      <c r="D148" s="178"/>
-      <c r="E148" s="178"/>
-      <c r="F148" s="178"/>
-    </row>
-    <row r="149" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="77" t="s">
-        <v>166</v>
-      </c>
-      <c r="B149" s="93"/>
-      <c r="C149" s="82"/>
-      <c r="D149" s="178"/>
-      <c r="E149" s="199"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A150" s="77"/>
-      <c r="B150" s="175"/>
-      <c r="C150" s="82"/>
-      <c r="E150" s="109"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A151" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="B151" s="175">
-        <v>-55000</v>
-      </c>
-      <c r="C151" s="82"/>
-      <c r="E151" s="109"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A152" s="100" t="s">
-        <v>30</v>
-      </c>
-      <c r="B152" s="101">
-        <f>SUM(B148:B151)</f>
-        <v>-365694.54000000004</v>
-      </c>
-      <c r="C152" s="82"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C153" s="83"/>
-      <c r="D153" s="178"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B154" s="80"/>
-      <c r="C154" s="76"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N156" s="12"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B159" s="205" t="s">
-        <v>164</v>
-      </c>
-      <c r="C159" s="205"/>
-      <c r="D159" s="205"/>
-      <c r="E159" s="205"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B160" s="205"/>
-      <c r="C160" s="205"/>
-      <c r="D160" s="205"/>
-      <c r="E160" s="205"/>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B161" s="205"/>
-      <c r="C161" s="205"/>
-      <c r="D161" s="205"/>
-      <c r="E161" s="205"/>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B162" s="205"/>
-      <c r="C162" s="205"/>
-      <c r="D162" s="205"/>
-      <c r="E162" s="205"/>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B163" s="205"/>
-      <c r="C163" s="205"/>
-      <c r="D163" s="205"/>
-      <c r="E163" s="205"/>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N143" s="12"/>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B146" s="198"/>
+      <c r="C146" s="198"/>
+      <c r="D146" s="198"/>
+      <c r="E146" s="198"/>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="198"/>
+      <c r="C147" s="198"/>
+      <c r="D147" s="198"/>
+      <c r="E147" s="198"/>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B148" s="198"/>
+      <c r="C148" s="198"/>
+      <c r="D148" s="198"/>
+      <c r="E148" s="198"/>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="198"/>
+      <c r="C149" s="198"/>
+      <c r="D149" s="198"/>
+      <c r="E149" s="198"/>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="198"/>
+      <c r="C150" s="198"/>
+      <c r="D150" s="198"/>
+      <c r="E150" s="198"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="B159:E163"/>
-    <mergeCell ref="D134:E139"/>
+  <mergeCells count="18">
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="B146:E150"/>
+    <mergeCell ref="D123:E128"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A62:C62"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4861,15 +4582,15 @@
       <c r="K1" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="239">
-        <f>RESUMEN!D116</f>
-        <v>10659184.91</v>
-      </c>
-      <c r="M1" s="240"/>
+      <c r="L1" s="232">
+        <f>RESUMEN!D105</f>
+        <v>9894961.5700000022</v>
+      </c>
+      <c r="M1" s="233"/>
       <c r="N1" s="152"/>
       <c r="O1" s="135">
         <f>L1*8.09%</f>
-        <v>862328.05921900005</v>
+        <v>800502.39101300016</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -4888,13 +4609,13 @@
       </c>
       <c r="L2" s="8"/>
       <c r="M2" s="152">
-        <f>5500000-150000-3015-250-12+1997000+170000+5497+450+30-1000000</f>
-        <v>6519700</v>
+        <f>(5500000-150000-3015-250-12+1997000+170000+5497+450+30)</f>
+        <v>7519700</v>
       </c>
       <c r="N2" s="153"/>
       <c r="O2" s="135">
         <f>O1-K7-553-50-86-8</f>
-        <v>463199.32129700005</v>
+        <v>387647.71090500016</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -4916,8 +4637,8 @@
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="128">
-        <f>RESUMEN!D129</f>
-        <v>310391.24</v>
+        <f>RESUMEN!D118</f>
+        <v>0</v>
       </c>
       <c r="N3" s="151"/>
       <c r="O3" s="73"/>
@@ -4941,70 +4662,69 @@
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="128">
-        <f>25000+310391+3500-500-800+110+11</f>
-        <v>337712</v>
+        <v>0</v>
       </c>
       <c r="N4" s="124"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="236" t="s">
+      <c r="A5" s="229" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="250" t="s">
+      <c r="B5" s="243" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="229" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="248" t="s">
+      <c r="D5" s="241" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="236" t="s">
+      <c r="E5" s="229" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="236" t="s">
+      <c r="F5" s="229" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="236" t="s">
+      <c r="G5" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="243" t="s">
+      <c r="H5" s="236" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="248" t="s">
+      <c r="I5" s="241" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="241" t="s">
+      <c r="J5" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="241" t="s">
+      <c r="K5" s="234" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="246" t="s">
+      <c r="L5" s="239" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="241" t="s">
+      <c r="M5" s="234" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="241" t="s">
+      <c r="N5" s="234" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="237"/>
-      <c r="B6" s="251"/>
-      <c r="C6" s="237"/>
-      <c r="D6" s="252"/>
-      <c r="E6" s="237"/>
-      <c r="F6" s="237"/>
-      <c r="G6" s="237"/>
-      <c r="H6" s="244"/>
-      <c r="I6" s="249"/>
-      <c r="J6" s="242"/>
-      <c r="K6" s="245"/>
-      <c r="L6" s="247"/>
-      <c r="M6" s="245"/>
-      <c r="N6" s="242"/>
+      <c r="A6" s="230"/>
+      <c r="B6" s="244"/>
+      <c r="C6" s="230"/>
+      <c r="D6" s="245"/>
+      <c r="E6" s="230"/>
+      <c r="F6" s="230"/>
+      <c r="G6" s="230"/>
+      <c r="H6" s="237"/>
+      <c r="I6" s="242"/>
+      <c r="J6" s="235"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="240"/>
+      <c r="M6" s="238"/>
+      <c r="N6" s="235"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -5021,35 +4741,33 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="88">
-        <v>330930.29965100001</v>
+        <v>423542.38923799997</v>
       </c>
       <c r="G7" s="191">
         <f>F7</f>
-        <v>330930.29965100001</v>
+        <v>423542.38923799997</v>
       </c>
       <c r="H7" s="131">
         <f>F7-G7</f>
         <v>0</v>
       </c>
       <c r="I7" s="106">
-        <v>14</v>
-      </c>
-      <c r="J7" s="88">
-        <v>25110.651315999999</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J7" s="88"/>
       <c r="K7" s="88">
-        <v>398431.737922</v>
+        <v>412157.680108</v>
       </c>
       <c r="L7" s="98">
         <v>0</v>
       </c>
       <c r="M7" s="6">
         <f>K7+J7+H7+L7</f>
-        <v>423542.38923799997</v>
+        <v>412157.680108</v>
       </c>
       <c r="N7" s="11">
         <f>M7*6% + M7</f>
-        <v>448954.93259227998</v>
+        <v>436887.14091447997</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -5067,25 +4785,25 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="88">
-        <v>118110.03981451588</v>
+        <v>151158.84501451589</v>
       </c>
       <c r="G8" s="191">
-        <v>118500</v>
+        <v>144100</v>
       </c>
       <c r="H8" s="131">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-389.96018548411666</v>
+        <v>7058.8450145158859</v>
       </c>
       <c r="I8" s="106">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" s="88">
         <f>M$4*E8%</f>
-        <v>7463.435199999999</v>
+        <v>0</v>
       </c>
       <c r="K8" s="88">
         <f>M$2*E8 /100</f>
-        <v>144085.37</v>
+        <v>166185.37</v>
       </c>
       <c r="L8" s="165">
         <f>J$3*E8%+J$4</f>
@@ -5093,11 +4811,11 @@
       </c>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>151158.84501451589</v>
+        <v>173244.21501451588</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>160228.37571538685</v>
+        <v>183638.86791538683</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -5115,38 +4833,37 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="88">
-        <v>222096.62408426331</v>
+        <v>177670.97348426332</v>
       </c>
       <c r="G9" s="192">
-        <f>250969-G34+RESUMEN!D66</f>
-        <v>333122.69579999999</v>
+        <f>214701-G34</f>
+        <v>177670.97519999999</v>
       </c>
       <c r="H9" s="131">
         <f t="shared" si="0"/>
-        <v>-111026.07171573667</v>
+        <v>-1.7157366673927754E-3</v>
       </c>
       <c r="I9" s="106">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J9" s="88">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
-        <v>14217.6752</v>
+        <v>0</v>
       </c>
       <c r="K9" s="88">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
-        <v>274479.37</v>
+        <v>316579.37</v>
       </c>
       <c r="L9" s="165">
-        <f t="shared" ref="L9:L51" si="4">J$3*E9%+J$4</f>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M9" s="6">
-        <f t="shared" ref="M9:M51" si="5">K9+J9+H9+L9</f>
-        <v>177670.97348426332</v>
+        <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
+        <v>326579.3682842633</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="1"/>
-        <v>188331.23189331911</v>
+        <v>346174.13038131909</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -5164,37 +4881,37 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="88">
-        <v>186446.70540596871</v>
+        <v>229352.20620596872</v>
       </c>
       <c r="G10" s="191">
-        <v>151845</v>
+        <v>185159</v>
       </c>
       <c r="H10" s="131">
         <f t="shared" si="0"/>
-        <v>34601.705405968707</v>
+        <v>44193.206205968716</v>
       </c>
       <c r="I10" s="106">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J10" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K10" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L10" s="165">
+        <f t="shared" ref="L9:L51" si="5">J$3*E10%+J$4</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <f t="shared" si="5"/>
-        <v>229352.20620596872</v>
+        <v>257752.68620596873</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="1"/>
-        <v>243113.33857832683</v>
+        <v>273217.84737832687</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -5212,38 +4929,38 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="88">
-        <v>183392.59890000001</v>
+        <v>235209.2316</v>
       </c>
       <c r="G11" s="191">
-        <f>F11</f>
-        <v>183392.59890000001</v>
+        <f>223626</f>
+        <v>223626</v>
       </c>
       <c r="H11" s="131">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11583.231599999999</v>
       </c>
       <c r="I11" s="106">
         <v>9</v>
       </c>
       <c r="J11" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K11" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L11" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
-        <f t="shared" si="5"/>
-        <v>235209.2316</v>
+        <v>269508.94160000002</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="1"/>
-        <v>249321.785496</v>
+        <v>285679.47809600004</v>
       </c>
       <c r="P11" s="109"/>
     </row>
@@ -5262,38 +4979,37 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="88">
-        <v>151846.93319999997</v>
+        <v>194750.50080000001</v>
       </c>
       <c r="G12" s="192">
         <f>F12</f>
-        <v>151846.93319999997</v>
+        <v>194750.50080000001</v>
       </c>
       <c r="H12" s="131">
         <f>F12-G12</f>
         <v>0</v>
       </c>
       <c r="I12" s="106">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K12" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L12" s="165">
+        <v>10000</v>
+      </c>
+      <c r="M12" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
-        <f t="shared" si="5"/>
-        <v>194750.50080000001</v>
+        <v>223559.48</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="1"/>
-        <v>206435.53084800002</v>
+        <v>236973.04880000002</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -5311,38 +5027,37 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="88">
-        <v>167108.97501924171</v>
+        <v>235208.87231924172</v>
       </c>
       <c r="G13" s="192">
-        <f>198655-G50</f>
-        <v>167109.33429999999</v>
+        <f>235209-G50</f>
+        <v>194750.26919999998</v>
       </c>
       <c r="H13" s="131">
         <f t="shared" si="0"/>
-        <v>-0.35928075827541761</v>
+        <v>40458.603119241743</v>
       </c>
       <c r="I13" s="106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K13" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L13" s="165">
+        <v>10000</v>
+      </c>
+      <c r="M13" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="6">
-        <f t="shared" si="5"/>
-        <v>235208.87231924172</v>
+        <v>308384.31311924173</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="1"/>
-        <v>249321.40465839623</v>
+        <v>326887.37190639623</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -5360,38 +5075,38 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="88">
-        <v>151846.93319999997</v>
+        <v>194750.50080000001</v>
       </c>
       <c r="G14" s="191">
-        <f>F14</f>
-        <v>151846.93319999997</v>
+        <f>185159</f>
+        <v>185159</v>
       </c>
       <c r="H14" s="131">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9591.5008000000089</v>
       </c>
       <c r="I14" s="106">
         <v>14</v>
       </c>
       <c r="J14" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K14" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L14" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="6">
-        <f t="shared" si="5"/>
-        <v>194750.50080000001</v>
+        <v>223150.98080000002</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="1"/>
-        <v>206435.53084800002</v>
+        <v>236540.03964800003</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -5403,44 +5118,44 @@
         <v>31</v>
       </c>
       <c r="D15" s="133" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="E15" s="7">
         <v>3.43</v>
       </c>
       <c r="F15" s="88">
-        <v>199779.76944653396</v>
+        <v>235208.61604653395</v>
       </c>
       <c r="G15" s="192">
-        <f>226514-G35</f>
-        <v>199780.38500000001</v>
+        <f>235209+34287-G35</f>
+        <v>235208.94</v>
       </c>
       <c r="H15" s="131">
         <f t="shared" si="0"/>
-        <v>-0.61555346605018713</v>
+        <v>-0.32395346605335362</v>
       </c>
       <c r="I15" s="106">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J15" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K15" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L15" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <f t="shared" si="5"/>
-        <v>235208.61604653395</v>
+        <v>257925.38604653394</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="1"/>
-        <v>249321.13300932597</v>
+        <v>273400.90920932597</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -5452,43 +5167,43 @@
         <v>32</v>
       </c>
       <c r="D16" s="133" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E16" s="7">
         <v>2.84</v>
       </c>
       <c r="F16" s="88">
-        <v>201082.98230066069</v>
+        <v>220949.42580066071</v>
       </c>
       <c r="G16" s="192">
-        <f>201083-G49</f>
-        <v>174884.05729999999</v>
+        <f>220949+33601-G49</f>
+        <v>220948.68119999999</v>
       </c>
       <c r="H16" s="131">
         <f t="shared" si="0"/>
-        <v>26198.925000660704</v>
+        <v>0.74460066072060727</v>
       </c>
       <c r="I16" s="106">
         <v>6</v>
       </c>
       <c r="J16" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K16" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L16" s="165">
         <v>0</v>
       </c>
       <c r="M16" s="6">
-        <f t="shared" si="5"/>
-        <v>220949.42580066071</v>
+        <f t="shared" si="4"/>
+        <v>213560.22460066073</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="1"/>
-        <v>234206.39134870036</v>
+        <v>226373.83807670037</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -5506,38 +5221,38 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="88">
-        <v>214568.00214911473</v>
+        <v>250529.74491111474</v>
       </c>
       <c r="G17" s="191">
-        <f>255356-G47-G48</f>
-        <v>199247.48883799999</v>
+        <f>318418-G47-G48</f>
+        <v>250529.62119999999</v>
       </c>
       <c r="H17" s="131">
         <f t="shared" si="0"/>
-        <v>15320.513311114744</v>
+        <v>0.1237111147493124</v>
       </c>
       <c r="I17" s="106">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J17" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K17" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L17" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="6">
-        <f t="shared" si="5"/>
-        <v>250529.74491111474</v>
+        <v>257925.83371111474</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="1"/>
-        <v>265561.5296057816</v>
+        <v>273401.38373378164</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -5555,38 +5270,38 @@
         <v>2.84</v>
       </c>
       <c r="F18" s="88">
-        <v>148953.67368325134</v>
+        <v>194180.49558325135</v>
       </c>
       <c r="G18" s="191">
-        <f>58000+76000+28000+16000+2000-G51</f>
-        <v>149523.6789</v>
+        <f>223000-G51</f>
+        <v>183912.75160000002</v>
       </c>
       <c r="H18" s="131">
         <f t="shared" si="0"/>
-        <v>-570.0052167486574</v>
+        <v>10267.743983251334</v>
       </c>
       <c r="I18" s="106">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K18" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L18" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="6">
-        <f t="shared" si="5"/>
-        <v>194180.49558325135</v>
+        <v>223827.22398325134</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="1"/>
-        <v>205831.32531824644</v>
+        <v>237256.85742224642</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -5604,38 +5319,38 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="88">
-        <v>183392.92216516795</v>
+        <v>235209.45796516797</v>
       </c>
       <c r="G19" s="192">
-        <f>212265-G41</f>
-        <v>183392.69579999999</v>
+        <f>272239-G41</f>
+        <v>235208.97519999999</v>
       </c>
       <c r="H19" s="131">
         <f t="shared" si="0"/>
-        <v>0.22636516796774231</v>
+        <v>0.48276516798068769</v>
       </c>
       <c r="I19" s="106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J19" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K19" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L19" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="6">
-        <f t="shared" si="5"/>
-        <v>235209.45796516797</v>
+        <v>257926.19276516797</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="1"/>
-        <v>249322.02544307805</v>
+        <v>273401.76433107804</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -5653,38 +5368,38 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="88">
-        <v>151847.82760707469</v>
+        <v>194750.27110707472</v>
       </c>
       <c r="G20" s="191">
-        <f>178047-G38</f>
-        <v>151848.05729999999</v>
+        <f>217106-G38</f>
+        <v>183504.68119999999</v>
       </c>
       <c r="H20" s="131">
         <f t="shared" si="0"/>
-        <v>-0.22969292529160157</v>
+        <v>11245.589907074725</v>
       </c>
       <c r="I20" s="106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K20" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L20" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="6">
-        <f t="shared" si="5"/>
-        <v>194750.27110707472</v>
+        <v>224805.06990707474</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="1"/>
-        <v>206435.28737349919</v>
+        <v>238293.37410149921</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -5702,38 +5417,38 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="88">
-        <v>183392.32449179579</v>
+        <v>235209.86029179581</v>
       </c>
       <c r="G21" s="191">
-        <f>212264-G45</f>
-        <v>183391.69579999999</v>
+        <f>272240-G45</f>
+        <v>235209.97519999999</v>
       </c>
       <c r="H21" s="131">
         <f t="shared" si="0"/>
-        <v>0.62869179580593482</v>
+        <v>-0.1149082041811198</v>
       </c>
       <c r="I21" s="106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K21" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L21" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="6">
-        <f t="shared" si="5"/>
-        <v>235209.86029179581</v>
+        <v>257925.59509179581</v>
       </c>
       <c r="N21" s="11">
         <f t="shared" si="1"/>
-        <v>249322.45190930355</v>
+        <v>273401.13079730357</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -5751,38 +5466,37 @@
         <v>2.84</v>
       </c>
       <c r="F22" s="88">
-        <v>151846.93319999997</v>
+        <v>194750.50080000001</v>
       </c>
       <c r="G22" s="191">
-        <f>F22</f>
-        <v>151846.93319999997</v>
+        <v>185159</v>
       </c>
       <c r="H22" s="131">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9591.5008000000089</v>
       </c>
       <c r="I22" s="106">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J22" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K22" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L22" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="6">
-        <f t="shared" si="5"/>
-        <v>194750.50080000001</v>
+        <v>223150.98080000002</v>
       </c>
       <c r="N22" s="11">
         <f t="shared" si="1"/>
-        <v>206435.53084800002</v>
+        <v>236540.03964800003</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -5800,37 +5514,37 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="88">
-        <v>385103.52163409517</v>
+        <v>57370.666484095156</v>
       </c>
       <c r="G23" s="192">
-        <f>447000-G46+RESUMEN!D71+RESUMEN!D72</f>
-        <v>582942.08675000002</v>
+        <f>118871-G46</f>
+        <v>84583.94</v>
       </c>
       <c r="H23" s="131">
         <f t="shared" si="0"/>
-        <v>-197838.56511590484</v>
+        <v>-27213.273515904846</v>
       </c>
       <c r="I23" s="106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K23" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L23" s="165">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="5"/>
-        <v>57370.666484095156</v>
+        <f t="shared" si="4"/>
+        <v>240712.43648409515</v>
       </c>
       <c r="N23" s="11">
         <f t="shared" si="1"/>
-        <v>60812.906473140865</v>
+        <v>255155.18267314087</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -5848,38 +5562,38 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="88">
-        <v>150534.54517107471</v>
+        <v>191483.98867107474</v>
       </c>
       <c r="G24" s="191">
-        <f>180000-G37</f>
-        <v>153801.05729999999</v>
+        <f>232000-G37</f>
+        <v>198398.68119999999</v>
       </c>
       <c r="H24" s="131">
         <f t="shared" si="0"/>
-        <v>-3266.5121289252711</v>
+        <v>-6914.692528925254</v>
       </c>
       <c r="I24" s="181">
         <v>5</v>
       </c>
       <c r="J24" s="88">
         <f t="shared" si="2"/>
-        <v>9591.0208000000002</v>
+        <v>0</v>
       </c>
       <c r="K24" s="88">
         <f t="shared" si="3"/>
-        <v>185159.48</v>
+        <v>213559.48</v>
       </c>
       <c r="L24" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="6">
-        <f t="shared" si="5"/>
-        <v>191483.98867107474</v>
+        <v>206644.78747107476</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="1"/>
-        <v>202973.02799133922</v>
+        <v>219043.47471933925</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -5897,38 +5611,37 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="88">
-        <v>183392.59890000001</v>
+        <v>235209.2316</v>
       </c>
       <c r="G25" s="191">
         <f>F25</f>
-        <v>183392.59890000001</v>
+        <v>235209.2316</v>
       </c>
       <c r="H25" s="131">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I25" s="106">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J25" s="88">
         <f t="shared" si="2"/>
-        <v>11583.521600000002</v>
+        <v>0</v>
       </c>
       <c r="K25" s="88">
         <f t="shared" si="3"/>
-        <v>223625.71</v>
+        <v>257925.71</v>
       </c>
       <c r="L25" s="165">
+        <v>10000</v>
+      </c>
+      <c r="M25" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="6">
-        <f t="shared" si="5"/>
-        <v>235209.2316</v>
+        <v>267925.70999999996</v>
       </c>
       <c r="N25" s="11">
         <f t="shared" si="1"/>
-        <v>249321.785496</v>
+        <v>284001.25259999995</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -5946,38 +5659,38 @@
         <v>6</v>
       </c>
       <c r="F26" s="88">
-        <v>-352713.925683963</v>
+        <v>-556256.30998396303</v>
       </c>
       <c r="G26" s="192">
-        <f>700000-G30-G31-G36</f>
-        <v>614987.10430000001</v>
+        <f>-G30-G31-G36</f>
+        <v>-109032.8508</v>
       </c>
       <c r="H26" s="132">
         <f t="shared" si="0"/>
-        <v>-967701.029983963</v>
+        <v>-447223.45918396302</v>
       </c>
       <c r="I26" s="106">
         <v>5</v>
       </c>
       <c r="J26" s="88">
         <f t="shared" si="2"/>
-        <v>20262.719999999998</v>
+        <v>0</v>
       </c>
       <c r="K26" s="88">
         <f t="shared" si="3"/>
-        <v>391182</v>
+        <v>451182</v>
       </c>
       <c r="L26" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="6">
-        <f t="shared" si="5"/>
-        <v>-556256.30998396303</v>
+        <v>3958.5408160369843</v>
       </c>
       <c r="N26" s="11">
         <f t="shared" si="1"/>
-        <v>-589631.6885830008</v>
+        <v>4196.0532649992037</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -5995,38 +5708,38 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="88">
-        <v>314921.57273526554</v>
+        <v>403845.12633526558</v>
       </c>
       <c r="G27" s="191">
-        <f>377000-G39-G40</f>
-        <v>314978.01319999999</v>
+        <f>483391-G39-G40</f>
+        <v>403845.0208</v>
       </c>
       <c r="H27" s="131">
         <f t="shared" si="0"/>
-        <v>-56.440464734449051</v>
+        <v>0.10553526558214799</v>
       </c>
       <c r="I27" s="106">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J27" s="88">
         <f t="shared" si="2"/>
-        <v>19891.236799999999</v>
+        <v>0</v>
       </c>
       <c r="K27" s="88">
         <f t="shared" si="3"/>
-        <v>384010.33</v>
+        <v>442910.33</v>
       </c>
       <c r="L27" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="6">
-        <f t="shared" si="5"/>
-        <v>403845.12633526558</v>
+        <v>442910.4355352656</v>
       </c>
       <c r="N27" s="11">
         <f t="shared" si="1"/>
-        <v>428075.83391538152</v>
+        <v>469485.06166738155</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -6044,38 +5757,38 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="88">
-        <v>314286.41577654087</v>
+        <v>304604.19637654093</v>
       </c>
       <c r="G28" s="191">
-        <f>371000-G32-G33+RESUMEN!D74</f>
-        <v>413583.78619999997</v>
+        <f>353860-G32-G33</f>
+        <v>281171.43280000001</v>
       </c>
       <c r="H28" s="131">
         <f t="shared" si="0"/>
-        <v>-99297.370423459099</v>
+        <v>23432.763576540921</v>
       </c>
       <c r="I28" s="106">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J28" s="88">
         <f t="shared" si="2"/>
-        <v>19891.236799999999</v>
+        <v>0</v>
       </c>
       <c r="K28" s="88">
         <f t="shared" si="3"/>
-        <v>384010.33</v>
+        <v>442910.33</v>
       </c>
       <c r="L28" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="6">
-        <f t="shared" si="5"/>
-        <v>304604.19637654093</v>
+        <v>466343.09357654094</v>
       </c>
       <c r="N28" s="11">
         <f t="shared" si="1"/>
-        <v>322880.44815913338</v>
+        <v>494323.67919113341</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -6093,38 +5806,38 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="88">
-        <v>325490.37115669996</v>
+        <v>316080.21825669997</v>
       </c>
       <c r="G29" s="192">
-        <f>401000-G42-G43-G44+RESUMEN!D73</f>
-        <v>413311.71970000002</v>
+        <f>-G42-G43-G44+RESUMEN!D60</f>
+        <v>-12010.373200000002</v>
       </c>
       <c r="H29" s="132">
         <f t="shared" si="0"/>
-        <v>-87821.348543300061</v>
+        <v>328090.5914567</v>
       </c>
       <c r="I29" s="106">
         <v>5</v>
       </c>
       <c r="J29" s="88">
         <f t="shared" si="2"/>
-        <v>19891.236799999999</v>
+        <v>0</v>
       </c>
       <c r="K29" s="88">
         <f t="shared" si="3"/>
-        <v>384010.33</v>
+        <v>442910.33</v>
       </c>
       <c r="L29" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="6">
-        <f t="shared" si="5"/>
-        <v>316080.21825669997</v>
+        <v>771000.92145669996</v>
       </c>
       <c r="N29" s="11">
         <f t="shared" si="1"/>
-        <v>335045.03135210194</v>
+        <v>817260.97674410196</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -6142,11 +5855,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="88">
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="G30" s="191">
         <f t="shared" ref="G30:G34" si="6">F30</f>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="H30" s="131">
         <f t="shared" si="0"/>
@@ -6155,23 +5868,23 @@
       <c r="I30" s="106"/>
       <c r="J30" s="88">
         <f t="shared" si="2"/>
-        <v>1823.6448</v>
+        <v>0</v>
       </c>
       <c r="K30" s="88">
         <f t="shared" si="3"/>
-        <v>35206.379999999997</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="L30" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="6">
-        <f t="shared" si="5"/>
-        <v>37030.024799999999</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="N30" s="11">
         <f t="shared" si="1"/>
-        <v>39251.826287999997</v>
+        <v>43042.762800000004</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -6189,11 +5902,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="88">
-        <v>29406.976500000004</v>
+        <v>37715.766000000003</v>
       </c>
       <c r="G31" s="191">
         <f t="shared" si="6"/>
-        <v>29406.976500000004</v>
+        <v>37715.766000000003</v>
       </c>
       <c r="H31" s="131">
         <f t="shared" si="0"/>
@@ -6202,23 +5915,23 @@
       <c r="I31" s="106"/>
       <c r="J31" s="88">
         <f t="shared" si="2"/>
-        <v>1857.4160000000002</v>
+        <v>0</v>
       </c>
       <c r="K31" s="88">
         <f t="shared" si="3"/>
-        <v>35858.350000000006</v>
+        <v>41358.350000000006</v>
       </c>
       <c r="L31" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="6">
-        <f t="shared" si="5"/>
-        <v>37715.766000000003</v>
+        <v>41358.350000000006</v>
       </c>
       <c r="N31" s="11">
         <f t="shared" si="1"/>
-        <v>39978.711960000001</v>
+        <v>43839.85100000001</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -6236,11 +5949,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="88">
-        <v>24060.253500000003</v>
+        <v>30858.354000000003</v>
       </c>
       <c r="G32" s="191">
         <f>F32</f>
-        <v>24060.253500000003</v>
+        <v>30858.354000000003</v>
       </c>
       <c r="H32" s="131">
         <f t="shared" si="0"/>
@@ -6249,23 +5962,23 @@
       <c r="I32" s="106"/>
       <c r="J32" s="88">
         <f t="shared" si="2"/>
-        <v>1519.7040000000002</v>
+        <v>0</v>
       </c>
       <c r="K32" s="88">
         <f t="shared" si="3"/>
-        <v>29338.65</v>
+        <v>33838.65</v>
       </c>
       <c r="L32" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="6">
-        <f t="shared" si="5"/>
-        <v>30858.354000000003</v>
+        <v>33838.65</v>
       </c>
       <c r="N32" s="11">
         <f t="shared" si="1"/>
-        <v>32709.855240000004</v>
+        <v>35868.969000000005</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -6283,11 +5996,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="88">
-        <v>32615.010299999998</v>
+        <v>41830.213199999998</v>
       </c>
       <c r="G33" s="191">
         <f t="shared" si="6"/>
-        <v>32615.010299999998</v>
+        <v>41830.213199999998</v>
       </c>
       <c r="H33" s="131">
         <f t="shared" si="0"/>
@@ -6296,23 +6009,23 @@
       <c r="I33" s="106"/>
       <c r="J33" s="88">
         <f t="shared" si="2"/>
-        <v>2060.0431999999996</v>
+        <v>0</v>
       </c>
       <c r="K33" s="88">
         <f t="shared" si="3"/>
-        <v>39770.17</v>
+        <v>45870.17</v>
       </c>
       <c r="L33" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="6">
-        <f t="shared" si="5"/>
-        <v>41830.213199999998</v>
+        <v>45870.17</v>
       </c>
       <c r="N33" s="11">
         <f t="shared" si="1"/>
-        <v>44340.025991999995</v>
+        <v>48622.3802</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -6330,11 +6043,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="88">
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="G34" s="191">
         <f t="shared" si="6"/>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="H34" s="131">
         <f t="shared" si="0"/>
@@ -6343,23 +6056,23 @@
       <c r="I34" s="106"/>
       <c r="J34" s="88">
         <f t="shared" si="2"/>
-        <v>1823.6448</v>
+        <v>0</v>
       </c>
       <c r="K34" s="88">
         <f t="shared" si="3"/>
-        <v>35206.379999999997</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="L34" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="6">
-        <f t="shared" si="5"/>
-        <v>37030.024799999999</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="N34" s="11">
         <f t="shared" si="1"/>
-        <v>39251.826287999997</v>
+        <v>43042.762800000004</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -6371,17 +6084,17 @@
         <v>6</v>
       </c>
       <c r="D35" s="133" t="s">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="E35" s="7">
         <v>0.5</v>
       </c>
       <c r="F35" s="11">
-        <v>26733.615000000002</v>
+        <v>34287.06</v>
       </c>
       <c r="G35" s="192">
         <f>F35</f>
-        <v>26733.615000000002</v>
+        <v>34287.06</v>
       </c>
       <c r="H35" s="131">
         <f t="shared" si="0"/>
@@ -6390,23 +6103,23 @@
       <c r="I35" s="106"/>
       <c r="J35" s="88">
         <f t="shared" si="2"/>
-        <v>1688.56</v>
+        <v>0</v>
       </c>
       <c r="K35" s="88">
         <f t="shared" si="3"/>
-        <v>32598.5</v>
+        <v>37598.5</v>
       </c>
       <c r="L35" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="6">
-        <f t="shared" si="5"/>
-        <v>34287.06</v>
+        <v>37598.5</v>
       </c>
       <c r="N35" s="11">
         <f t="shared" si="1"/>
-        <v>36344.283599999995</v>
+        <v>39854.410000000003</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -6424,11 +6137,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="88">
-        <v>26733.615000000002</v>
+        <v>34287.06</v>
       </c>
       <c r="G36" s="191">
         <f t="shared" ref="G36:G41" si="7">F36</f>
-        <v>26733.615000000002</v>
+        <v>34287.06</v>
       </c>
       <c r="H36" s="131">
         <f t="shared" si="0"/>
@@ -6437,23 +6150,23 @@
       <c r="I36" s="106"/>
       <c r="J36" s="88">
         <f t="shared" si="2"/>
-        <v>1688.56</v>
+        <v>0</v>
       </c>
       <c r="K36" s="88">
         <f t="shared" si="3"/>
-        <v>32598.5</v>
+        <v>37598.5</v>
       </c>
       <c r="L36" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="6">
-        <f t="shared" si="5"/>
-        <v>34287.06</v>
+        <v>37598.5</v>
       </c>
       <c r="N36" s="11">
         <f t="shared" si="1"/>
-        <v>36344.283599999995</v>
+        <v>39854.410000000003</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -6471,11 +6184,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="88">
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="G37" s="191">
         <f t="shared" si="7"/>
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="H37" s="131">
         <f t="shared" si="0"/>
@@ -6484,23 +6197,23 @@
       <c r="I37" s="106"/>
       <c r="J37" s="88">
         <f t="shared" si="2"/>
-        <v>1654.7888</v>
+        <v>0</v>
       </c>
       <c r="K37" s="88">
         <f t="shared" si="3"/>
-        <v>31946.53</v>
+        <v>36846.53</v>
       </c>
       <c r="L37" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="6">
-        <f t="shared" si="5"/>
-        <v>33601.318800000001</v>
+        <v>36846.53</v>
       </c>
       <c r="N37" s="11">
         <f t="shared" si="1"/>
-        <v>35617.397927999999</v>
+        <v>39057.321799999998</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -6518,11 +6231,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="88">
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="G38" s="191">
         <f t="shared" si="7"/>
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="H38" s="131">
         <f t="shared" si="0"/>
@@ -6531,23 +6244,23 @@
       <c r="I38" s="106"/>
       <c r="J38" s="88">
         <f t="shared" si="2"/>
-        <v>1654.7888</v>
+        <v>0</v>
       </c>
       <c r="K38" s="88">
         <f t="shared" si="3"/>
-        <v>31946.53</v>
+        <v>36846.53</v>
       </c>
       <c r="L38" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="6">
-        <f t="shared" si="5"/>
-        <v>33601.318800000001</v>
+        <v>36846.53</v>
       </c>
       <c r="N38" s="11">
         <f t="shared" si="1"/>
-        <v>35617.397927999999</v>
+        <v>39057.321799999998</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -6565,11 +6278,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="88">
-        <v>31545.665699999998</v>
+        <v>40458.730800000005</v>
       </c>
       <c r="G39" s="191">
         <f t="shared" si="7"/>
-        <v>31545.665699999998</v>
+        <v>40458.730800000005</v>
       </c>
       <c r="H39" s="131">
         <f t="shared" si="0"/>
@@ -6578,23 +6291,23 @@
       <c r="I39" s="106"/>
       <c r="J39" s="88">
         <f t="shared" si="2"/>
-        <v>1992.5008</v>
+        <v>0</v>
       </c>
       <c r="K39" s="88">
         <f t="shared" si="3"/>
-        <v>38466.230000000003</v>
+        <v>44366.23</v>
       </c>
       <c r="L39" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="6">
-        <f t="shared" si="5"/>
-        <v>40458.730800000005</v>
+        <v>44366.23</v>
       </c>
       <c r="N39" s="11">
         <f t="shared" si="1"/>
-        <v>42886.254648000002</v>
+        <v>47028.203800000003</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -6612,11 +6325,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="88">
-        <v>30476.321099999997</v>
+        <v>39087.248399999997</v>
       </c>
       <c r="G40" s="191">
         <f t="shared" si="7"/>
-        <v>30476.321099999997</v>
+        <v>39087.248399999997</v>
       </c>
       <c r="H40" s="131">
         <f t="shared" si="0"/>
@@ -6625,23 +6338,23 @@
       <c r="I40" s="106"/>
       <c r="J40" s="88">
         <f t="shared" si="2"/>
-        <v>1924.9583999999998</v>
+        <v>0</v>
       </c>
       <c r="K40" s="88">
         <f t="shared" si="3"/>
-        <v>37162.289999999994</v>
+        <v>42862.29</v>
       </c>
       <c r="L40" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="6">
-        <f t="shared" si="5"/>
-        <v>39087.248399999997</v>
+        <v>42862.29</v>
       </c>
       <c r="N40" s="11">
         <f t="shared" si="1"/>
-        <v>41432.483303999994</v>
+        <v>45434.027399999999</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -6659,11 +6372,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="88">
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="G41" s="191">
         <f t="shared" si="7"/>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="H41" s="131">
         <f t="shared" si="0"/>
@@ -6672,23 +6385,23 @@
       <c r="I41" s="106"/>
       <c r="J41" s="88">
         <f t="shared" si="2"/>
-        <v>1823.6448</v>
+        <v>0</v>
       </c>
       <c r="K41" s="88">
         <f t="shared" si="3"/>
-        <v>35206.379999999997</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="L41" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="6">
-        <f t="shared" si="5"/>
-        <v>37030.024799999999</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="N41" s="11">
         <f t="shared" si="1"/>
-        <v>39251.826287999997</v>
+        <v>43042.762800000004</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -6706,11 +6419,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="88">
-        <v>29406.976500000004</v>
+        <v>37715.766000000003</v>
       </c>
       <c r="G42" s="191">
         <f>F42</f>
-        <v>29406.976500000004</v>
+        <v>37715.766000000003</v>
       </c>
       <c r="H42" s="131">
         <f t="shared" si="0"/>
@@ -6719,23 +6432,23 @@
       <c r="I42" s="106"/>
       <c r="J42" s="88">
         <f t="shared" si="2"/>
-        <v>1857.4160000000002</v>
+        <v>0</v>
       </c>
       <c r="K42" s="88">
         <f t="shared" si="3"/>
-        <v>35858.350000000006</v>
+        <v>41358.350000000006</v>
       </c>
       <c r="L42" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="6">
-        <f t="shared" si="5"/>
-        <v>37715.766000000003</v>
+        <v>41358.350000000006</v>
       </c>
       <c r="N42" s="11">
         <f t="shared" si="1"/>
-        <v>39978.711960000001</v>
+        <v>43839.85100000001</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -6753,11 +6466,11 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="88">
-        <v>24060.253500000003</v>
+        <v>30858.354000000003</v>
       </c>
       <c r="G43" s="191">
         <f t="shared" ref="G43:G44" si="8">F43</f>
-        <v>24060.253500000003</v>
+        <v>30858.354000000003</v>
       </c>
       <c r="H43" s="131">
         <f t="shared" si="0"/>
@@ -6766,27 +6479,27 @@
       <c r="I43" s="106"/>
       <c r="J43" s="88">
         <f t="shared" si="2"/>
-        <v>1519.7040000000002</v>
+        <v>0</v>
       </c>
       <c r="K43" s="88">
         <f t="shared" si="3"/>
-        <v>29338.65</v>
+        <v>33838.65</v>
       </c>
       <c r="L43" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="6">
-        <f t="shared" si="5"/>
-        <v>30858.354000000003</v>
+        <v>33838.65</v>
       </c>
       <c r="N43" s="11">
         <f t="shared" si="1"/>
-        <v>32709.855240000004</v>
+        <v>35868.969000000005</v>
       </c>
       <c r="P43" s="109">
         <f>L1-K52</f>
-        <v>4268496.902077999</v>
+        <v>2571447.6198920002</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -6804,11 +6517,11 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="88">
-        <v>32615.010299999998</v>
+        <v>41830.213199999998</v>
       </c>
       <c r="G44" s="191">
         <f t="shared" si="8"/>
-        <v>32615.010299999998</v>
+        <v>41830.213199999998</v>
       </c>
       <c r="H44" s="131">
         <f t="shared" si="0"/>
@@ -6817,23 +6530,23 @@
       <c r="I44" s="106"/>
       <c r="J44" s="88">
         <f t="shared" si="2"/>
-        <v>2060.0431999999996</v>
+        <v>0</v>
       </c>
       <c r="K44" s="88">
         <f t="shared" si="3"/>
-        <v>39770.17</v>
+        <v>45870.17</v>
       </c>
       <c r="L44" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="6">
-        <f t="shared" si="5"/>
-        <v>41830.213199999998</v>
+        <v>45870.17</v>
       </c>
       <c r="N44" s="11">
         <f t="shared" si="1"/>
-        <v>44340.025991999995</v>
+        <v>48622.3802</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -6851,11 +6564,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="88">
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="G45" s="191">
         <f t="shared" ref="G45:G51" si="9">F45</f>
-        <v>28872.304200000002</v>
+        <v>37030.024799999999</v>
       </c>
       <c r="H45" s="131">
         <f t="shared" si="0"/>
@@ -6864,23 +6577,23 @@
       <c r="I45" s="106"/>
       <c r="J45" s="88">
         <f t="shared" si="2"/>
-        <v>1823.6448</v>
+        <v>0</v>
       </c>
       <c r="K45" s="88">
         <f t="shared" si="3"/>
-        <v>35206.379999999997</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="L45" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="6">
-        <f t="shared" si="5"/>
-        <v>37030.024799999999</v>
+        <v>40606.380000000005</v>
       </c>
       <c r="N45" s="11">
         <f t="shared" si="1"/>
-        <v>39251.826287999997</v>
+        <v>43042.762800000004</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -6898,11 +6611,11 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="88">
-        <v>61479.973249999995</v>
+        <v>34287.06</v>
       </c>
       <c r="G46" s="191">
         <f>F46</f>
-        <v>61479.973249999995</v>
+        <v>34287.06</v>
       </c>
       <c r="H46" s="131">
         <f t="shared" si="0"/>
@@ -6911,23 +6624,23 @@
       <c r="I46" s="106"/>
       <c r="J46" s="88">
         <f t="shared" si="2"/>
-        <v>1688.56</v>
+        <v>0</v>
       </c>
       <c r="K46" s="88">
         <f t="shared" si="3"/>
-        <v>32598.5</v>
+        <v>37598.5</v>
       </c>
       <c r="L46" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M46" s="6">
-        <f t="shared" si="5"/>
-        <v>34287.06</v>
+        <v>37598.5</v>
       </c>
       <c r="N46" s="11">
         <f t="shared" si="1"/>
-        <v>36344.283599999995</v>
+        <v>39854.410000000003</v>
       </c>
       <c r="Q46" t="s">
         <v>133</v>
@@ -6948,11 +6661,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="88">
-        <v>28337.6319</v>
+        <v>34287.06</v>
       </c>
       <c r="G47" s="191">
         <f t="shared" si="9"/>
-        <v>28337.6319</v>
+        <v>34287.06</v>
       </c>
       <c r="H47" s="131">
         <f t="shared" si="0"/>
@@ -6961,28 +6674,28 @@
       <c r="I47" s="106"/>
       <c r="J47" s="88">
         <f t="shared" si="2"/>
-        <v>1688.56</v>
+        <v>0</v>
       </c>
       <c r="K47" s="88">
         <f t="shared" si="3"/>
-        <v>32598.5</v>
+        <v>37598.5</v>
       </c>
       <c r="L47" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="6">
-        <f t="shared" si="5"/>
-        <v>34287.06</v>
+        <v>37598.5</v>
       </c>
       <c r="N47" s="11">
         <f t="shared" si="1"/>
-        <v>36344.283599999995</v>
+        <v>39854.410000000003</v>
       </c>
       <c r="O47" s="138"/>
       <c r="Q47" s="135">
         <f>M3-J52</f>
-        <v>0.14079999987734482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -7000,11 +6713,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="88">
-        <v>27770.879261999999</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="G48" s="191">
         <f t="shared" si="9"/>
-        <v>27770.879261999999</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="H48" s="131">
         <f t="shared" si="0"/>
@@ -7013,23 +6726,23 @@
       <c r="I48" s="106"/>
       <c r="J48" s="88">
         <f t="shared" si="2"/>
-        <v>1654.7888</v>
+        <v>0</v>
       </c>
       <c r="K48" s="88">
         <f t="shared" si="3"/>
-        <v>31946.53</v>
+        <v>36846.53</v>
       </c>
       <c r="L48" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="6">
-        <f t="shared" si="5"/>
-        <v>33601.318800000001</v>
+        <v>36846.53</v>
       </c>
       <c r="N48" s="11">
         <f t="shared" si="1"/>
-        <v>35617.397927999999</v>
+        <v>39057.321799999998</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -7048,11 +6761,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="88">
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="G49" s="191">
         <f>F49</f>
-        <v>26198.9427</v>
+        <v>33601.318800000001</v>
       </c>
       <c r="H49" s="131">
         <f t="shared" si="0"/>
@@ -7061,23 +6774,23 @@
       <c r="I49" s="106"/>
       <c r="J49" s="88">
         <f t="shared" si="2"/>
-        <v>1654.7888</v>
+        <v>0</v>
       </c>
       <c r="K49" s="88">
         <f t="shared" si="3"/>
-        <v>31946.53</v>
+        <v>36846.53</v>
       </c>
       <c r="L49" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="6">
-        <f t="shared" si="5"/>
-        <v>33601.318800000001</v>
+        <v>36846.53</v>
       </c>
       <c r="N49" s="11">
         <f t="shared" si="1"/>
-        <v>35617.397927999999</v>
+        <v>39057.321799999998</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -7095,11 +6808,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="88">
-        <v>31545.665699999998</v>
+        <v>40458.730800000005</v>
       </c>
       <c r="G50" s="192">
         <f>F50</f>
-        <v>31545.665699999998</v>
+        <v>40458.730800000005</v>
       </c>
       <c r="H50" s="131">
         <f t="shared" si="0"/>
@@ -7108,23 +6821,23 @@
       <c r="I50" s="106"/>
       <c r="J50" s="88">
         <f t="shared" si="2"/>
-        <v>1992.5008</v>
+        <v>0</v>
       </c>
       <c r="K50" s="88">
         <f t="shared" si="3"/>
-        <v>38466.230000000003</v>
+        <v>44366.23</v>
       </c>
       <c r="L50" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="6">
-        <f t="shared" si="5"/>
-        <v>40458.730800000005</v>
+        <v>44366.23</v>
       </c>
       <c r="N50" s="11">
         <f t="shared" si="1"/>
-        <v>42886.254648000002</v>
+        <v>47028.203800000003</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -7142,11 +6855,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="88">
-        <v>30476.321099999997</v>
+        <v>39087.248399999997</v>
       </c>
       <c r="G51" s="191">
         <f t="shared" si="9"/>
-        <v>30476.321099999997</v>
+        <v>39087.248399999997</v>
       </c>
       <c r="H51" s="131">
         <f t="shared" si="0"/>
@@ -7155,23 +6868,23 @@
       <c r="I51" s="106"/>
       <c r="J51" s="88">
         <f t="shared" si="2"/>
-        <v>1924.9583999999998</v>
+        <v>0</v>
       </c>
       <c r="K51" s="88">
         <f t="shared" si="3"/>
-        <v>37162.289999999994</v>
+        <v>42862.29</v>
       </c>
       <c r="L51" s="165">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M51" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="6">
-        <f t="shared" si="5"/>
-        <v>39087.248399999997</v>
+        <v>42862.29</v>
       </c>
       <c r="N51" s="11">
         <f t="shared" si="1"/>
-        <v>41432.483303999994</v>
+        <v>45434.027399999999</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7185,69 +6898,69 @@
       </c>
       <c r="F52" s="90">
         <f>SUM(F7:F51)</f>
-        <v>4929008.8575203009</v>
+        <v>5354343.2489072988</v>
       </c>
       <c r="G52" s="90">
         <f>SUM(G7:G51)</f>
-        <v>6320855.3670509998</v>
+        <v>5340180.0816379944</v>
       </c>
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
       <c r="J52" s="127">
         <f>SUM(J8:J51)</f>
-        <v>310391.09920000011</v>
+        <v>0</v>
       </c>
       <c r="K52" s="90">
         <f>SUM(K7:K51)</f>
-        <v>6390688.0079220012</v>
+        <v>7323513.9501080019</v>
       </c>
       <c r="L52" s="174">
         <f>SUM(L7:L51)</f>
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="M52" s="91">
         <f>SUM(M7:M51)</f>
-        <v>5354343.2489072988</v>
+        <v>7387677.1173773035</v>
       </c>
       <c r="N52" s="90">
         <f>SUM(N7:N51)</f>
-        <v>5675603.843841739</v>
+        <v>7830937.744419938</v>
       </c>
       <c r="P52" s="135"/>
     </row>
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="138">
         <f>K52-L1</f>
-        <v>-4268496.902077999</v>
+        <v>-2571447.6198920002</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="238"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
+      <c r="C54" s="231"/>
+      <c r="D54" s="231"/>
+      <c r="E54" s="231"/>
+      <c r="F54" s="231"/>
+      <c r="G54" s="231"/>
+      <c r="H54" s="231"/>
+      <c r="I54" s="231"/>
+      <c r="J54" s="231"/>
+      <c r="K54" s="231"/>
+      <c r="L54" s="231"/>
+      <c r="M54" s="231"/>
+      <c r="N54" s="231"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
-      <c r="I55" s="238"/>
-      <c r="J55" s="238"/>
-      <c r="K55" s="238"/>
-      <c r="L55" s="238"/>
-      <c r="M55" s="238"/>
-      <c r="N55" s="238"/>
+      <c r="C55" s="231"/>
+      <c r="D55" s="231"/>
+      <c r="E55" s="231"/>
+      <c r="F55" s="231"/>
+      <c r="G55" s="231"/>
+      <c r="H55" s="231"/>
+      <c r="I55" s="231"/>
+      <c r="J55" s="231"/>
+      <c r="K55" s="231"/>
+      <c r="L55" s="231"/>
+      <c r="M55" s="231"/>
+      <c r="N55" s="231"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="168"/>
@@ -7264,104 +6977,104 @@
       <c r="N56" s="168"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="238" t="s">
+      <c r="C57" s="231" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="238"/>
-      <c r="E57" s="238"/>
-      <c r="F57" s="238"/>
-      <c r="G57" s="238"/>
-      <c r="H57" s="238"/>
-      <c r="I57" s="238"/>
-      <c r="J57" s="238"/>
-      <c r="K57" s="238"/>
-      <c r="L57" s="238"/>
-      <c r="M57" s="238"/>
-      <c r="N57" s="238"/>
+      <c r="D57" s="231"/>
+      <c r="E57" s="231"/>
+      <c r="F57" s="231"/>
+      <c r="G57" s="231"/>
+      <c r="H57" s="231"/>
+      <c r="I57" s="231"/>
+      <c r="J57" s="231"/>
+      <c r="K57" s="231"/>
+      <c r="L57" s="231"/>
+      <c r="M57" s="231"/>
+      <c r="N57" s="231"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="238"/>
-      <c r="D58" s="238"/>
-      <c r="E58" s="238"/>
-      <c r="F58" s="238"/>
-      <c r="G58" s="238"/>
-      <c r="H58" s="238"/>
-      <c r="I58" s="238"/>
-      <c r="J58" s="238"/>
-      <c r="K58" s="238"/>
-      <c r="L58" s="238"/>
-      <c r="M58" s="238"/>
-      <c r="N58" s="238"/>
+      <c r="C58" s="231"/>
+      <c r="D58" s="231"/>
+      <c r="E58" s="231"/>
+      <c r="F58" s="231"/>
+      <c r="G58" s="231"/>
+      <c r="H58" s="231"/>
+      <c r="I58" s="231"/>
+      <c r="J58" s="231"/>
+      <c r="K58" s="231"/>
+      <c r="L58" s="231"/>
+      <c r="M58" s="231"/>
+      <c r="N58" s="231"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="238"/>
-      <c r="D59" s="238"/>
-      <c r="E59" s="238"/>
-      <c r="F59" s="238"/>
-      <c r="G59" s="238"/>
-      <c r="H59" s="238"/>
-      <c r="I59" s="238"/>
-      <c r="J59" s="238"/>
-      <c r="K59" s="238"/>
-      <c r="L59" s="238"/>
-      <c r="M59" s="238"/>
-      <c r="N59" s="238"/>
+      <c r="C59" s="231"/>
+      <c r="D59" s="231"/>
+      <c r="E59" s="231"/>
+      <c r="F59" s="231"/>
+      <c r="G59" s="231"/>
+      <c r="H59" s="231"/>
+      <c r="I59" s="231"/>
+      <c r="J59" s="231"/>
+      <c r="K59" s="231"/>
+      <c r="L59" s="231"/>
+      <c r="M59" s="231"/>
+      <c r="N59" s="231"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="238"/>
-      <c r="D60" s="238"/>
-      <c r="E60" s="238"/>
-      <c r="F60" s="238"/>
-      <c r="G60" s="238"/>
-      <c r="H60" s="238"/>
-      <c r="I60" s="238"/>
-      <c r="J60" s="238"/>
-      <c r="K60" s="238"/>
-      <c r="L60" s="238"/>
-      <c r="M60" s="238"/>
-      <c r="N60" s="238"/>
+      <c r="C60" s="231"/>
+      <c r="D60" s="231"/>
+      <c r="E60" s="231"/>
+      <c r="F60" s="231"/>
+      <c r="G60" s="231"/>
+      <c r="H60" s="231"/>
+      <c r="I60" s="231"/>
+      <c r="J60" s="231"/>
+      <c r="K60" s="231"/>
+      <c r="L60" s="231"/>
+      <c r="M60" s="231"/>
+      <c r="N60" s="231"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="238"/>
-      <c r="D61" s="238"/>
-      <c r="E61" s="238"/>
-      <c r="F61" s="238"/>
-      <c r="G61" s="238"/>
-      <c r="H61" s="238"/>
-      <c r="I61" s="238"/>
-      <c r="J61" s="238"/>
-      <c r="K61" s="238"/>
-      <c r="L61" s="238"/>
-      <c r="M61" s="238"/>
-      <c r="N61" s="238"/>
+      <c r="C61" s="231"/>
+      <c r="D61" s="231"/>
+      <c r="E61" s="231"/>
+      <c r="F61" s="231"/>
+      <c r="G61" s="231"/>
+      <c r="H61" s="231"/>
+      <c r="I61" s="231"/>
+      <c r="J61" s="231"/>
+      <c r="K61" s="231"/>
+      <c r="L61" s="231"/>
+      <c r="M61" s="231"/>
+      <c r="N61" s="231"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="238"/>
-      <c r="D62" s="238"/>
-      <c r="E62" s="238"/>
-      <c r="F62" s="238"/>
-      <c r="G62" s="238"/>
-      <c r="H62" s="238"/>
-      <c r="I62" s="238"/>
-      <c r="J62" s="238"/>
-      <c r="K62" s="238"/>
-      <c r="L62" s="238"/>
-      <c r="M62" s="238"/>
-      <c r="N62" s="238"/>
+      <c r="C62" s="231"/>
+      <c r="D62" s="231"/>
+      <c r="E62" s="231"/>
+      <c r="F62" s="231"/>
+      <c r="G62" s="231"/>
+      <c r="H62" s="231"/>
+      <c r="I62" s="231"/>
+      <c r="J62" s="231"/>
+      <c r="K62" s="231"/>
+      <c r="L62" s="231"/>
+      <c r="M62" s="231"/>
+      <c r="N62" s="231"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="238"/>
-      <c r="D63" s="238"/>
-      <c r="E63" s="238"/>
-      <c r="F63" s="238"/>
-      <c r="G63" s="238"/>
-      <c r="H63" s="238"/>
-      <c r="I63" s="238"/>
-      <c r="J63" s="238"/>
-      <c r="K63" s="238"/>
-      <c r="L63" s="238"/>
-      <c r="M63" s="238"/>
-      <c r="N63" s="238"/>
+      <c r="C63" s="231"/>
+      <c r="D63" s="231"/>
+      <c r="E63" s="231"/>
+      <c r="F63" s="231"/>
+      <c r="G63" s="231"/>
+      <c r="H63" s="231"/>
+      <c r="I63" s="231"/>
+      <c r="J63" s="231"/>
+      <c r="K63" s="231"/>
+      <c r="L63" s="231"/>
+      <c r="M63" s="231"/>
+      <c r="N63" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -7488,10 +7201,10 @@
       <c r="O4" s="49"/>
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="253" t="s">
+      <c r="A5" s="246" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="253" t="s">
+      <c r="B5" s="246" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="55" t="s">
@@ -7503,7 +7216,7 @@
       <c r="E5" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="253" t="s">
+      <c r="F5" s="246" t="s">
         <v>76</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -7525,16 +7238,16 @@
         <v>30</v>
       </c>
       <c r="M5" s="41"/>
-      <c r="N5" s="253" t="s">
+      <c r="N5" s="246" t="s">
         <v>79</v>
       </c>
-      <c r="O5" s="253" t="s">
+      <c r="O5" s="246" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="254"/>
-      <c r="B6" s="254"/>
+      <c r="A6" s="247"/>
+      <c r="B6" s="247"/>
       <c r="C6" s="56" t="s">
         <v>81</v>
       </c>
@@ -7544,7 +7257,7 @@
       <c r="E6" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="254"/>
+      <c r="F6" s="247"/>
       <c r="G6" s="44" t="s">
         <v>82</v>
       </c>
@@ -7564,8 +7277,8 @@
         <v>85</v>
       </c>
       <c r="M6" s="47"/>
-      <c r="N6" s="254"/>
-      <c r="O6" s="254"/>
+      <c r="N6" s="247"/>
+      <c r="O6" s="247"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
